--- a/通讯录.xlsx
+++ b/通讯录.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$236</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="443">
   <si>
     <t>管理员</t>
   </si>
@@ -430,9 +430,6 @@
     <t>曾清桦</t>
   </si>
   <si>
-    <t>吴惠琳</t>
-  </si>
-  <si>
     <t>12tlower</t>
   </si>
   <si>
@@ -529,726 +526,711 @@
     <t>教育行业维护部</t>
   </si>
   <si>
+    <t>xmcustm01</t>
+  </si>
+  <si>
+    <t>搜索增值事业部</t>
+  </si>
+  <si>
+    <t>冯乔芳</t>
+  </si>
+  <si>
+    <t>12t033</t>
+  </si>
+  <si>
+    <t>建站十分</t>
+  </si>
+  <si>
+    <t>XM005</t>
+  </si>
+  <si>
+    <t>叶惠</t>
+  </si>
+  <si>
+    <t>12t052</t>
+  </si>
+  <si>
+    <t>蓝淑敏</t>
+  </si>
+  <si>
+    <t>12t092</t>
+  </si>
+  <si>
+    <t>张唯唯</t>
+  </si>
+  <si>
+    <t>12t024</t>
+  </si>
+  <si>
+    <t>郑秀东</t>
+  </si>
+  <si>
+    <t>xm020</t>
+  </si>
+  <si>
+    <t>叶晓欢</t>
+  </si>
+  <si>
+    <t>12t087</t>
+  </si>
+  <si>
+    <t>林华卿</t>
+  </si>
+  <si>
+    <t>12t043</t>
+  </si>
+  <si>
+    <t>程秋平</t>
+  </si>
+  <si>
+    <t>12t016</t>
+  </si>
+  <si>
+    <t>新开三部</t>
+  </si>
+  <si>
+    <t>刘珏</t>
+  </si>
+  <si>
+    <t>12t005</t>
+  </si>
+  <si>
+    <t>林霖</t>
+  </si>
+  <si>
+    <t>12t032</t>
+  </si>
+  <si>
+    <t>童莺莺</t>
+  </si>
+  <si>
+    <t>12t050</t>
+  </si>
+  <si>
+    <t>徐林萍</t>
+  </si>
+  <si>
+    <t>12t082</t>
+  </si>
+  <si>
+    <t>林裕芳</t>
+  </si>
+  <si>
+    <t>12t090</t>
+  </si>
+  <si>
+    <t>张静</t>
+  </si>
+  <si>
+    <t>12t1002</t>
+  </si>
+  <si>
+    <t>廖淑云</t>
+  </si>
+  <si>
+    <t>12t089</t>
+  </si>
+  <si>
+    <t>黄迷</t>
+  </si>
+  <si>
+    <t>12t014</t>
+  </si>
+  <si>
+    <t>黄明华</t>
+  </si>
+  <si>
+    <t>12t1008</t>
+  </si>
+  <si>
+    <t>郑文星</t>
+  </si>
+  <si>
+    <t>12t1009</t>
+  </si>
+  <si>
+    <t>郑淑敏</t>
+  </si>
+  <si>
+    <t>12t091</t>
+  </si>
+  <si>
+    <t>12t066</t>
+  </si>
+  <si>
+    <t>陈碧云</t>
+  </si>
+  <si>
+    <t>12t047</t>
+  </si>
+  <si>
+    <t>赖春连</t>
+  </si>
+  <si>
+    <t>12t069</t>
+  </si>
+  <si>
+    <t>陈巧云</t>
+  </si>
+  <si>
+    <t>12t029</t>
+  </si>
+  <si>
+    <t>江媚</t>
+  </si>
+  <si>
+    <t>12t030</t>
+  </si>
+  <si>
+    <t>陈丽环</t>
+  </si>
+  <si>
+    <t>12t1015</t>
+  </si>
+  <si>
+    <t>李远红</t>
+  </si>
+  <si>
+    <t>12t1010</t>
+  </si>
+  <si>
+    <t>池紫婷</t>
+  </si>
+  <si>
+    <t>12t1012</t>
+  </si>
+  <si>
+    <t>12t1028</t>
+  </si>
+  <si>
+    <t>行业一部</t>
+  </si>
+  <si>
+    <t>xmk01</t>
+  </si>
+  <si>
+    <t>厦门KOL</t>
+  </si>
+  <si>
+    <t>林佳惠</t>
+  </si>
+  <si>
+    <t>xmk03</t>
+  </si>
+  <si>
+    <t>邓玲玲</t>
+  </si>
+  <si>
+    <t>12t095</t>
+  </si>
+  <si>
+    <t>失效挽救部</t>
+  </si>
+  <si>
+    <t>失效挽救</t>
+  </si>
+  <si>
+    <t>纪荣裕</t>
+  </si>
+  <si>
+    <t>12t039</t>
+  </si>
+  <si>
+    <t>医疗事业部</t>
+  </si>
+  <si>
+    <t>吴晓燕</t>
+  </si>
+  <si>
+    <t>12t036</t>
+  </si>
+  <si>
+    <t>叶姗姗</t>
+  </si>
+  <si>
+    <t>12t012</t>
+  </si>
+  <si>
+    <t>陈玉云</t>
+  </si>
+  <si>
+    <t>12t1029</t>
+  </si>
+  <si>
+    <t>方秋燕</t>
+  </si>
+  <si>
+    <t>12t018</t>
+  </si>
+  <si>
+    <t>泉州医疗</t>
+  </si>
+  <si>
+    <t>张秀梅</t>
+  </si>
+  <si>
+    <t>12t1034</t>
+  </si>
+  <si>
+    <t>陈鹭霞</t>
+  </si>
+  <si>
+    <t>12t1027</t>
+  </si>
+  <si>
+    <t>汤斐莉</t>
+  </si>
+  <si>
+    <t>12t015</t>
+  </si>
+  <si>
+    <t>林桂英</t>
+  </si>
+  <si>
+    <t>12t063</t>
+  </si>
+  <si>
+    <t>王智勇</t>
+  </si>
+  <si>
+    <t>12t096</t>
+  </si>
+  <si>
+    <t>梁烨</t>
+  </si>
+  <si>
+    <t>12t094</t>
+  </si>
+  <si>
+    <t>林志龙</t>
+  </si>
+  <si>
+    <t>12t1023</t>
+  </si>
+  <si>
+    <t>苏晨</t>
+  </si>
+  <si>
+    <t>12t002</t>
+  </si>
+  <si>
+    <t>12t053</t>
+  </si>
+  <si>
+    <t>xmcustm11</t>
+  </si>
+  <si>
+    <t>泉州增值运营部</t>
+  </si>
+  <si>
+    <t>叶彩华</t>
+  </si>
+  <si>
+    <t>xmcustm08</t>
+  </si>
+  <si>
+    <t>泉州KOL</t>
+  </si>
+  <si>
+    <t>李华</t>
+  </si>
+  <si>
+    <t>xm009</t>
+  </si>
+  <si>
+    <t>王丽真</t>
+  </si>
+  <si>
+    <t>12t1031</t>
+  </si>
+  <si>
+    <t>许少鸣</t>
+  </si>
+  <si>
+    <t>12t022</t>
+  </si>
+  <si>
+    <t>王真珍</t>
+  </si>
+  <si>
+    <t>12t097</t>
+  </si>
+  <si>
+    <t>徐灵钰</t>
+  </si>
+  <si>
+    <t>12t099</t>
+  </si>
+  <si>
+    <t>游瑞凤</t>
+  </si>
+  <si>
+    <t>12t059</t>
+  </si>
+  <si>
+    <t>李丽红</t>
+  </si>
+  <si>
+    <t>12t061</t>
+  </si>
+  <si>
+    <t>胡艺红</t>
+  </si>
+  <si>
+    <t>xm022</t>
+  </si>
+  <si>
+    <t>泉州维护二部</t>
+  </si>
+  <si>
+    <t>曾达威</t>
+  </si>
+  <si>
+    <t>12t031</t>
+  </si>
+  <si>
+    <t>12t076</t>
+  </si>
+  <si>
+    <t>12t077</t>
+  </si>
+  <si>
+    <t>林小凤</t>
+  </si>
+  <si>
+    <t>12t026</t>
+  </si>
+  <si>
+    <t>曾雅芳</t>
+  </si>
+  <si>
+    <t>12t1017</t>
+  </si>
+  <si>
+    <t>林秋琼</t>
+  </si>
+  <si>
+    <t>12t060</t>
+  </si>
+  <si>
+    <t>黄锴</t>
+  </si>
+  <si>
+    <t>12t006</t>
+  </si>
+  <si>
+    <t>张婷婷</t>
+  </si>
+  <si>
+    <t>12t1020</t>
+  </si>
+  <si>
+    <t>黄凤苗</t>
+  </si>
+  <si>
+    <t>xm019</t>
+  </si>
+  <si>
+    <t>吴燕红</t>
+  </si>
+  <si>
+    <t>12t013</t>
+  </si>
+  <si>
+    <t>王凤钦</t>
+  </si>
+  <si>
+    <t>12t085</t>
+  </si>
+  <si>
+    <t>傅佳玲</t>
+  </si>
+  <si>
+    <t>12t079</t>
+  </si>
+  <si>
+    <t>吴敏凤</t>
+  </si>
+  <si>
+    <t>12t080</t>
+  </si>
+  <si>
+    <t>张滟莲</t>
+  </si>
+  <si>
+    <t>12t041</t>
+  </si>
+  <si>
+    <t>邱彬彬</t>
+  </si>
+  <si>
+    <t>KOLQZ01</t>
+  </si>
+  <si>
+    <t>陈浩</t>
+  </si>
+  <si>
+    <t>qzko1</t>
+  </si>
+  <si>
+    <t>施桂兰</t>
+  </si>
+  <si>
+    <t>12t1014</t>
+  </si>
+  <si>
+    <t>陈燕秀</t>
+  </si>
+  <si>
+    <t>xm021</t>
+  </si>
+  <si>
+    <t>吴清玉</t>
+  </si>
+  <si>
+    <t>12t020</t>
+  </si>
+  <si>
+    <t>游惠卿</t>
+  </si>
+  <si>
+    <t>12t083</t>
+  </si>
+  <si>
+    <t>林聪义</t>
+  </si>
+  <si>
+    <t>12t038</t>
+  </si>
+  <si>
+    <t>黄淑玲</t>
+  </si>
+  <si>
+    <t>12t1016</t>
+  </si>
+  <si>
+    <t>连海珠</t>
+  </si>
+  <si>
+    <t>12t081</t>
+  </si>
+  <si>
+    <t>洪宏</t>
+  </si>
+  <si>
+    <t>12t1019</t>
+  </si>
+  <si>
+    <t>陈秋菊</t>
+  </si>
+  <si>
+    <t>zlfeed01</t>
+  </si>
+  <si>
+    <t>运营策略中心</t>
+  </si>
+  <si>
+    <t>漳州培训</t>
+  </si>
+  <si>
+    <t>林惠兰</t>
+  </si>
+  <si>
+    <t>12t1013</t>
+  </si>
+  <si>
+    <t>丁洁</t>
+  </si>
+  <si>
+    <t>12t1035</t>
+  </si>
+  <si>
+    <t>夏皖鹭</t>
+  </si>
+  <si>
+    <t>xiamenzongdai，xmzhuce01</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>12t068</t>
+  </si>
+  <si>
+    <t>行发基木鱼</t>
+  </si>
+  <si>
+    <t>12t086</t>
+  </si>
+  <si>
+    <t>朱书兰</t>
+  </si>
+  <si>
+    <t>xm026</t>
+  </si>
+  <si>
+    <t>信息流VIP</t>
+  </si>
+  <si>
+    <t>萧月梅</t>
+  </si>
+  <si>
+    <t>12t71</t>
+  </si>
+  <si>
+    <t>胡晓惠</t>
+  </si>
+  <si>
+    <t>12t74</t>
+  </si>
+  <si>
+    <t>林丹丹</t>
+  </si>
+  <si>
+    <t>12t034</t>
+  </si>
+  <si>
+    <t>姚美玲</t>
+  </si>
+  <si>
+    <t>12t011</t>
+  </si>
+  <si>
+    <t>陈雪梅</t>
+  </si>
+  <si>
+    <t>12t051</t>
+  </si>
+  <si>
+    <t>詹大钧</t>
+  </si>
+  <si>
+    <t>12t028</t>
+  </si>
+  <si>
+    <t>郑博萱</t>
+  </si>
+  <si>
+    <t>12t1022</t>
+  </si>
+  <si>
+    <t>朱丽珊</t>
+  </si>
+  <si>
+    <t>12t042</t>
+  </si>
+  <si>
+    <t>葛晓丹</t>
+  </si>
+  <si>
+    <t>12t093</t>
+  </si>
+  <si>
+    <t>李丹凤</t>
+  </si>
+  <si>
+    <t>12t017</t>
+  </si>
+  <si>
+    <t>郭琳娟</t>
+  </si>
+  <si>
+    <t>12t064</t>
+  </si>
+  <si>
+    <t>12t72</t>
+  </si>
+  <si>
+    <t>杨晶晶</t>
+  </si>
+  <si>
+    <t>12t037</t>
+  </si>
+  <si>
+    <t>KOLXM02</t>
+  </si>
+  <si>
+    <t>大客KOL销售</t>
+  </si>
+  <si>
+    <t>林洁</t>
+  </si>
+  <si>
+    <t>xmk04</t>
+  </si>
+  <si>
+    <t>郑燕森</t>
+  </si>
+  <si>
+    <t>qzk02</t>
+  </si>
+  <si>
+    <t>泉州KOL客服</t>
+  </si>
+  <si>
+    <t>许珊珊</t>
+  </si>
+  <si>
+    <t>xmkuang03</t>
+  </si>
+  <si>
+    <t>xmfq01</t>
+  </si>
+  <si>
+    <t>kuangjiaxm02，xmkuang01</t>
+  </si>
+  <si>
+    <t>xmkuang28</t>
+  </si>
+  <si>
+    <t>12t048</t>
+  </si>
+  <si>
+    <t>大客医疗</t>
+  </si>
+  <si>
+    <t>庄艺娜</t>
+  </si>
+  <si>
+    <t>qzk03</t>
+  </si>
+  <si>
+    <t>谢龙辉</t>
+  </si>
+  <si>
+    <t>12t1001</t>
+  </si>
+  <si>
+    <t>12t004</t>
+  </si>
+  <si>
+    <t>xiamen01</t>
+  </si>
+  <si>
+    <t>12t098</t>
+  </si>
+  <si>
+    <t>王达斌</t>
+  </si>
+  <si>
+    <t>12t003</t>
+  </si>
+  <si>
+    <t>苏巧萍</t>
+  </si>
+  <si>
+    <t>xmqudao003</t>
+  </si>
+  <si>
+    <t>12t070</t>
+  </si>
+  <si>
+    <t>12t1030</t>
+  </si>
+  <si>
     <t>茅巧丽</t>
   </si>
   <si>
-    <t>xmcustm01</t>
-  </si>
-  <si>
-    <t>搜索增值事业部</t>
-  </si>
-  <si>
-    <t>冯乔芳</t>
-  </si>
-  <si>
-    <t>12t033</t>
-  </si>
-  <si>
-    <t>建站十分</t>
-  </si>
-  <si>
-    <t>XM005</t>
-  </si>
-  <si>
-    <t>叶惠</t>
-  </si>
-  <si>
-    <t>12t052</t>
-  </si>
-  <si>
-    <t>蓝淑敏</t>
-  </si>
-  <si>
-    <t>12t092</t>
-  </si>
-  <si>
-    <t>张唯唯</t>
-  </si>
-  <si>
-    <t>12t024</t>
-  </si>
-  <si>
-    <t>郑秀东</t>
-  </si>
-  <si>
-    <t>xm020</t>
-  </si>
-  <si>
-    <t>叶晓欢</t>
-  </si>
-  <si>
-    <t>12t087</t>
-  </si>
-  <si>
-    <t>林华卿</t>
-  </si>
-  <si>
-    <t>12t043</t>
-  </si>
-  <si>
-    <t>程秋平</t>
-  </si>
-  <si>
-    <t>12t016</t>
-  </si>
-  <si>
-    <t>新开三部</t>
-  </si>
-  <si>
-    <t>刘珏</t>
-  </si>
-  <si>
-    <t>离职</t>
-  </si>
-  <si>
-    <t>12t005</t>
-  </si>
-  <si>
-    <t>林霖</t>
-  </si>
-  <si>
-    <t>12t032</t>
-  </si>
-  <si>
-    <t>童莺莺</t>
-  </si>
-  <si>
-    <t>12t050</t>
-  </si>
-  <si>
-    <t>徐林萍</t>
-  </si>
-  <si>
-    <t>12t082</t>
-  </si>
-  <si>
-    <t>林裕芳</t>
-  </si>
-  <si>
-    <t>12t090</t>
-  </si>
-  <si>
-    <t>张静</t>
-  </si>
-  <si>
-    <t>12t1002</t>
-  </si>
-  <si>
-    <t>廖淑云</t>
-  </si>
-  <si>
-    <t>12t089</t>
-  </si>
-  <si>
-    <t>黄迷</t>
-  </si>
-  <si>
-    <t>12t014</t>
-  </si>
-  <si>
-    <t>黄明华</t>
-  </si>
-  <si>
-    <t>12t1008</t>
-  </si>
-  <si>
-    <t>郑文星</t>
-  </si>
-  <si>
-    <t>12t1009</t>
-  </si>
-  <si>
-    <t>郑淑敏</t>
-  </si>
-  <si>
-    <t>12t091</t>
-  </si>
-  <si>
-    <t>12t066</t>
-  </si>
-  <si>
-    <t>陈碧云</t>
-  </si>
-  <si>
-    <t>12t047</t>
-  </si>
-  <si>
-    <t>赖春连</t>
-  </si>
-  <si>
-    <t>12t069</t>
-  </si>
-  <si>
-    <t>陈巧云</t>
-  </si>
-  <si>
-    <t>蒋丽娟</t>
-  </si>
-  <si>
-    <t>12t029</t>
-  </si>
-  <si>
-    <t>江媚</t>
-  </si>
-  <si>
-    <t>12t030</t>
-  </si>
-  <si>
-    <t>陈丽环</t>
-  </si>
-  <si>
-    <t>12t1015</t>
-  </si>
-  <si>
-    <t>李远红</t>
-  </si>
-  <si>
-    <t>12t1010</t>
-  </si>
-  <si>
-    <t>池紫婷</t>
-  </si>
-  <si>
-    <t>12t1012</t>
-  </si>
-  <si>
-    <t>12t1028</t>
-  </si>
-  <si>
-    <t>行业一部</t>
-  </si>
-  <si>
-    <t>xmk01</t>
-  </si>
-  <si>
-    <t>厦门KOL</t>
-  </si>
-  <si>
-    <t>林佳惠</t>
-  </si>
-  <si>
-    <t>xmk03</t>
-  </si>
-  <si>
-    <t>邓玲玲</t>
-  </si>
-  <si>
-    <t>12t095</t>
-  </si>
-  <si>
-    <t>失效挽救部</t>
-  </si>
-  <si>
-    <t>失效挽救</t>
-  </si>
-  <si>
-    <t>纪荣裕</t>
-  </si>
-  <si>
-    <t>12t039</t>
-  </si>
-  <si>
-    <t>医疗事业部</t>
-  </si>
-  <si>
-    <t>吴晓燕</t>
-  </si>
-  <si>
-    <t>12t036</t>
-  </si>
-  <si>
-    <t>叶姗姗</t>
-  </si>
-  <si>
-    <t>12t012</t>
-  </si>
-  <si>
-    <t>陈玉云</t>
-  </si>
-  <si>
-    <t>12t1029</t>
-  </si>
-  <si>
-    <t>方秋燕</t>
-  </si>
-  <si>
-    <t>12t018</t>
-  </si>
-  <si>
-    <t>泉州医疗</t>
-  </si>
-  <si>
-    <t>张秀梅</t>
-  </si>
-  <si>
-    <t>12t1034</t>
-  </si>
-  <si>
-    <t>陈鹭霞</t>
-  </si>
-  <si>
-    <t>12t1027</t>
-  </si>
-  <si>
-    <t>汤斐莉</t>
-  </si>
-  <si>
-    <t>12t015</t>
-  </si>
-  <si>
-    <t>林桂英</t>
-  </si>
-  <si>
-    <t>12t063</t>
-  </si>
-  <si>
-    <t>王智勇</t>
-  </si>
-  <si>
-    <t>12t096</t>
-  </si>
-  <si>
-    <t>梁烨</t>
-  </si>
-  <si>
-    <t>12t094</t>
-  </si>
-  <si>
-    <t>林志龙</t>
-  </si>
-  <si>
-    <t>12t1023</t>
-  </si>
-  <si>
-    <t>苏晨</t>
-  </si>
-  <si>
-    <t>12t002</t>
-  </si>
-  <si>
-    <t>12t053</t>
-  </si>
-  <si>
-    <t>xmcustm11</t>
-  </si>
-  <si>
-    <t>泉州增值运营部</t>
-  </si>
-  <si>
-    <t>叶彩华</t>
-  </si>
-  <si>
-    <t>xmcustm08</t>
-  </si>
-  <si>
-    <t>泉州KOL</t>
-  </si>
-  <si>
-    <t>李华</t>
-  </si>
-  <si>
-    <t>xm009</t>
-  </si>
-  <si>
-    <t>王丽真</t>
-  </si>
-  <si>
-    <t>陈健</t>
-  </si>
-  <si>
-    <t>12t1031</t>
-  </si>
-  <si>
-    <t>许少鸣</t>
-  </si>
-  <si>
-    <t>12t022</t>
-  </si>
-  <si>
-    <t>王真珍</t>
-  </si>
-  <si>
-    <t>12t097</t>
-  </si>
-  <si>
-    <t>徐灵钰</t>
-  </si>
-  <si>
-    <t>12t099</t>
-  </si>
-  <si>
-    <t>游瑞凤</t>
-  </si>
-  <si>
-    <t>12t059</t>
-  </si>
-  <si>
-    <t>李丽红</t>
-  </si>
-  <si>
-    <t>12t061</t>
-  </si>
-  <si>
-    <t>胡艺红</t>
-  </si>
-  <si>
-    <t>xm022</t>
-  </si>
-  <si>
-    <t>泉州维护二部</t>
-  </si>
-  <si>
-    <t>曾达威</t>
-  </si>
-  <si>
-    <t>12t031</t>
-  </si>
-  <si>
-    <t>12t076</t>
-  </si>
-  <si>
-    <t>12t077</t>
-  </si>
-  <si>
-    <t>林小凤</t>
-  </si>
-  <si>
-    <t>12t026</t>
-  </si>
-  <si>
-    <t>曾雅芳</t>
-  </si>
-  <si>
-    <t>12t1017</t>
-  </si>
-  <si>
-    <t>林秋琼</t>
-  </si>
-  <si>
-    <t>12t060</t>
-  </si>
-  <si>
-    <t>黄锴</t>
-  </si>
-  <si>
-    <t>12t006</t>
-  </si>
-  <si>
-    <t>张婷婷</t>
-  </si>
-  <si>
-    <t>12t1020</t>
-  </si>
-  <si>
-    <t>黄凤苗</t>
-  </si>
-  <si>
-    <t>xm019</t>
-  </si>
-  <si>
-    <t>吴燕红</t>
-  </si>
-  <si>
-    <t>12t013</t>
-  </si>
-  <si>
-    <t>王凤钦</t>
-  </si>
-  <si>
-    <t>12t085</t>
-  </si>
-  <si>
-    <t>傅佳玲</t>
-  </si>
-  <si>
-    <t>王艳冰</t>
-  </si>
-  <si>
-    <t>12t079</t>
-  </si>
-  <si>
-    <t>吴敏凤</t>
-  </si>
-  <si>
-    <t>12t080</t>
-  </si>
-  <si>
-    <t>张滟莲</t>
-  </si>
-  <si>
-    <t>王小婷</t>
-  </si>
-  <si>
-    <t>12t041</t>
-  </si>
-  <si>
-    <t>邱彬彬</t>
-  </si>
-  <si>
-    <t>KOLQZ01</t>
-  </si>
-  <si>
-    <t>陈浩</t>
-  </si>
-  <si>
-    <t>qzko1</t>
-  </si>
-  <si>
-    <t>施桂兰</t>
-  </si>
-  <si>
-    <t>12t1014</t>
-  </si>
-  <si>
-    <t>陈燕秀</t>
-  </si>
-  <si>
-    <t>xm021</t>
-  </si>
-  <si>
-    <t>吴清玉</t>
-  </si>
-  <si>
-    <t>12t020</t>
-  </si>
-  <si>
-    <t>游惠卿</t>
-  </si>
-  <si>
-    <t>12t083</t>
-  </si>
-  <si>
-    <t>林聪义</t>
-  </si>
-  <si>
-    <t>12t038</t>
-  </si>
-  <si>
-    <t>黄淑玲</t>
-  </si>
-  <si>
-    <t>12t1016</t>
-  </si>
-  <si>
-    <t>连海珠</t>
-  </si>
-  <si>
-    <t>12t081</t>
-  </si>
-  <si>
-    <t>洪宏</t>
-  </si>
-  <si>
-    <t>12t1019</t>
-  </si>
-  <si>
-    <t>陈秋菊</t>
-  </si>
-  <si>
-    <t>zlfeed01</t>
-  </si>
-  <si>
-    <t>运营策略中心</t>
-  </si>
-  <si>
-    <t>漳州培训</t>
-  </si>
-  <si>
-    <t>林惠兰</t>
-  </si>
-  <si>
-    <t>12t1013</t>
-  </si>
-  <si>
-    <t>丁洁</t>
-  </si>
-  <si>
-    <t>12t1035</t>
-  </si>
-  <si>
-    <t>夏皖鹭</t>
-  </si>
-  <si>
-    <t>xiamenzongdai，xmzhuce01</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>12t068</t>
-  </si>
-  <si>
-    <t>行发基木鱼</t>
-  </si>
-  <si>
-    <t>12t086</t>
-  </si>
-  <si>
-    <t>朱书兰</t>
-  </si>
-  <si>
-    <t>xm026</t>
-  </si>
-  <si>
-    <t>信息流VIP</t>
-  </si>
-  <si>
-    <t>萧月梅</t>
-  </si>
-  <si>
-    <t>12t71</t>
-  </si>
-  <si>
-    <t>胡晓惠</t>
-  </si>
-  <si>
-    <t>12t74</t>
-  </si>
-  <si>
-    <t>林丹丹</t>
-  </si>
-  <si>
-    <t>12t034</t>
-  </si>
-  <si>
-    <t>姚美玲</t>
-  </si>
-  <si>
-    <t>12t011</t>
-  </si>
-  <si>
-    <t>陈雪梅</t>
-  </si>
-  <si>
-    <t>12t051</t>
-  </si>
-  <si>
-    <t>詹大钧</t>
-  </si>
-  <si>
-    <t>12t028</t>
-  </si>
-  <si>
-    <t>郑博萱</t>
-  </si>
-  <si>
-    <t>12t1022</t>
-  </si>
-  <si>
-    <t>朱丽珊</t>
-  </si>
-  <si>
-    <t>12t042</t>
-  </si>
-  <si>
-    <t>葛晓丹</t>
-  </si>
-  <si>
-    <t>12t093</t>
-  </si>
-  <si>
-    <t>李丹凤</t>
-  </si>
-  <si>
-    <t>12t017</t>
-  </si>
-  <si>
-    <t>郭琳娟</t>
-  </si>
-  <si>
-    <t>12t064</t>
-  </si>
-  <si>
-    <t>12t72</t>
-  </si>
-  <si>
-    <t>杨晶晶</t>
-  </si>
-  <si>
-    <t>12t037</t>
-  </si>
-  <si>
-    <t>KOLXM02</t>
-  </si>
-  <si>
-    <t>大客KOL销售</t>
-  </si>
-  <si>
-    <t>林洁</t>
-  </si>
-  <si>
-    <t>xmk04</t>
-  </si>
-  <si>
-    <t>郑燕森</t>
-  </si>
-  <si>
-    <t>qzk02</t>
-  </si>
-  <si>
-    <t>泉州KOL客服</t>
-  </si>
-  <si>
-    <t>许珊珊</t>
-  </si>
-  <si>
-    <t>xmkuang03</t>
-  </si>
-  <si>
-    <t>xmfq01</t>
-  </si>
-  <si>
-    <t>kuangjiaxm02，xmkuang01</t>
-  </si>
-  <si>
-    <t>xmkuang28</t>
-  </si>
-  <si>
-    <t>12t048</t>
-  </si>
-  <si>
-    <t>大客医疗</t>
-  </si>
-  <si>
-    <t>庄艺娜</t>
-  </si>
-  <si>
-    <t>qzk03</t>
-  </si>
-  <si>
-    <t>谢龙辉</t>
-  </si>
-  <si>
-    <t>12t1001</t>
-  </si>
-  <si>
-    <t>12t004</t>
-  </si>
-  <si>
-    <t>xiamen01</t>
-  </si>
-  <si>
-    <t>12t098</t>
-  </si>
-  <si>
-    <t>王达斌</t>
-  </si>
-  <si>
-    <t>12t003</t>
-  </si>
-  <si>
-    <t>苏巧萍</t>
-  </si>
-  <si>
-    <t>xmqudao003</t>
-  </si>
-  <si>
-    <t>12t070</t>
-  </si>
-  <si>
-    <t>12t1030</t>
-  </si>
-  <si>
     <t>12t1006</t>
   </si>
   <si>
@@ -1288,13 +1270,13 @@
     <t>xmk02</t>
   </si>
   <si>
+    <t>何清霞</t>
+  </si>
+  <si>
     <t>尹林平</t>
   </si>
   <si>
     <t>kolxm01</t>
-  </si>
-  <si>
-    <t>蒋铃溪</t>
   </si>
   <si>
     <t>12tsales</t>
@@ -1371,8 +1353,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -1419,23 +1401,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1457,6 +1440,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -1464,8 +1471,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1479,35 +1494,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1519,24 +1509,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1557,6 +1539,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1569,25 +1641,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1599,121 +1701,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1725,13 +1713,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1742,54 +1724,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1812,7 +1746,37 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1842,16 +1806,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1863,7 +1845,7 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1872,121 +1854,121 @@
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2412,6 +2394,7 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" s="2"/>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G33" si="0">D2</f>
         <v>注册</v>
@@ -2446,6 +2429,7 @@
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E3" s="2"/>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>陈沅</v>
@@ -2480,6 +2464,7 @@
       <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="E4" s="2"/>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
         <v>俞培培</v>
@@ -2514,6 +2499,7 @@
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="E5" s="2"/>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>陈金锐</v>
@@ -2548,6 +2534,7 @@
       <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="E6" s="2"/>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>杨丹凤</v>
@@ -2582,6 +2569,7 @@
       <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="E7" s="2"/>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>许曾美</v>
@@ -2616,6 +2604,7 @@
       <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="E8" s="2"/>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>信息流</v>
@@ -2650,6 +2639,7 @@
       <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
+      <c r="E9" s="2"/>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>信息流</v>
@@ -2684,6 +2674,7 @@
       <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="E10" s="2"/>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>沈晓芬</v>
@@ -2718,6 +2709,7 @@
       <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
+      <c r="E11" s="2"/>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>厦门总代理</v>
@@ -2752,6 +2744,7 @@
       <c r="D12" s="2" t="s">
         <v>40</v>
       </c>
+      <c r="E12" s="2"/>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>泉州失效库</v>
@@ -2786,6 +2779,7 @@
       <c r="D13" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="E13" s="2"/>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>泉州建站</v>
@@ -2820,6 +2814,7 @@
       <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="E14" s="2"/>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>丘连珍</v>
@@ -2854,6 +2849,7 @@
       <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E15" s="2"/>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架代理</v>
@@ -2888,6 +2884,7 @@
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E16" s="2"/>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2922,6 +2919,7 @@
       <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E17" s="2"/>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2956,6 +2954,7 @@
       <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E18" s="2"/>
       <c r="G18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2990,6 +2989,7 @@
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E19" s="2"/>
       <c r="G19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3024,6 +3024,7 @@
       <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E20" s="2"/>
       <c r="G20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3058,6 +3059,7 @@
       <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E21" s="2"/>
       <c r="G21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3092,6 +3094,7 @@
       <c r="D22" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E22" s="2"/>
       <c r="G22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3126,6 +3129,7 @@
       <c r="D23" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E23" s="2"/>
       <c r="G23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3160,6 +3164,7 @@
       <c r="D24" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E24" s="2"/>
       <c r="G24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3194,6 +3199,7 @@
       <c r="D25" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E25" s="2"/>
       <c r="G25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3228,6 +3234,7 @@
       <c r="D26" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E26" s="2"/>
       <c r="G26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3262,6 +3269,7 @@
       <c r="D27" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E27" s="2"/>
       <c r="G27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3296,6 +3304,7 @@
       <c r="D28" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E28" s="2"/>
       <c r="G28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3330,6 +3339,7 @@
       <c r="D29" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E29" s="2"/>
       <c r="G29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3364,6 +3374,7 @@
       <c r="D30" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E30" s="2"/>
       <c r="G30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3398,6 +3409,7 @@
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E31" s="2"/>
       <c r="G31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3432,6 +3444,7 @@
       <c r="D32" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E32" s="2"/>
       <c r="G32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3466,6 +3479,7 @@
       <c r="D33" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E33" s="2"/>
       <c r="G33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3500,6 +3514,7 @@
       <c r="D34" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E34" s="2"/>
       <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G66" si="2">D34</f>
         <v>框架</v>
@@ -3534,6 +3549,7 @@
       <c r="D35" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E35" s="2"/>
       <c r="G35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3568,6 +3584,7 @@
       <c r="D36" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E36" s="2"/>
       <c r="G36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3602,6 +3619,7 @@
       <c r="D37" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E37" s="2"/>
       <c r="G37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3636,6 +3654,7 @@
       <c r="D38" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E38" s="2"/>
       <c r="G38" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3670,6 +3689,7 @@
       <c r="D39" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E39" s="2"/>
       <c r="G39" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3704,6 +3724,7 @@
       <c r="D40" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E40" s="2"/>
       <c r="G40" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3738,6 +3759,7 @@
       <c r="D41" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E41" s="2"/>
       <c r="G41" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3772,6 +3794,7 @@
       <c r="D42" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E42" s="2"/>
       <c r="G42" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3806,6 +3829,7 @@
       <c r="D43" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E43" s="2"/>
       <c r="G43" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3840,6 +3864,7 @@
       <c r="D44" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E44" s="2"/>
       <c r="G44" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3874,6 +3899,7 @@
       <c r="D45" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E45" s="2"/>
       <c r="G45" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3908,6 +3934,7 @@
       <c r="D46" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E46" s="2"/>
       <c r="G46" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3942,6 +3969,7 @@
       <c r="D47" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E47" s="2"/>
       <c r="G47" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3976,6 +4004,7 @@
       <c r="D48" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E48" s="2"/>
       <c r="G48" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4010,6 +4039,7 @@
       <c r="D49" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E49" s="2"/>
       <c r="G49" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4044,6 +4074,7 @@
       <c r="D50" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E50" s="2"/>
       <c r="G50" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4078,6 +4109,7 @@
       <c r="D51" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E51" s="2"/>
       <c r="G51" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4112,6 +4144,7 @@
       <c r="D52" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E52" s="2"/>
       <c r="G52" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4146,6 +4179,7 @@
       <c r="D53" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E53" s="2"/>
       <c r="G53" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4180,6 +4214,7 @@
       <c r="D54" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E54" s="2"/>
       <c r="G54" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4214,6 +4249,7 @@
       <c r="D55" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E55" s="2"/>
       <c r="G55" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4248,6 +4284,7 @@
       <c r="D56" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E56" s="2"/>
       <c r="G56" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4282,6 +4319,7 @@
       <c r="D57" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="E57" s="2"/>
       <c r="G57" s="2" t="str">
         <f t="shared" si="2"/>
         <v>漆丽华</v>
@@ -4316,6 +4354,7 @@
       <c r="D58" s="2" t="s">
         <v>94</v>
       </c>
+      <c r="E58" s="2"/>
       <c r="G58" s="2" t="str">
         <f t="shared" si="2"/>
         <v>林雅清</v>
@@ -4350,6 +4389,7 @@
       <c r="D59" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="E59" s="2"/>
       <c r="G59" s="2" t="str">
         <f t="shared" si="2"/>
         <v>卢德华</v>
@@ -4384,6 +4424,7 @@
       <c r="D60" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="E60" s="2"/>
       <c r="G60" s="2" t="str">
         <f t="shared" si="2"/>
         <v>胡丽萍</v>
@@ -4418,6 +4459,7 @@
       <c r="D61" s="2" t="s">
         <v>102</v>
       </c>
+      <c r="E61" s="2"/>
       <c r="G61" s="2" t="str">
         <f t="shared" si="2"/>
         <v>吴苏晗笑</v>
@@ -4452,6 +4494,7 @@
       <c r="D62" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="E62" s="2"/>
       <c r="G62" s="2" t="str">
         <f t="shared" si="2"/>
         <v>李任飘</v>
@@ -4486,6 +4529,7 @@
       <c r="D63" s="2" t="s">
         <v>108</v>
       </c>
+      <c r="E63" s="2"/>
       <c r="G63" s="2" t="str">
         <f t="shared" si="2"/>
         <v>林菁菁</v>
@@ -4520,6 +4564,7 @@
       <c r="D64" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="E64" s="2"/>
       <c r="G64" s="2" t="str">
         <f t="shared" si="2"/>
         <v>黄春荣</v>
@@ -4554,6 +4599,7 @@
       <c r="D65" s="2" t="s">
         <v>113</v>
       </c>
+      <c r="E65" s="2"/>
       <c r="G65" s="2" t="str">
         <f t="shared" si="2"/>
         <v>谭丽</v>
@@ -4588,6 +4634,7 @@
       <c r="D66" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="E66" s="2"/>
       <c r="G66" s="2" t="str">
         <f t="shared" si="2"/>
         <v>胡光柱</v>
@@ -4622,6 +4669,7 @@
       <c r="D67" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="E67" s="2"/>
       <c r="G67" s="2" t="str">
         <f t="shared" ref="G67:G130" si="3">D67</f>
         <v>洪荣堃</v>
@@ -4656,6 +4704,7 @@
       <c r="D68" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="E68" s="2"/>
       <c r="G68" s="2" t="str">
         <f t="shared" si="3"/>
         <v>洪荣堃</v>
@@ -4690,6 +4739,7 @@
       <c r="D69" s="2" t="s">
         <v>118</v>
       </c>
+      <c r="E69" s="2"/>
       <c r="G69" s="2" t="str">
         <f t="shared" si="3"/>
         <v>洪荣堃</v>
@@ -4724,6 +4774,7 @@
       <c r="D70" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="E70" s="2"/>
       <c r="G70" s="2" t="str">
         <f t="shared" si="3"/>
         <v>傅素玲</v>
@@ -4758,6 +4809,7 @@
       <c r="D71" s="2" t="s">
         <v>126</v>
       </c>
+      <c r="E71" s="2"/>
       <c r="G71" s="2" t="str">
         <f t="shared" si="3"/>
         <v>方丽容</v>
@@ -4792,6 +4844,7 @@
       <c r="D72" s="2" t="s">
         <v>128</v>
       </c>
+      <c r="E72" s="2"/>
       <c r="G72" s="2" t="str">
         <f t="shared" si="3"/>
         <v>董宝阳</v>
@@ -4826,6 +4879,7 @@
       <c r="D73" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="E73" s="2"/>
       <c r="G73" s="2" t="str">
         <f t="shared" si="3"/>
         <v>代玉</v>
@@ -4860,6 +4914,7 @@
       <c r="D74" s="2" t="s">
         <v>132</v>
       </c>
+      <c r="E74" s="2"/>
       <c r="G74" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈婷</v>
@@ -4894,6 +4949,7 @@
       <c r="D75" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="E75" s="2"/>
       <c r="G75" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张慧敏</v>
@@ -4928,6 +4984,7 @@
       <c r="D76" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="E76" s="2"/>
       <c r="G76" s="2" t="str">
         <f t="shared" si="3"/>
         <v>曾清桦</v>
@@ -4946,22 +5003,23 @@
         <v>101</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:15">
       <c r="A77" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>140</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="G77" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈美媛</v>
@@ -4971,21 +5029,21 @@
         <v>品牌部</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="N77" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="O77" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:15">
       <c r="A78" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>31</v>
@@ -4994,8 +5052,9 @@
         <v>125</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>142</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="E78" s="2"/>
       <c r="G78" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈俊华</v>
@@ -5005,7 +5064,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>31</v>
@@ -5014,22 +5073,23 @@
         <v>125</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="1:15">
       <c r="A79" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="E79" s="2"/>
       <c r="G79" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶玲</v>
@@ -5039,31 +5099,32 @@
         <v>维护部门</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O79" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="1:15">
       <c r="A80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>148</v>
-      </c>
+      <c r="E80" s="2"/>
       <c r="G80" s="2" t="str">
         <f t="shared" si="3"/>
         <v>宋宇红</v>
@@ -5073,31 +5134,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M80" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="M80" s="2" t="s">
+      <c r="N80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O80" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="1:15">
       <c r="A81" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="G81" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林旭芬</v>
@@ -5107,31 +5169,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L81" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O81" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N81" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O81" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="1:15">
       <c r="A82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>152</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="G82" s="2" t="str">
         <f t="shared" si="3"/>
         <v>王志凤</v>
@@ -5141,31 +5204,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O82" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="1:15">
       <c r="A83" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>154</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="G83" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张致远</v>
@@ -5175,31 +5239,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L83" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O83" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N83" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="1:15">
       <c r="A84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="G84" s="2" t="str">
         <f t="shared" si="3"/>
         <v>吴启建</v>
@@ -5209,31 +5274,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O84" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="1:15">
       <c r="A85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="G85" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑晓蓉</v>
@@ -5243,31 +5309,32 @@
         <v>渠道增值部</v>
       </c>
       <c r="L85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="O85" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:15">
       <c r="A86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="E86" s="2"/>
       <c r="G86" s="2" t="str">
         <f t="shared" si="3"/>
         <v>胡茜</v>
@@ -5277,21 +5344,21 @@
         <v>行发事业部</v>
       </c>
       <c r="L86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M86" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M86" s="2" t="s">
+      <c r="N86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="O86" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="N86" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="O86" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="1:15">
       <c r="A87" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>14</v>
@@ -5300,8 +5367,9 @@
         <v>15</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>163</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="E87" s="2"/>
       <c r="G87" s="2" t="str">
         <f t="shared" si="3"/>
         <v>杜鑫鑫</v>
@@ -5311,7 +5379,7 @@
         <v>维护部门</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>14</v>
@@ -5320,12 +5388,12 @@
         <v>15</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="1:15">
       <c r="A88" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>45</v>
@@ -5334,8 +5402,9 @@
         <v>98</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>165</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="E88" s="2"/>
       <c r="G88" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑色艳</v>
@@ -5345,7 +5414,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>45</v>
@@ -5354,12 +5423,12 @@
         <v>98</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="1:15">
       <c r="A89" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>45</v>
@@ -5368,8 +5437,9 @@
         <v>98</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>167</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="E89" s="2"/>
       <c r="G89" s="2" t="str">
         <f t="shared" si="3"/>
         <v>李珍珍</v>
@@ -5379,7 +5449,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M89" s="2" t="s">
         <v>45</v>
@@ -5388,22 +5458,23 @@
         <v>98</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="1:15">
       <c r="A90" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>134</v>
       </c>
+      <c r="E90" s="2"/>
       <c r="G90" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张慧敏</v>
@@ -5413,31 +5484,32 @@
         <v>行发维护大区</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="1:15">
       <c r="A91" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>173</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="G91" s="2" t="str">
         <f t="shared" si="3"/>
         <v>冯乔芳</v>
@@ -5447,21 +5519,21 @@
         <v>搜索增值事业部</v>
       </c>
       <c r="L91" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="M91" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="N91" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="92" customHeight="1" spans="1:15">
       <c r="A92" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>6</v>
@@ -5470,8 +5542,9 @@
         <v>6</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="E92" s="2"/>
       <c r="G92" s="2" t="str">
         <f t="shared" si="3"/>
         <v>建站十分</v>
@@ -5481,7 +5554,7 @@
         <v>新开部门</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>6</v>
@@ -5490,12 +5563,12 @@
         <v>6</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" customHeight="1" spans="1:15">
       <c r="A93" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>6</v>
@@ -5504,8 +5577,9 @@
         <v>7</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>177</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="E93" s="2"/>
       <c r="G93" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶惠</v>
@@ -5515,7 +5589,7 @@
         <v>新开部门</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>6</v>
@@ -5524,12 +5598,12 @@
         <v>7</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="1:15">
       <c r="A94" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>6</v>
@@ -5538,8 +5612,9 @@
         <v>7</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>179</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E94" s="2"/>
       <c r="G94" s="2" t="str">
         <f t="shared" si="3"/>
         <v>蓝淑敏</v>
@@ -5549,7 +5624,7 @@
         <v>新开部门</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>6</v>
@@ -5558,12 +5633,12 @@
         <v>7</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="1:15">
       <c r="A95" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>6</v>
@@ -5572,8 +5647,9 @@
         <v>7</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="E95" s="2"/>
       <c r="G95" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张唯唯</v>
@@ -5583,7 +5659,7 @@
         <v>新开部门</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>6</v>
@@ -5592,12 +5668,12 @@
         <v>7</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="1:15">
       <c r="A96" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>6</v>
@@ -5606,8 +5682,9 @@
         <v>7</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>183</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="E96" s="2"/>
       <c r="G96" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑秀东</v>
@@ -5617,7 +5694,7 @@
         <v>新开部门</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>6</v>
@@ -5626,12 +5703,12 @@
         <v>7</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="1:15">
       <c r="A97" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>6</v>
@@ -5640,8 +5717,9 @@
         <v>112</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>185</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="E97" s="2"/>
       <c r="G97" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶晓欢</v>
@@ -5651,7 +5729,7 @@
         <v>新开部门</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>6</v>
@@ -5660,12 +5738,12 @@
         <v>112</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="1:15">
       <c r="A98" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>6</v>
@@ -5674,8 +5752,9 @@
         <v>112</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="E98" s="2"/>
       <c r="G98" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林华卿</v>
@@ -5685,7 +5764,7 @@
         <v>新开部门</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>6</v>
@@ -5694,12 +5773,12 @@
         <v>112</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="1:15">
       <c r="A99" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>6</v>
@@ -5708,8 +5787,9 @@
         <v>112</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="E99" s="2"/>
       <c r="G99" s="2" t="str">
         <f t="shared" si="3"/>
         <v>程秋平</v>
@@ -5719,7 +5799,7 @@
         <v>新开部门</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>6</v>
@@ -5728,25 +5808,23 @@
         <v>112</v>
       </c>
       <c r="O99" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="1:15">
       <c r="A100" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>193</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="E100" s="2"/>
       <c r="G100" s="2" t="str">
         <f t="shared" si="3"/>
         <v>刘珏</v>
@@ -5756,21 +5834,21 @@
         <v>新开部门</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M100" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="1:15">
       <c r="A101" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>6</v>
@@ -5779,8 +5857,9 @@
         <v>112</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="E101" s="2"/>
       <c r="G101" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林霖</v>
@@ -5790,7 +5869,7 @@
         <v>新开部门</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="M101" s="2" t="s">
         <v>6</v>
@@ -5799,12 +5878,12 @@
         <v>112</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="1:15">
       <c r="A102" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>6</v>
@@ -5813,8 +5892,9 @@
         <v>112</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>197</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="E102" s="2"/>
       <c r="G102" s="2" t="str">
         <f t="shared" si="3"/>
         <v>童莺莺</v>
@@ -5824,7 +5904,7 @@
         <v>新开部门</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M102" s="2" t="s">
         <v>6</v>
@@ -5833,22 +5913,23 @@
         <v>112</v>
       </c>
       <c r="O102" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="1:15">
       <c r="A103" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="E103" s="2"/>
       <c r="G103" s="2" t="str">
         <f t="shared" si="3"/>
         <v>徐林萍</v>
@@ -5858,21 +5939,21 @@
         <v>新开部门</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>6</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="1:15">
       <c r="A104" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>6</v>
@@ -5881,8 +5962,9 @@
         <v>7</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>201</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="E104" s="2"/>
       <c r="G104" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林裕芳</v>
@@ -5892,7 +5974,7 @@
         <v>新开部门</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M104" s="2" t="s">
         <v>6</v>
@@ -5901,12 +5983,12 @@
         <v>7</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="1:15">
       <c r="A105" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>38</v>
@@ -5915,8 +5997,9 @@
         <v>39</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="E105" s="2"/>
       <c r="G105" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张静</v>
@@ -5926,7 +6009,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>38</v>
@@ -5935,12 +6018,12 @@
         <v>39</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="1:15">
       <c r="A106" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>45</v>
@@ -5949,8 +6032,9 @@
         <v>101</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="E106" s="2"/>
       <c r="G106" s="2" t="str">
         <f t="shared" si="3"/>
         <v>廖淑云</v>
@@ -5960,7 +6044,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>45</v>
@@ -5969,12 +6053,12 @@
         <v>101</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="1:15">
       <c r="A107" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>14</v>
@@ -5983,8 +6067,9 @@
         <v>15</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>207</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="E107" s="2"/>
       <c r="G107" s="2" t="str">
         <f t="shared" si="3"/>
         <v>黄迷</v>
@@ -5994,7 +6079,7 @@
         <v>维护部门</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>14</v>
@@ -6003,12 +6088,12 @@
         <v>15</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="1:15">
       <c r="A108" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>14</v>
@@ -6017,8 +6102,9 @@
         <v>15</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>209</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="E108" s="2"/>
       <c r="G108" s="2" t="str">
         <f t="shared" si="3"/>
         <v>黄明华</v>
@@ -6028,7 +6114,7 @@
         <v>维护部门</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>14</v>
@@ -6037,12 +6123,12 @@
         <v>15</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="1:15">
       <c r="A109" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>14</v>
@@ -6051,8 +6137,9 @@
         <v>15</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>211</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E109" s="2"/>
       <c r="G109" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑文星</v>
@@ -6062,7 +6149,7 @@
         <v>维护部门</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M109" s="2" t="s">
         <v>14</v>
@@ -6071,12 +6158,12 @@
         <v>15</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="1:15">
       <c r="A110" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>14</v>
@@ -6085,8 +6172,9 @@
         <v>15</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>213</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="E110" s="2"/>
       <c r="G110" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑淑敏</v>
@@ -6096,7 +6184,7 @@
         <v>维护部门</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="M110" s="2" t="s">
         <v>14</v>
@@ -6105,12 +6193,12 @@
         <v>15</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="1:15">
       <c r="A111" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>10</v>
@@ -6121,6 +6209,7 @@
       <c r="D111" s="2" t="s">
         <v>136</v>
       </c>
+      <c r="E111" s="2"/>
       <c r="G111" s="2" t="str">
         <f t="shared" si="3"/>
         <v>曾清桦</v>
@@ -6130,7 +6219,7 @@
         <v>大客部门</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M111" s="2" t="s">
         <v>10</v>
@@ -6144,7 +6233,7 @@
     </row>
     <row r="112" customHeight="1" spans="1:15">
       <c r="A112" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>14</v>
@@ -6153,8 +6242,9 @@
         <v>15</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>216</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="E112" s="2"/>
       <c r="G112" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈碧云</v>
@@ -6164,7 +6254,7 @@
         <v>维护部门</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M112" s="2" t="s">
         <v>14</v>
@@ -6173,22 +6263,23 @@
         <v>15</v>
       </c>
       <c r="O112" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:15">
       <c r="A113" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>218</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="E113" s="2"/>
       <c r="G113" s="2" t="str">
         <f t="shared" si="3"/>
         <v>赖春连</v>
@@ -6198,31 +6289,32 @@
         <v>维护部门</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O113" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="1:15">
       <c r="A114" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>220</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="E114" s="2"/>
       <c r="G114" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈巧云</v>
@@ -6232,21 +6324,21 @@
         <v>维护部门</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="1:15">
       <c r="A115" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>14</v>
@@ -6255,8 +6347,9 @@
         <v>101</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>223</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="E115" s="2"/>
       <c r="G115" s="2" t="str">
         <f t="shared" si="3"/>
         <v>江媚</v>
@@ -6266,7 +6359,7 @@
         <v>维护部门</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>14</v>
@@ -6275,12 +6368,12 @@
         <v>101</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:15">
       <c r="A116" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>14</v>
@@ -6289,8 +6382,9 @@
         <v>101</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>225</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="E116" s="2"/>
       <c r="G116" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈丽环</v>
@@ -6300,7 +6394,7 @@
         <v>维护部门</v>
       </c>
       <c r="L116" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M116" s="2" t="s">
         <v>14</v>
@@ -6309,12 +6403,12 @@
         <v>101</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:15">
       <c r="A117" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>14</v>
@@ -6323,8 +6417,9 @@
         <v>101</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>227</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="E117" s="2"/>
       <c r="G117" s="2" t="str">
         <f t="shared" si="3"/>
         <v>李远红</v>
@@ -6334,7 +6429,7 @@
         <v>维护部门</v>
       </c>
       <c r="L117" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>14</v>
@@ -6343,12 +6438,12 @@
         <v>101</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:15">
       <c r="A118" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>14</v>
@@ -6357,8 +6452,9 @@
         <v>101</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>229</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="E118" s="2"/>
       <c r="G118" s="2" t="str">
         <f t="shared" si="3"/>
         <v>池紫婷</v>
@@ -6368,7 +6464,7 @@
         <v>维护部门</v>
       </c>
       <c r="L118" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M118" s="2" t="s">
         <v>14</v>
@@ -6377,12 +6473,12 @@
         <v>101</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:15">
       <c r="A119" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>45</v>
@@ -6391,8 +6487,9 @@
         <v>98</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>205</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="E119" s="2"/>
       <c r="G119" s="2" t="str">
         <f t="shared" si="3"/>
         <v>廖淑云</v>
@@ -6402,7 +6499,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>45</v>
@@ -6411,22 +6508,23 @@
         <v>98</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:15">
       <c r="A120" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>183</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="E120" s="2"/>
       <c r="G120" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑秀东</v>
@@ -6436,31 +6534,32 @@
         <v>大客部门</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M120" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O120" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:15">
       <c r="A121" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>235</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="E121" s="2"/>
       <c r="G121" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林佳惠</v>
@@ -6470,31 +6569,32 @@
         <v>大客部门</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O121" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:15">
       <c r="A122" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>237</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="E122" s="2"/>
       <c r="G122" s="2" t="str">
         <f t="shared" si="3"/>
         <v>邓玲玲</v>
@@ -6504,31 +6604,32 @@
         <v>大客部门</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="M122" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:15">
       <c r="A123" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="E123" s="2"/>
       <c r="G123" s="2" t="str">
         <f t="shared" si="3"/>
         <v>纪荣裕</v>
@@ -6538,31 +6639,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:15">
       <c r="A124" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>244</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="E124" s="2"/>
       <c r="G124" s="2" t="str">
         <f t="shared" si="3"/>
         <v>吴晓燕</v>
@@ -6572,31 +6674,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:15">
       <c r="A125" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="E125" s="2"/>
       <c r="G125" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶姗姗</v>
@@ -6606,31 +6709,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O125" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:15">
       <c r="A126" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>248</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="E126" s="2"/>
       <c r="G126" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈玉云</v>
@@ -6640,31 +6744,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:15">
       <c r="A127" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>250</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="E127" s="2"/>
       <c r="G127" s="2" t="str">
         <f t="shared" si="3"/>
         <v>方秋燕</v>
@@ -6674,31 +6779,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:15">
       <c r="A128" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>253</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="E128" s="2"/>
       <c r="G128" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张秀梅</v>
@@ -6708,31 +6814,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L128" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="M128" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O128" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="1:15">
       <c r="A129" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>255</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="E129" s="2"/>
       <c r="G129" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈鹭霞</v>
@@ -6742,31 +6849,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="M129" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O129" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="130" customHeight="1" spans="1:15">
       <c r="A130" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>257</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="E130" s="2"/>
       <c r="G130" s="2" t="str">
         <f t="shared" si="3"/>
         <v>汤斐莉</v>
@@ -6776,31 +6884,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" customHeight="1" spans="1:15">
       <c r="A131" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>259</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="E131" s="2"/>
       <c r="G131" s="2" t="str">
         <f t="shared" ref="G131:G194" si="5">D131</f>
         <v>林桂英</v>
@@ -6810,31 +6919,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="1:15">
       <c r="A132" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>261</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="E132" s="2"/>
       <c r="G132" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王智勇</v>
@@ -6844,21 +6954,21 @@
         <v>医疗事业部</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" customHeight="1" spans="1:15">
       <c r="A133" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>6</v>
@@ -6867,8 +6977,9 @@
         <v>112</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>263</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="E133" s="2"/>
       <c r="G133" s="2" t="str">
         <f t="shared" si="5"/>
         <v>梁烨</v>
@@ -6878,7 +6989,7 @@
         <v>新开部门</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="M133" s="2" t="s">
         <v>6</v>
@@ -6887,22 +6998,23 @@
         <v>112</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="134" customHeight="1" spans="1:15">
       <c r="A134" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>265</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="E134" s="2"/>
       <c r="G134" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林志龙</v>
@@ -6912,31 +7024,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" customHeight="1" spans="1:15">
       <c r="A135" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>267</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="E135" s="2"/>
       <c r="G135" s="2" t="str">
         <f t="shared" si="5"/>
         <v>苏晨</v>
@@ -6946,31 +7059,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="1:15">
       <c r="A136" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>265</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="E136" s="2"/>
       <c r="G136" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林志龙</v>
@@ -6980,31 +7094,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="1:15">
       <c r="A137" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="E137" s="2"/>
       <c r="G137" s="2" t="str">
         <f t="shared" si="5"/>
         <v>纪荣裕</v>
@@ -7014,31 +7129,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="1:15">
       <c r="A138" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>272</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="E138" s="2"/>
       <c r="G138" s="2" t="str">
         <f t="shared" si="5"/>
         <v>叶彩华</v>
@@ -7048,31 +7164,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="M138" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O138" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="1:15">
       <c r="A139" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>275</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="E139" s="2"/>
       <c r="G139" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李华</v>
@@ -7082,21 +7199,21 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M139" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="1:15">
       <c r="A140" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>38</v>
@@ -7105,8 +7222,9 @@
         <v>39</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>277</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="E140" s="2"/>
       <c r="G140" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王丽真</v>
@@ -7116,7 +7234,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="M140" s="2" t="s">
         <v>38</v>
@@ -7125,12 +7243,12 @@
         <v>39</v>
       </c>
       <c r="O140" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="1:15">
       <c r="A141" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>38</v>
@@ -7139,8 +7257,9 @@
         <v>39</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>280</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="E141" s="2"/>
       <c r="G141" s="2" t="str">
         <f t="shared" si="5"/>
         <v>许少鸣</v>
@@ -7150,7 +7269,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M141" s="2" t="s">
         <v>38</v>
@@ -7159,12 +7278,12 @@
         <v>39</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:15">
       <c r="A142" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>38</v>
@@ -7173,8 +7292,9 @@
         <v>39</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>282</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="E142" s="2"/>
       <c r="G142" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王真珍</v>
@@ -7184,7 +7304,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="M142" s="2" t="s">
         <v>38</v>
@@ -7198,7 +7318,7 @@
     </row>
     <row r="143" customHeight="1" spans="1:15">
       <c r="A143" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>14</v>
@@ -7207,8 +7327,9 @@
         <v>15</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="E143" s="2"/>
       <c r="G143" s="2" t="str">
         <f t="shared" si="5"/>
         <v>徐灵钰</v>
@@ -7218,7 +7339,7 @@
         <v>维护部门</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M143" s="2" t="s">
         <v>14</v>
@@ -7227,12 +7348,12 @@
         <v>15</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:15">
       <c r="A144" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>31</v>
@@ -7241,8 +7362,9 @@
         <v>32</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="E144" s="2"/>
       <c r="G144" s="2" t="str">
         <f t="shared" si="5"/>
         <v>游瑞凤</v>
@@ -7252,7 +7374,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M144" s="2" t="s">
         <v>31</v>
@@ -7261,12 +7383,12 @@
         <v>32</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="1:15">
       <c r="A145" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>38</v>
@@ -7275,8 +7397,9 @@
         <v>39</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>288</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="E145" s="2"/>
       <c r="G145" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李丽红</v>
@@ -7286,7 +7409,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L145" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="M145" s="2" t="s">
         <v>38</v>
@@ -7295,12 +7418,12 @@
         <v>39</v>
       </c>
       <c r="O145" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="1:15">
       <c r="A146" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>38</v>
@@ -7309,8 +7432,9 @@
         <v>117</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>290</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="E146" s="2"/>
       <c r="G146" s="2" t="str">
         <f t="shared" si="5"/>
         <v>胡艺红</v>
@@ -7320,7 +7444,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L146" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M146" s="2" t="s">
         <v>38</v>
@@ -7329,22 +7453,23 @@
         <v>117</v>
       </c>
       <c r="O146" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="1:15">
       <c r="A147" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>293</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="E147" s="2"/>
       <c r="G147" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7354,31 +7479,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L147" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="M147" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O147" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:15">
       <c r="A148" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>293</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="E148" s="2"/>
       <c r="G148" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7388,31 +7514,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M148" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O148" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="1:15">
       <c r="A149" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>293</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="E149" s="2"/>
       <c r="G149" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7422,31 +7549,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L149" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="M149" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O149" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="150" customHeight="1" spans="1:15">
       <c r="A150" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C150" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D150" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>297</v>
-      </c>
+      <c r="E150" s="2"/>
       <c r="G150" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林小凤</v>
@@ -7456,31 +7584,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="M150" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N150" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O150" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="O150" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="1:15">
       <c r="A151" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>299</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="E151" s="2"/>
       <c r="G151" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾雅芳</v>
@@ -7490,31 +7619,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="M151" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O151" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="1:15">
       <c r="A152" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>301</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="E152" s="2"/>
       <c r="G152" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林秋琼</v>
@@ -7524,31 +7654,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="M152" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O152" s="2" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="1:15">
       <c r="A153" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>303</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="E153" s="2"/>
       <c r="G153" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄锴</v>
@@ -7558,31 +7689,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="M153" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O153" s="2" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:15">
       <c r="A154" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>305</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="E154" s="2"/>
       <c r="G154" s="2" t="str">
         <f t="shared" si="5"/>
         <v>张婷婷</v>
@@ -7592,31 +7724,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L154" s="2" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="M154" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O154" s="2" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:15">
       <c r="A155" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>307</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="E155" s="2"/>
       <c r="G155" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄凤苗</v>
@@ -7626,21 +7759,21 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M155" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O155" s="2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:15">
       <c r="A156" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>38</v>
@@ -7649,8 +7782,9 @@
         <v>42</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>309</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="E156" s="2"/>
       <c r="G156" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴燕红</v>
@@ -7660,7 +7794,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="M156" s="2" t="s">
         <v>38</v>
@@ -7669,12 +7803,12 @@
         <v>42</v>
       </c>
       <c r="O156" s="2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:15">
       <c r="A157" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>38</v>
@@ -7683,8 +7817,9 @@
         <v>42</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>311</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="E157" s="2"/>
       <c r="G157" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王凤钦</v>
@@ -7694,7 +7829,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L157" s="2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M157" s="2" t="s">
         <v>38</v>
@@ -7703,12 +7838,12 @@
         <v>42</v>
       </c>
       <c r="O157" s="2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="158" customHeight="1" spans="1:15">
       <c r="A158" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>38</v>
@@ -7717,8 +7852,9 @@
         <v>42</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>313</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="E158" s="2"/>
       <c r="G158" s="2" t="str">
         <f t="shared" si="5"/>
         <v>傅佳玲</v>
@@ -7728,7 +7864,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L158" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="M158" s="2" t="s">
         <v>38</v>
@@ -7737,12 +7873,12 @@
         <v>42</v>
       </c>
       <c r="O158" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="159" customHeight="1" spans="1:15">
       <c r="A159" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>38</v>
@@ -7751,8 +7887,9 @@
         <v>42</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>316</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="E159" s="2"/>
       <c r="G159" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴敏凤</v>
@@ -7762,7 +7899,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L159" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M159" s="2" t="s">
         <v>38</v>
@@ -7771,12 +7908,12 @@
         <v>42</v>
       </c>
       <c r="O159" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:15">
       <c r="A160" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>38</v>
@@ -7785,8 +7922,9 @@
         <v>42</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>318</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="E160" s="2"/>
       <c r="G160" s="2" t="str">
         <f t="shared" si="5"/>
         <v>张滟莲</v>
@@ -7796,7 +7934,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L160" s="2" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M160" s="2" t="s">
         <v>38</v>
@@ -7805,12 +7943,12 @@
         <v>42</v>
       </c>
       <c r="O160" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="161" customHeight="1" spans="1:15">
       <c r="A161" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>38</v>
@@ -7819,8 +7957,9 @@
         <v>42</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>321</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="E161" s="2"/>
       <c r="G161" s="2" t="str">
         <f t="shared" si="5"/>
         <v>邱彬彬</v>
@@ -7830,7 +7969,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L161" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="M161" s="2" t="s">
         <v>38</v>
@@ -7839,22 +7978,23 @@
         <v>42</v>
       </c>
       <c r="O161" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:15">
       <c r="A162" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>323</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="E162" s="2"/>
       <c r="G162" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈浩</v>
@@ -7864,31 +8004,32 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M162" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O162" s="2" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="1:15">
       <c r="A163" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>325</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E163" s="2"/>
       <c r="G163" s="2" t="str">
         <f t="shared" si="5"/>
         <v>施桂兰</v>
@@ -7898,21 +8039,21 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L163" s="2" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="M163" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O163" s="2" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="164" customHeight="1" spans="1:15">
       <c r="A164" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>31</v>
@@ -7921,8 +8062,9 @@
         <v>32</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>327</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="E164" s="2"/>
       <c r="G164" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈燕秀</v>
@@ -7932,7 +8074,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="M164" s="2" t="s">
         <v>31</v>
@@ -7941,12 +8083,12 @@
         <v>32</v>
       </c>
       <c r="O164" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="165" customHeight="1" spans="1:15">
       <c r="A165" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>31</v>
@@ -7955,8 +8097,9 @@
         <v>125</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>329</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="E165" s="2"/>
       <c r="G165" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴清玉</v>
@@ -7966,7 +8109,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L165" s="2" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="M165" s="2" t="s">
         <v>31</v>
@@ -7975,12 +8118,12 @@
         <v>125</v>
       </c>
       <c r="O165" s="2" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" customHeight="1" spans="1:15">
       <c r="A166" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>31</v>
@@ -7989,8 +8132,9 @@
         <v>125</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>331</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="E166" s="2"/>
       <c r="G166" s="2" t="str">
         <f t="shared" si="5"/>
         <v>游惠卿</v>
@@ -8000,7 +8144,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L166" s="2" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M166" s="2" t="s">
         <v>31</v>
@@ -8009,12 +8153,12 @@
         <v>125</v>
       </c>
       <c r="O166" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="1:15">
       <c r="A167" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>31</v>
@@ -8023,8 +8167,9 @@
         <v>125</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>333</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="E167" s="2"/>
       <c r="G167" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林聪义</v>
@@ -8034,7 +8179,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L167" s="2" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="M167" s="2" t="s">
         <v>31</v>
@@ -8043,12 +8188,12 @@
         <v>125</v>
       </c>
       <c r="O167" s="2" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="168" customHeight="1" spans="1:15">
       <c r="A168" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>31</v>
@@ -8057,8 +8202,9 @@
         <v>32</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>335</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="E168" s="2"/>
       <c r="G168" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄淑玲</v>
@@ -8068,7 +8214,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="M168" s="2" t="s">
         <v>31</v>
@@ -8077,12 +8223,12 @@
         <v>32</v>
       </c>
       <c r="O168" s="2" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="169" customHeight="1" spans="1:15">
       <c r="A169" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>31</v>
@@ -8091,8 +8237,9 @@
         <v>32</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>337</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="E169" s="2"/>
       <c r="G169" s="2" t="str">
         <f t="shared" si="5"/>
         <v>连海珠</v>
@@ -8102,7 +8249,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="M169" s="2" t="s">
         <v>31</v>
@@ -8111,12 +8258,12 @@
         <v>32</v>
       </c>
       <c r="O169" s="2" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
     </row>
     <row r="170" customHeight="1" spans="1:15">
       <c r="A170" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>31</v>
@@ -8125,8 +8272,9 @@
         <v>32</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>339</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="E170" s="2"/>
       <c r="G170" s="2" t="str">
         <f t="shared" si="5"/>
         <v>洪宏</v>
@@ -8136,7 +8284,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L170" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M170" s="2" t="s">
         <v>31</v>
@@ -8145,12 +8293,12 @@
         <v>32</v>
       </c>
       <c r="O170" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" customHeight="1" spans="1:15">
       <c r="A171" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>38</v>
@@ -8159,8 +8307,9 @@
         <v>39</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>341</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="E171" s="2"/>
       <c r="G171" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈秋菊</v>
@@ -8170,7 +8319,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L171" s="2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="M171" s="2" t="s">
         <v>38</v>
@@ -8179,22 +8328,23 @@
         <v>39</v>
       </c>
       <c r="O171" s="2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="172" customHeight="1" spans="1:15">
       <c r="A172" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>345</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="E172" s="2"/>
       <c r="G172" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林惠兰</v>
@@ -8204,31 +8354,32 @@
         <v>运营策略中心</v>
       </c>
       <c r="L172" s="2" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="M172" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="O172" s="2" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="173" customHeight="1" spans="1:15">
       <c r="A173" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>347</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="E173" s="2"/>
       <c r="G173" s="2" t="str">
         <f t="shared" si="5"/>
         <v>丁洁</v>
@@ -8238,31 +8389,32 @@
         <v>运营策略中心</v>
       </c>
       <c r="L173" s="2" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="M173" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="O173" s="2" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="174" customHeight="1" spans="1:15">
       <c r="A174" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>349</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="E174" s="2"/>
       <c r="G174" s="2" t="str">
         <f t="shared" si="5"/>
         <v>夏皖鹭</v>
@@ -8272,31 +8424,32 @@
         <v>大客部门</v>
       </c>
       <c r="L174" s="2" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M174" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O174" s="2" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="175" customHeight="1" spans="1:15">
       <c r="A175" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="E175" s="2"/>
       <c r="G175" s="2" t="str">
         <f t="shared" si="5"/>
         <v>无</v>
@@ -8306,21 +8459,21 @@
         <v>大客部门</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="M175" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="O175" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="176" customHeight="1" spans="1:15">
       <c r="A176" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>45</v>
@@ -8329,8 +8482,9 @@
         <v>45</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>353</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="E176" s="2"/>
       <c r="G176" s="2" t="str">
         <f t="shared" si="5"/>
         <v>行发基木鱼</v>
@@ -8340,7 +8494,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="M176" s="2" t="s">
         <v>45</v>
@@ -8349,12 +8503,12 @@
         <v>45</v>
       </c>
       <c r="O176" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
     </row>
     <row r="177" customHeight="1" spans="1:15">
       <c r="A177" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>45</v>
@@ -8363,8 +8517,9 @@
         <v>98</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>355</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="E177" s="2"/>
       <c r="G177" s="2" t="str">
         <f t="shared" si="5"/>
         <v>朱书兰</v>
@@ -8374,7 +8529,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="M177" s="2" t="s">
         <v>45</v>
@@ -8383,22 +8538,23 @@
         <v>98</v>
       </c>
       <c r="O177" s="2" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="178" customHeight="1" spans="1:15">
       <c r="A178" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>358</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="E178" s="2"/>
       <c r="G178" s="2" t="str">
         <f t="shared" si="5"/>
         <v>萧月梅</v>
@@ -8408,31 +8564,32 @@
         <v>行发维护大区</v>
       </c>
       <c r="L178" s="2" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="M178" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="O178" s="2" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" customHeight="1" spans="1:15">
       <c r="A179" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>360</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E179" s="2"/>
       <c r="G179" s="2" t="str">
         <f t="shared" si="5"/>
         <v>胡晓惠</v>
@@ -8442,31 +8599,32 @@
         <v>行发维护大区</v>
       </c>
       <c r="L179" s="2" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M179" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O179" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="180" customHeight="1" spans="1:15">
       <c r="A180" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>362</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="E180" s="2"/>
       <c r="G180" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林丹丹</v>
@@ -8476,31 +8634,32 @@
         <v>行发维护大区</v>
       </c>
       <c r="L180" s="2" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="M180" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O180" s="2" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181" customHeight="1" spans="1:15">
       <c r="A181" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>364</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="E181" s="2"/>
       <c r="G181" s="2" t="str">
         <f t="shared" si="5"/>
         <v>姚美玲</v>
@@ -8510,31 +8669,32 @@
         <v>行发维护大区</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="M181" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O181" s="2" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
     </row>
     <row r="182" customHeight="1" spans="1:15">
       <c r="A182" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>366</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="E182" s="2"/>
       <c r="G182" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈雪梅</v>
@@ -8544,21 +8704,21 @@
         <v>行发维护大区</v>
       </c>
       <c r="L182" s="2" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="M182" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O182" s="2" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="183" customHeight="1" spans="1:15">
       <c r="A183" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>6</v>
@@ -8567,8 +8727,9 @@
         <v>112</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>368</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="E183" s="2"/>
       <c r="G183" s="2" t="str">
         <f t="shared" si="5"/>
         <v>詹大钧</v>
@@ -8578,7 +8739,7 @@
         <v>新开部门</v>
       </c>
       <c r="L183" s="2" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="M183" s="2" t="s">
         <v>6</v>
@@ -8587,22 +8748,23 @@
         <v>112</v>
       </c>
       <c r="O183" s="2" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
     </row>
     <row r="184" customHeight="1" spans="1:15">
       <c r="A184" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>370</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="E184" s="2"/>
       <c r="G184" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郑博萱</v>
@@ -8612,21 +8774,21 @@
         <v>维护部门</v>
       </c>
       <c r="L184" s="2" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="M184" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O184" s="2" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
     </row>
     <row r="185" customHeight="1" spans="1:15">
       <c r="A185" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>45</v>
@@ -8635,8 +8797,9 @@
         <v>98</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>372</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="E185" s="2"/>
       <c r="G185" s="2" t="str">
         <f t="shared" si="5"/>
         <v>朱丽珊</v>
@@ -8646,7 +8809,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L185" s="2" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="M185" s="2" t="s">
         <v>45</v>
@@ -8655,22 +8818,23 @@
         <v>98</v>
       </c>
       <c r="O185" s="2" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="186" customHeight="1" spans="1:15">
       <c r="A186" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>374</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="E186" s="2"/>
       <c r="G186" s="2" t="str">
         <f t="shared" si="5"/>
         <v>葛晓丹</v>
@@ -8680,31 +8844,32 @@
         <v>大客部门</v>
       </c>
       <c r="L186" s="2" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="M186" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O186" s="2" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
     </row>
     <row r="187" customHeight="1" spans="1:15">
       <c r="A187" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>376</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="E187" s="2"/>
       <c r="G187" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李丹凤</v>
@@ -8714,31 +8879,32 @@
         <v>大客部门</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="M187" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O187" s="2" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="188" customHeight="1" spans="1:15">
       <c r="A188" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>378</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="E188" s="2"/>
       <c r="G188" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郭琳娟</v>
@@ -8748,31 +8914,32 @@
         <v>大客部门</v>
       </c>
       <c r="L188" s="2" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="M188" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O188" s="2" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="189" customHeight="1" spans="1:15">
       <c r="A189" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>19</v>
       </c>
+      <c r="E189" s="2"/>
       <c r="G189" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈金锐</v>
@@ -8782,31 +8949,32 @@
         <v>大客部门</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="M189" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>18</v>
+        <v>228</v>
       </c>
       <c r="O189" s="2" t="s">
-        <v>220</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" customHeight="1" spans="1:15">
       <c r="A190" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>381</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="E190" s="2"/>
       <c r="G190" s="2" t="str">
         <f t="shared" si="5"/>
         <v>杨晶晶</v>
@@ -8816,21 +8984,21 @@
         <v>维护部门</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="M190" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O190" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="191" customHeight="1" spans="1:15">
       <c r="A191" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>10</v>
@@ -8841,6 +9009,7 @@
       <c r="D191" s="2" t="s">
         <v>132</v>
       </c>
+      <c r="E191" s="2"/>
       <c r="G191" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈婷</v>
@@ -8850,7 +9019,7 @@
         <v>大客部门</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="M191" s="2" t="s">
         <v>10</v>
@@ -8864,17 +9033,18 @@
     </row>
     <row r="192" customHeight="1" spans="1:15">
       <c r="A192" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>385</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="E192" s="2"/>
       <c r="G192" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林洁</v>
@@ -8884,31 +9054,32 @@
         <v>大客部门</v>
       </c>
       <c r="L192" s="2" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="M192" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="O192" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" customHeight="1" spans="1:15">
       <c r="A193" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>387</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="E193" s="2"/>
       <c r="G193" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郑燕森</v>
@@ -8918,31 +9089,32 @@
         <v>大客部门</v>
       </c>
       <c r="L193" s="2" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="M193" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N193" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O193" s="2" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="194" customHeight="1" spans="1:15">
       <c r="A194" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>390</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="E194" s="2"/>
       <c r="G194" s="2" t="str">
         <f t="shared" si="5"/>
         <v>许珊珊</v>
@@ -8952,21 +9124,21 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L194" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="M194" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="O194" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="195" customHeight="1" spans="1:15">
       <c r="A195" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>35</v>
@@ -8977,6 +9149,7 @@
       <c r="D195" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E195" s="2"/>
       <c r="G195" s="2" t="str">
         <f t="shared" ref="G195:G230" si="7">D195</f>
         <v>框架</v>
@@ -8986,7 +9159,7 @@
         <v>框架</v>
       </c>
       <c r="L195" s="2" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="M195" s="2" t="s">
         <v>35</v>
@@ -9000,7 +9173,7 @@
     </row>
     <row r="196" customHeight="1" spans="1:15">
       <c r="A196" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>35</v>
@@ -9011,6 +9184,7 @@
       <c r="D196" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E196" s="2"/>
       <c r="G196" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9020,7 +9194,7 @@
         <v>框架</v>
       </c>
       <c r="L196" s="2" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="M196" s="2" t="s">
         <v>35</v>
@@ -9034,7 +9208,7 @@
     </row>
     <row r="197" customHeight="1" spans="1:15">
       <c r="A197" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>35</v>
@@ -9045,6 +9219,7 @@
       <c r="D197" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E197" s="2"/>
       <c r="G197" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9054,7 +9229,7 @@
         <v>框架</v>
       </c>
       <c r="L197" s="2" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="M197" s="2" t="s">
         <v>35</v>
@@ -9068,7 +9243,7 @@
     </row>
     <row r="198" customHeight="1" spans="1:15">
       <c r="A198" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>35</v>
@@ -9079,6 +9254,7 @@
       <c r="D198" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E198" s="2"/>
       <c r="G198" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9088,7 +9264,7 @@
         <v>框架</v>
       </c>
       <c r="L198" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M198" s="2" t="s">
         <v>35</v>
@@ -9102,17 +9278,18 @@
     </row>
     <row r="199" customHeight="1" spans="1:15">
       <c r="A199" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>397</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="E199" s="2"/>
       <c r="G199" s="2" t="str">
         <f t="shared" si="7"/>
         <v>庄艺娜</v>
@@ -9122,31 +9299,32 @@
         <v>医疗事业部</v>
       </c>
       <c r="L199" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="M199" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="O199" s="2" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="200" customHeight="1" spans="1:15">
       <c r="A200" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>399</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="E200" s="2"/>
       <c r="G200" s="2" t="str">
         <f t="shared" si="7"/>
         <v>谢龙辉</v>
@@ -9156,21 +9334,21 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L200" s="2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="M200" s="2" t="s">
         <v>38</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="O200" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="201" customHeight="1" spans="1:15">
       <c r="A201" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>31</v>
@@ -9179,8 +9357,9 @@
         <v>32</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="E201" s="2"/>
       <c r="G201" s="2" t="str">
         <f t="shared" si="7"/>
         <v>无</v>
@@ -9190,7 +9369,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L201" s="2" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="M201" s="2" t="s">
         <v>31</v>
@@ -9199,12 +9378,12 @@
         <v>32</v>
       </c>
       <c r="O201" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="202" customHeight="1" spans="1:15">
       <c r="A202" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>31</v>
@@ -9213,8 +9392,9 @@
         <v>32</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>351</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="E202" s="2"/>
       <c r="G202" s="2" t="str">
         <f t="shared" si="7"/>
         <v>无</v>
@@ -9224,7 +9404,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L202" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="M202" s="2" t="s">
         <v>31</v>
@@ -9233,12 +9413,12 @@
         <v>32</v>
       </c>
       <c r="O202" s="2" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="203" customHeight="1" spans="1:15">
       <c r="A203" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>35</v>
@@ -9249,6 +9429,7 @@
       <c r="D203" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E203" s="2"/>
       <c r="G203" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9258,7 +9439,7 @@
         <v>框架</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="M203" s="2" t="s">
         <v>35</v>
@@ -9272,7 +9453,7 @@
     </row>
     <row r="204" customHeight="1" spans="1:15">
       <c r="A204" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>31</v>
@@ -9281,8 +9462,9 @@
         <v>125</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>404</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="E204" s="2"/>
       <c r="G204" s="2" t="str">
         <f t="shared" si="7"/>
         <v>王达斌</v>
@@ -9292,7 +9474,7 @@
         <v>漳州客服部</v>
       </c>
       <c r="L204" s="2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M204" s="2" t="s">
         <v>31</v>
@@ -9301,12 +9483,12 @@
         <v>125</v>
       </c>
       <c r="O204" s="2" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="205" customHeight="1" spans="1:15">
       <c r="A205" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>38</v>
@@ -9315,8 +9497,9 @@
         <v>39</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>406</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="E205" s="2"/>
       <c r="G205" s="2" t="str">
         <f t="shared" si="7"/>
         <v>苏巧萍</v>
@@ -9326,7 +9509,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L205" s="2" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="M205" s="2" t="s">
         <v>38</v>
@@ -9335,12 +9518,12 @@
         <v>39</v>
       </c>
       <c r="O205" s="2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="206" customHeight="1" spans="1:15">
       <c r="A206" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>35</v>
@@ -9351,6 +9534,7 @@
       <c r="D206" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E206" s="2"/>
       <c r="G206" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9360,7 +9544,7 @@
         <v>框架</v>
       </c>
       <c r="L206" s="2" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="M206" s="2" t="s">
         <v>35</v>
@@ -9374,7 +9558,7 @@
     </row>
     <row r="207" customHeight="1" spans="1:15">
       <c r="A207" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>38</v>
@@ -9385,6 +9569,7 @@
       <c r="D207" s="2" t="s">
         <v>110</v>
       </c>
+      <c r="E207" s="2"/>
       <c r="G207" s="2" t="str">
         <f t="shared" si="7"/>
         <v>黄春荣</v>
@@ -9394,7 +9579,7 @@
         <v>泉州中小企业增值部</v>
       </c>
       <c r="L207" s="2" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="M207" s="2" t="s">
         <v>38</v>
@@ -9408,7 +9593,7 @@
     </row>
     <row r="208" customHeight="1" spans="1:15">
       <c r="A208" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>45</v>
@@ -9417,8 +9602,9 @@
         <v>98</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>170</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="E208" s="2"/>
       <c r="G208" s="2" t="str">
         <f t="shared" si="7"/>
         <v>茅巧丽</v>
@@ -9428,7 +9614,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L208" s="2" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="M208" s="2" t="s">
         <v>45</v>
@@ -9437,12 +9623,12 @@
         <v>98</v>
       </c>
       <c r="O208" s="2" t="s">
-        <v>170</v>
+        <v>403</v>
       </c>
     </row>
     <row r="209" customHeight="1" spans="1:15">
       <c r="A209" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>45</v>
@@ -9451,8 +9637,9 @@
         <v>46</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>411</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="E209" s="2"/>
       <c r="G209" s="2" t="str">
         <f t="shared" si="7"/>
         <v>林婷</v>
@@ -9462,7 +9649,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="M209" s="2" t="s">
         <v>45</v>
@@ -9471,22 +9658,23 @@
         <v>46</v>
       </c>
       <c r="O209" s="2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="210" customHeight="1" spans="1:15">
       <c r="A210" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>413</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="E210" s="2"/>
       <c r="G210" s="2" t="str">
         <f t="shared" si="7"/>
         <v>李佳敏</v>
@@ -9496,31 +9684,32 @@
         <v>维护部门</v>
       </c>
       <c r="L210" s="2" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="M210" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N210" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O210" s="2" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="211" customHeight="1" spans="1:15">
       <c r="A211" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>415</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="E211" s="2"/>
       <c r="G211" s="2" t="str">
         <f t="shared" si="7"/>
         <v>郑博</v>
@@ -9530,21 +9719,21 @@
         <v>大客部门</v>
       </c>
       <c r="L211" s="2" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="M211" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N211" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="O211" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="212" customHeight="1" spans="1:15">
       <c r="A212" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>10</v>
@@ -9553,8 +9742,9 @@
         <v>18</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>417</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="E212" s="2"/>
       <c r="G212" s="2" t="str">
         <f t="shared" si="7"/>
         <v>郭雅玲</v>
@@ -9564,7 +9754,7 @@
         <v>大客部门</v>
       </c>
       <c r="L212" s="2" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="M212" s="2" t="s">
         <v>10</v>
@@ -9573,22 +9763,23 @@
         <v>18</v>
       </c>
       <c r="O212" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="213" customHeight="1" spans="1:15">
       <c r="A213" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>419</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="E213" s="2"/>
       <c r="G213" s="2" t="str">
         <f t="shared" si="7"/>
         <v>张燕红</v>
@@ -9598,21 +9789,21 @@
         <v>医疗事业部</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="M213" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N213" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="O213" s="2" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="214" customHeight="1" spans="1:15">
       <c r="A214" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>45</v>
@@ -9621,8 +9812,9 @@
         <v>98</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>421</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="E214" s="2"/>
       <c r="G214" s="2" t="str">
         <f t="shared" si="7"/>
         <v>周莉莉</v>
@@ -9632,7 +9824,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L214" s="2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="M214" s="2" t="s">
         <v>45</v>
@@ -9641,46 +9833,47 @@
         <v>98</v>
       </c>
       <c r="O214" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="215" customHeight="1" spans="1:15">
       <c r="A215" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>423</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="D215" t="s">
+        <v>417</v>
+      </c>
+      <c r="E215" s="2"/>
       <c r="G215" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>尹林平</v>
+        <v>何清霞</v>
       </c>
       <c r="H215" s="2" t="str">
         <f t="shared" si="8"/>
         <v>大客部门</v>
       </c>
       <c r="L215" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="M215" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N215" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="O215" s="2" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="216" customHeight="1" spans="1:15">
       <c r="A216" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>10</v>
@@ -9691,6 +9884,7 @@
       <c r="D216" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="E216" s="2"/>
       <c r="G216" s="2" t="str">
         <f t="shared" si="7"/>
         <v>陈沅</v>
@@ -9700,31 +9894,32 @@
         <v>大客部门</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="M216" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N216" s="2" t="s">
-        <v>384</v>
+        <v>11</v>
       </c>
       <c r="O216" s="2" t="s">
-        <v>425</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217" customHeight="1" spans="1:15">
       <c r="A217" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>241</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="E217" s="2"/>
       <c r="G217" s="2" t="str">
         <f t="shared" si="7"/>
         <v>纪荣裕</v>
@@ -9734,31 +9929,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="M217" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N217" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O217" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="218" customHeight="1" spans="1:15">
       <c r="A218" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>267</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="E218" s="2"/>
       <c r="G218" s="2" t="str">
         <f t="shared" si="7"/>
         <v>苏晨</v>
@@ -9768,31 +9964,32 @@
         <v>失效挽救部</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="M218" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N218" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O218" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="219" customHeight="1" spans="1:15">
       <c r="A219" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>399</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="E219" s="2"/>
       <c r="G219" s="2" t="str">
         <f t="shared" si="7"/>
         <v>谢龙辉</v>
@@ -9802,31 +9999,32 @@
         <v>泉州KOL部门</v>
       </c>
       <c r="L219" s="2" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="M219" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N219" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="O219" s="2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="220" customHeight="1" spans="1:15">
       <c r="A220" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>390</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="E220" s="2"/>
       <c r="G220" s="2" t="str">
         <f t="shared" si="7"/>
         <v>许珊珊</v>
@@ -9836,31 +10034,32 @@
         <v>泉州KOL部门</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="N220" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="O220" s="2" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
     </row>
     <row r="221" customHeight="1" spans="1:15">
       <c r="A221" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>385</v>
-      </c>
+        <v>378</v>
+      </c>
+      <c r="E221" s="2"/>
       <c r="G221" s="2" t="str">
         <f t="shared" si="7"/>
         <v>林洁</v>
@@ -9870,31 +10069,32 @@
         <v>大客部门</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="M221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N221" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="O221" s="2" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="222" customHeight="1" spans="1:15">
       <c r="A222" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>381</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="E222" s="2"/>
       <c r="G222" s="2" t="str">
         <f t="shared" si="7"/>
         <v>杨晶晶</v>
@@ -9904,31 +10104,32 @@
         <v>大客部门</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="M222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="O222" s="2" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="223" customHeight="1" spans="1:15">
       <c r="A223" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D223" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="E223" s="2"/>
       <c r="G223" s="2" t="str">
         <f t="shared" si="7"/>
         <v>叶玲</v>
@@ -9938,31 +10139,32 @@
         <v>维护部门</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="M223" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N223" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O223" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="O223" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="224" customHeight="1" spans="1:15">
       <c r="A224" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>360</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E224" s="2"/>
       <c r="G224" s="2" t="str">
         <f t="shared" si="7"/>
         <v>胡晓惠</v>
@@ -9972,21 +10174,21 @@
         <v>行发维护大区</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="M224" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N224" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O224" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="225" customHeight="1" spans="1:15">
       <c r="A225" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>35</v>
@@ -9997,6 +10199,7 @@
       <c r="D225" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E225" s="2"/>
       <c r="G225" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10006,7 +10209,7 @@
         <v>框架</v>
       </c>
       <c r="L225" s="2" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="M225" s="2" t="s">
         <v>35</v>
@@ -10020,7 +10223,7 @@
     </row>
     <row r="226" customHeight="1" spans="1:15">
       <c r="A226" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>14</v>
@@ -10029,8 +10232,9 @@
         <v>15</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>163</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="E226" s="2"/>
       <c r="G226" s="2" t="str">
         <f t="shared" si="7"/>
         <v>杜鑫鑫</v>
@@ -10040,7 +10244,7 @@
         <v>维护部门</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="M226" s="2" t="s">
         <v>14</v>
@@ -10049,12 +10253,12 @@
         <v>15</v>
       </c>
       <c r="O226" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="227" customHeight="1" spans="1:15">
       <c r="A227" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>35</v>
@@ -10065,6 +10269,7 @@
       <c r="D227" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E227" s="2"/>
       <c r="G227" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10074,7 +10279,7 @@
         <v>框架</v>
       </c>
       <c r="L227" s="2" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="M227" s="2" t="s">
         <v>35</v>
@@ -10088,17 +10293,18 @@
     </row>
     <row r="228" customHeight="1" spans="1:15">
       <c r="A228" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>360</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="E228" s="2"/>
       <c r="G228" s="2" t="str">
         <f t="shared" si="7"/>
         <v>胡晓惠</v>
@@ -10108,21 +10314,21 @@
         <v>行发维护大区</v>
       </c>
       <c r="L228" s="2" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="M228" s="2" t="s">
         <v>45</v>
       </c>
       <c r="N228" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O228" s="2" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
     </row>
     <row r="229" customHeight="1" spans="1:15">
       <c r="A229" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>35</v>
@@ -10133,6 +10339,7 @@
       <c r="D229" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E229" s="2"/>
       <c r="G229" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10142,7 +10349,7 @@
         <v>框架</v>
       </c>
       <c r="L229" s="2" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="M229" s="2" t="s">
         <v>35</v>
@@ -10156,7 +10363,7 @@
     </row>
     <row r="230" customHeight="1" spans="1:15">
       <c r="A230" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>45</v>
@@ -10165,8 +10372,9 @@
         <v>98</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>421</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="E230" s="2"/>
       <c r="G230" s="2" t="str">
         <f t="shared" si="7"/>
         <v>周莉莉</v>
@@ -10176,7 +10384,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="M230" s="2" t="s">
         <v>45</v>
@@ -10185,12 +10393,12 @@
         <v>98</v>
       </c>
       <c r="O230" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="231" customHeight="1" spans="1:15">
       <c r="A231" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>35</v>
@@ -10201,16 +10409,17 @@
       <c r="D231" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E231" s="2"/>
       <c r="G231" s="2" t="str">
-        <f t="shared" ref="G231:G232" si="9">D231</f>
+        <f>D231</f>
         <v>框架</v>
       </c>
       <c r="H231" s="2" t="str">
-        <f t="shared" ref="H231:H232" si="10">B231</f>
+        <f t="shared" ref="H231:H232" si="9">B231</f>
         <v>框架</v>
       </c>
       <c r="L231" s="2" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="M231" s="2" t="s">
         <v>35</v>
@@ -10224,7 +10433,7 @@
     </row>
     <row r="232" customHeight="1" spans="1:15">
       <c r="A232" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>35</v>
@@ -10235,16 +10444,17 @@
       <c r="D232" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E232" s="2"/>
       <c r="G232" s="2" t="str">
+        <f t="shared" ref="G231:G232" si="10">D232</f>
+        <v>框架</v>
+      </c>
+      <c r="H232" s="2" t="str">
         <f t="shared" si="9"/>
         <v>框架</v>
       </c>
-      <c r="H232" s="2" t="str">
-        <f t="shared" si="10"/>
-        <v>框架</v>
-      </c>
       <c r="L232" s="2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="M232" s="2" t="s">
         <v>35</v>
@@ -10258,7 +10468,7 @@
     </row>
     <row r="233" customHeight="1" spans="1:15">
       <c r="A233" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>35</v>
@@ -10269,6 +10479,7 @@
       <c r="D233" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E233" s="2"/>
       <c r="G233" s="2" t="str">
         <f t="shared" ref="G233" si="11">D233</f>
         <v>框架</v>
@@ -10278,7 +10489,7 @@
         <v>框架</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="M233" s="2" t="s">
         <v>35</v>
@@ -10292,7 +10503,7 @@
     </row>
     <row r="234" customHeight="1" spans="1:15">
       <c r="A234" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>35</v>
@@ -10303,6 +10514,7 @@
       <c r="D234" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="E234" s="2"/>
       <c r="G234" s="2" t="str">
         <f t="shared" ref="G234" si="13">D234</f>
         <v>框架</v>
@@ -10312,7 +10524,7 @@
         <v>框架</v>
       </c>
       <c r="L234" s="2" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="M234" s="2" t="s">
         <v>35</v>
@@ -10326,7 +10538,7 @@
     </row>
     <row r="235" spans="1:15">
       <c r="A235" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>6</v>
@@ -10335,8 +10547,9 @@
         <v>7</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>177</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="E235" s="2"/>
       <c r="G235" s="2" t="str">
         <f t="shared" ref="G235:G236" si="15">D235</f>
         <v>叶惠</v>
@@ -10346,7 +10559,7 @@
         <v>新开部门</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M235" s="2" t="s">
         <v>6</v>
@@ -10355,22 +10568,23 @@
         <v>7</v>
       </c>
       <c r="O235" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="236" spans="1:15">
       <c r="A236" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>448</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="E236" s="2"/>
       <c r="G236" s="2" t="str">
         <f t="shared" si="15"/>
         <v>厦门自营电商</v>
@@ -10380,22 +10594,19 @@
         <v>行发维护大区</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="M236" s="2" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="N236" s="2" t="s">
-        <v>112</v>
+        <v>350</v>
       </c>
       <c r="O236" s="2" t="s">
-        <v>263</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E236">
-    <extLst/>
-  </autoFilter>
   <conditionalFormatting sqref="A2:A232">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/通讯录.xlsx
+++ b/通讯录.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1891" uniqueCount="442">
   <si>
     <t>管理员</t>
   </si>
@@ -1271,9 +1271,6 @@
   </si>
   <si>
     <t>何清霞</t>
-  </si>
-  <si>
-    <t>尹林平</t>
   </si>
   <si>
     <t>kolxm01</t>
@@ -1353,8 +1350,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -1381,14 +1378,76 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1402,38 +1461,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1450,52 +1478,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1510,15 +1493,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1539,13 +1536,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1557,91 +1644,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1659,7 +1662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1671,49 +1686,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1728,16 +1725,42 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1767,42 +1790,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1815,25 +1821,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1842,133 +1839,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2336,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -2381,7 +2378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:15">
+    <row r="2" hidden="1" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2394,7 +2391,6 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2"/>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G33" si="0">D2</f>
         <v>注册</v>
@@ -2416,7 +2412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:15">
+    <row r="3" hidden="1" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2429,7 +2425,6 @@
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>陈沅</v>
@@ -2451,7 +2446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:15">
+    <row r="4" hidden="1" customHeight="1" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -2464,7 +2459,6 @@
       <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2"/>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
         <v>俞培培</v>
@@ -2486,7 +2480,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="1:15">
+    <row r="5" hidden="1" customHeight="1" spans="1:15">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2499,7 +2493,6 @@
       <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="2"/>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
         <v>陈金锐</v>
@@ -2521,7 +2514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:15">
+    <row r="6" hidden="1" customHeight="1" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -2534,7 +2527,6 @@
       <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="2"/>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
         <v>杨丹凤</v>
@@ -2556,7 +2548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:15">
+    <row r="7" hidden="1" customHeight="1" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2569,7 +2561,6 @@
       <c r="D7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2"/>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
         <v>许曾美</v>
@@ -2591,7 +2582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:15">
+    <row r="8" hidden="1" customHeight="1" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -2604,7 +2595,6 @@
       <c r="D8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="2"/>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
         <v>信息流</v>
@@ -2626,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:15">
+    <row r="9" hidden="1" customHeight="1" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2639,7 +2629,6 @@
       <c r="D9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="2"/>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
         <v>信息流</v>
@@ -2661,7 +2650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:15">
+    <row r="10" hidden="1" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -2674,7 +2663,6 @@
       <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2"/>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
         <v>沈晓芬</v>
@@ -2696,7 +2684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:15">
+    <row r="11" hidden="1" customHeight="1" spans="1:15">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -2709,7 +2697,6 @@
       <c r="D11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="2"/>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
         <v>厦门总代理</v>
@@ -2731,7 +2718,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:15">
+    <row r="12" hidden="1" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -2744,7 +2731,6 @@
       <c r="D12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="2"/>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
         <v>泉州失效库</v>
@@ -2766,7 +2752,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:15">
+    <row r="13" hidden="1" customHeight="1" spans="1:15">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -2779,7 +2765,6 @@
       <c r="D13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="2"/>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
         <v>泉州建站</v>
@@ -2801,7 +2786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:15">
+    <row r="14" hidden="1" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -2814,7 +2799,6 @@
       <c r="D14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="2"/>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
         <v>丘连珍</v>
@@ -2836,7 +2820,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:15">
+    <row r="15" hidden="1" customHeight="1" spans="1:15">
       <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
@@ -2849,7 +2833,6 @@
       <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="2"/>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架代理</v>
@@ -2871,7 +2854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:15">
+    <row r="16" hidden="1" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -2884,7 +2867,6 @@
       <c r="D16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="2"/>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2906,7 +2888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="1:15">
+    <row r="17" hidden="1" customHeight="1" spans="1:15">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -2919,7 +2901,6 @@
       <c r="D17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="2"/>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2941,7 +2922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="1:15">
+    <row r="18" hidden="1" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
@@ -2954,7 +2935,6 @@
       <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="2"/>
       <c r="G18" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -2976,7 +2956,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:15">
+    <row r="19" hidden="1" customHeight="1" spans="1:15">
       <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
@@ -2989,7 +2969,6 @@
       <c r="D19" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="2"/>
       <c r="G19" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3011,7 +2990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="1:15">
+    <row r="20" hidden="1" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
         <v>54</v>
       </c>
@@ -3024,7 +3003,6 @@
       <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="2"/>
       <c r="G20" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3046,7 +3024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="1:15">
+    <row r="21" hidden="1" customHeight="1" spans="1:15">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -3059,7 +3037,6 @@
       <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="G21" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3081,7 +3058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="1:15">
+    <row r="22" hidden="1" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -3094,7 +3071,6 @@
       <c r="D22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="2"/>
       <c r="G22" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3116,7 +3092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" customHeight="1" spans="1:15">
+    <row r="23" hidden="1" customHeight="1" spans="1:15">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -3129,7 +3105,6 @@
       <c r="D23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="2"/>
       <c r="G23" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3151,7 +3126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="1:15">
+    <row r="24" hidden="1" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
         <v>58</v>
       </c>
@@ -3164,7 +3139,6 @@
       <c r="D24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="2"/>
       <c r="G24" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3186,7 +3160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="1:15">
+    <row r="25" hidden="1" customHeight="1" spans="1:15">
       <c r="A25" s="2" t="s">
         <v>59</v>
       </c>
@@ -3199,7 +3173,6 @@
       <c r="D25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E25" s="2"/>
       <c r="G25" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3221,7 +3194,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" customHeight="1" spans="1:15">
+    <row r="26" hidden="1" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
         <v>60</v>
       </c>
@@ -3234,7 +3207,6 @@
       <c r="D26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="2"/>
       <c r="G26" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3256,7 +3228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" customHeight="1" spans="1:15">
+    <row r="27" hidden="1" customHeight="1" spans="1:15">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -3269,7 +3241,6 @@
       <c r="D27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="2"/>
       <c r="G27" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3291,7 +3262,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" customHeight="1" spans="1:15">
+    <row r="28" hidden="1" customHeight="1" spans="1:15">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -3304,7 +3275,6 @@
       <c r="D28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="2"/>
       <c r="G28" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3326,7 +3296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" customHeight="1" spans="1:15">
+    <row r="29" hidden="1" customHeight="1" spans="1:15">
       <c r="A29" s="2" t="s">
         <v>63</v>
       </c>
@@ -3339,7 +3309,6 @@
       <c r="D29" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="2"/>
       <c r="G29" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3361,7 +3330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="1:15">
+    <row r="30" hidden="1" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -3374,7 +3343,6 @@
       <c r="D30" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="2"/>
       <c r="G30" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3396,7 +3364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:15">
+    <row r="31" hidden="1" customHeight="1" spans="1:15">
       <c r="A31" s="2" t="s">
         <v>65</v>
       </c>
@@ -3409,7 +3377,6 @@
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="2"/>
       <c r="G31" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3431,7 +3398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:15">
+    <row r="32" hidden="1" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
         <v>66</v>
       </c>
@@ -3444,7 +3411,6 @@
       <c r="D32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E32" s="2"/>
       <c r="G32" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3466,7 +3432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="1:15">
+    <row r="33" hidden="1" customHeight="1" spans="1:15">
       <c r="A33" s="2" t="s">
         <v>67</v>
       </c>
@@ -3479,7 +3445,6 @@
       <c r="D33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E33" s="2"/>
       <c r="G33" s="2" t="str">
         <f t="shared" si="0"/>
         <v>框架</v>
@@ -3501,7 +3466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" customHeight="1" spans="1:15">
+    <row r="34" hidden="1" customHeight="1" spans="1:15">
       <c r="A34" s="2" t="s">
         <v>68</v>
       </c>
@@ -3514,7 +3479,6 @@
       <c r="D34" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E34" s="2"/>
       <c r="G34" s="2" t="str">
         <f t="shared" ref="G34:G66" si="2">D34</f>
         <v>框架</v>
@@ -3536,7 +3500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:15">
+    <row r="35" hidden="1" customHeight="1" spans="1:15">
       <c r="A35" s="2" t="s">
         <v>69</v>
       </c>
@@ -3549,7 +3513,6 @@
       <c r="D35" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="2"/>
       <c r="G35" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3571,7 +3534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" customHeight="1" spans="1:15">
+    <row r="36" hidden="1" customHeight="1" spans="1:15">
       <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
@@ -3584,7 +3547,6 @@
       <c r="D36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="2"/>
       <c r="G36" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3606,7 +3568,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" customHeight="1" spans="1:15">
+    <row r="37" hidden="1" customHeight="1" spans="1:15">
       <c r="A37" s="2" t="s">
         <v>71</v>
       </c>
@@ -3619,7 +3581,6 @@
       <c r="D37" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="2"/>
       <c r="G37" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3641,7 +3602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" customHeight="1" spans="1:15">
+    <row r="38" hidden="1" customHeight="1" spans="1:15">
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
@@ -3654,7 +3615,6 @@
       <c r="D38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="2"/>
       <c r="G38" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3676,7 +3636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" customHeight="1" spans="1:15">
+    <row r="39" hidden="1" customHeight="1" spans="1:15">
       <c r="A39" s="2" t="s">
         <v>73</v>
       </c>
@@ -3689,7 +3649,6 @@
       <c r="D39" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="2"/>
       <c r="G39" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3711,7 +3670,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="1:15">
+    <row r="40" hidden="1" customHeight="1" spans="1:15">
       <c r="A40" s="2" t="s">
         <v>74</v>
       </c>
@@ -3724,7 +3683,6 @@
       <c r="D40" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E40" s="2"/>
       <c r="G40" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3746,7 +3704,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" customHeight="1" spans="1:15">
+    <row r="41" hidden="1" customHeight="1" spans="1:15">
       <c r="A41" s="2" t="s">
         <v>75</v>
       </c>
@@ -3759,7 +3717,6 @@
       <c r="D41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="2"/>
       <c r="G41" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3781,7 +3738,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" customHeight="1" spans="1:15">
+    <row r="42" hidden="1" customHeight="1" spans="1:15">
       <c r="A42" s="2" t="s">
         <v>76</v>
       </c>
@@ -3794,7 +3751,6 @@
       <c r="D42" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E42" s="2"/>
       <c r="G42" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3816,7 +3772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" customHeight="1" spans="1:15">
+    <row r="43" hidden="1" customHeight="1" spans="1:15">
       <c r="A43" s="2" t="s">
         <v>77</v>
       </c>
@@ -3829,7 +3785,6 @@
       <c r="D43" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="2"/>
       <c r="G43" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3851,7 +3806,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" customHeight="1" spans="1:15">
+    <row r="44" hidden="1" customHeight="1" spans="1:15">
       <c r="A44" s="2" t="s">
         <v>78</v>
       </c>
@@ -3864,7 +3819,6 @@
       <c r="D44" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E44" s="2"/>
       <c r="G44" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3886,7 +3840,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" customHeight="1" spans="1:15">
+    <row r="45" hidden="1" customHeight="1" spans="1:15">
       <c r="A45" s="2" t="s">
         <v>79</v>
       </c>
@@ -3899,7 +3853,6 @@
       <c r="D45" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E45" s="2"/>
       <c r="G45" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3921,7 +3874,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" customHeight="1" spans="1:15">
+    <row r="46" hidden="1" customHeight="1" spans="1:15">
       <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
@@ -3934,7 +3887,6 @@
       <c r="D46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E46" s="2"/>
       <c r="G46" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3956,7 +3908,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="1:15">
+    <row r="47" hidden="1" customHeight="1" spans="1:15">
       <c r="A47" s="2" t="s">
         <v>81</v>
       </c>
@@ -3969,7 +3921,6 @@
       <c r="D47" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E47" s="2"/>
       <c r="G47" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -3991,7 +3942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" customHeight="1" spans="1:15">
+    <row r="48" hidden="1" customHeight="1" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>82</v>
       </c>
@@ -4004,7 +3955,6 @@
       <c r="D48" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E48" s="2"/>
       <c r="G48" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4026,7 +3976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" customHeight="1" spans="1:15">
+    <row r="49" hidden="1" customHeight="1" spans="1:15">
       <c r="A49" s="2" t="s">
         <v>83</v>
       </c>
@@ -4039,7 +3989,6 @@
       <c r="D49" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E49" s="2"/>
       <c r="G49" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4061,7 +4010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" customHeight="1" spans="1:15">
+    <row r="50" hidden="1" customHeight="1" spans="1:15">
       <c r="A50" s="2" t="s">
         <v>84</v>
       </c>
@@ -4074,7 +4023,6 @@
       <c r="D50" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E50" s="2"/>
       <c r="G50" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4096,7 +4044,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" customHeight="1" spans="1:15">
+    <row r="51" hidden="1" customHeight="1" spans="1:15">
       <c r="A51" s="2" t="s">
         <v>85</v>
       </c>
@@ -4109,7 +4057,6 @@
       <c r="D51" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E51" s="2"/>
       <c r="G51" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4131,7 +4078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" customHeight="1" spans="1:15">
+    <row r="52" hidden="1" customHeight="1" spans="1:15">
       <c r="A52" s="2" t="s">
         <v>86</v>
       </c>
@@ -4144,7 +4091,6 @@
       <c r="D52" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E52" s="2"/>
       <c r="G52" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4166,7 +4112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" customHeight="1" spans="1:15">
+    <row r="53" hidden="1" customHeight="1" spans="1:15">
       <c r="A53" s="2" t="s">
         <v>87</v>
       </c>
@@ -4179,7 +4125,6 @@
       <c r="D53" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="2"/>
       <c r="G53" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4201,7 +4146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="1:15">
+    <row r="54" hidden="1" customHeight="1" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>88</v>
       </c>
@@ -4214,7 +4159,6 @@
       <c r="D54" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="2"/>
       <c r="G54" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4236,7 +4180,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" customHeight="1" spans="1:15">
+    <row r="55" hidden="1" customHeight="1" spans="1:15">
       <c r="A55" s="2" t="s">
         <v>89</v>
       </c>
@@ -4249,7 +4193,6 @@
       <c r="D55" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E55" s="2"/>
       <c r="G55" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4271,7 +4214,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" customHeight="1" spans="1:15">
+    <row r="56" hidden="1" customHeight="1" spans="1:15">
       <c r="A56" s="2" t="s">
         <v>90</v>
       </c>
@@ -4284,7 +4227,6 @@
       <c r="D56" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E56" s="2"/>
       <c r="G56" s="2" t="str">
         <f t="shared" si="2"/>
         <v>框架</v>
@@ -4306,7 +4248,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" customHeight="1" spans="1:15">
+    <row r="57" hidden="1" customHeight="1" spans="1:15">
       <c r="A57" s="2" t="s">
         <v>91</v>
       </c>
@@ -4319,7 +4261,6 @@
       <c r="D57" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E57" s="2"/>
       <c r="G57" s="2" t="str">
         <f t="shared" si="2"/>
         <v>漆丽华</v>
@@ -4341,7 +4282,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" customHeight="1" spans="1:15">
+    <row r="58" hidden="1" customHeight="1" spans="1:15">
       <c r="A58" s="2" t="s">
         <v>93</v>
       </c>
@@ -4354,7 +4295,6 @@
       <c r="D58" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E58" s="2"/>
       <c r="G58" s="2" t="str">
         <f t="shared" si="2"/>
         <v>林雅清</v>
@@ -4376,7 +4316,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="59" customHeight="1" spans="1:15">
+    <row r="59" hidden="1" customHeight="1" spans="1:15">
       <c r="A59" s="2" t="s">
         <v>95</v>
       </c>
@@ -4389,7 +4329,6 @@
       <c r="D59" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E59" s="2"/>
       <c r="G59" s="2" t="str">
         <f t="shared" si="2"/>
         <v>卢德华</v>
@@ -4411,7 +4350,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" customHeight="1" spans="1:15">
+    <row r="60" hidden="1" customHeight="1" spans="1:15">
       <c r="A60" s="2" t="s">
         <v>97</v>
       </c>
@@ -4424,7 +4363,6 @@
       <c r="D60" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E60" s="2"/>
       <c r="G60" s="2" t="str">
         <f t="shared" si="2"/>
         <v>胡丽萍</v>
@@ -4446,7 +4384,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" customHeight="1" spans="1:15">
+    <row r="61" hidden="1" customHeight="1" spans="1:15">
       <c r="A61" s="2" t="s">
         <v>100</v>
       </c>
@@ -4459,7 +4397,6 @@
       <c r="D61" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E61" s="2"/>
       <c r="G61" s="2" t="str">
         <f t="shared" si="2"/>
         <v>吴苏晗笑</v>
@@ -4481,7 +4418,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" customHeight="1" spans="1:15">
+    <row r="62" hidden="1" customHeight="1" spans="1:15">
       <c r="A62" s="2" t="s">
         <v>103</v>
       </c>
@@ -4494,7 +4431,6 @@
       <c r="D62" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E62" s="2"/>
       <c r="G62" s="2" t="str">
         <f t="shared" si="2"/>
         <v>李任飘</v>
@@ -4516,7 +4452,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" customHeight="1" spans="1:15">
+    <row r="63" hidden="1" customHeight="1" spans="1:15">
       <c r="A63" s="2" t="s">
         <v>107</v>
       </c>
@@ -4529,7 +4465,6 @@
       <c r="D63" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E63" s="2"/>
       <c r="G63" s="2" t="str">
         <f t="shared" si="2"/>
         <v>林菁菁</v>
@@ -4551,7 +4486,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="64" customHeight="1" spans="1:15">
+    <row r="64" hidden="1" customHeight="1" spans="1:15">
       <c r="A64" s="2" t="s">
         <v>109</v>
       </c>
@@ -4564,7 +4499,6 @@
       <c r="D64" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E64" s="2"/>
       <c r="G64" s="2" t="str">
         <f t="shared" si="2"/>
         <v>黄春荣</v>
@@ -4586,7 +4520,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:15">
+    <row r="65" hidden="1" customHeight="1" spans="1:15">
       <c r="A65" s="2" t="s">
         <v>111</v>
       </c>
@@ -4599,7 +4533,6 @@
       <c r="D65" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="2"/>
       <c r="G65" s="2" t="str">
         <f t="shared" si="2"/>
         <v>谭丽</v>
@@ -4621,7 +4554,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:15">
+    <row r="66" hidden="1" customHeight="1" spans="1:15">
       <c r="A66" s="2" t="s">
         <v>114</v>
       </c>
@@ -4634,7 +4567,6 @@
       <c r="D66" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E66" s="2"/>
       <c r="G66" s="2" t="str">
         <f t="shared" si="2"/>
         <v>胡光柱</v>
@@ -4656,7 +4588,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="1:15">
+    <row r="67" hidden="1" customHeight="1" spans="1:15">
       <c r="A67" s="2" t="s">
         <v>116</v>
       </c>
@@ -4669,7 +4601,6 @@
       <c r="D67" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E67" s="2"/>
       <c r="G67" s="2" t="str">
         <f t="shared" ref="G67:G130" si="3">D67</f>
         <v>洪荣堃</v>
@@ -4691,7 +4622,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="1:15">
+    <row r="68" hidden="1" customHeight="1" spans="1:15">
       <c r="A68" s="2" t="s">
         <v>119</v>
       </c>
@@ -4704,7 +4635,6 @@
       <c r="D68" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E68" s="2"/>
       <c r="G68" s="2" t="str">
         <f t="shared" si="3"/>
         <v>洪荣堃</v>
@@ -4726,7 +4656,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:15">
+    <row r="69" hidden="1" customHeight="1" spans="1:15">
       <c r="A69" s="2" t="s">
         <v>120</v>
       </c>
@@ -4739,7 +4669,6 @@
       <c r="D69" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E69" s="2"/>
       <c r="G69" s="2" t="str">
         <f t="shared" si="3"/>
         <v>洪荣堃</v>
@@ -4761,7 +4690,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" customHeight="1" spans="1:15">
+    <row r="70" hidden="1" customHeight="1" spans="1:15">
       <c r="A70" s="2" t="s">
         <v>121</v>
       </c>
@@ -4774,7 +4703,6 @@
       <c r="D70" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E70" s="2"/>
       <c r="G70" s="2" t="str">
         <f t="shared" si="3"/>
         <v>傅素玲</v>
@@ -4796,7 +4724,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" customHeight="1" spans="1:15">
+    <row r="71" hidden="1" customHeight="1" spans="1:15">
       <c r="A71" s="2" t="s">
         <v>124</v>
       </c>
@@ -4809,7 +4737,6 @@
       <c r="D71" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E71" s="2"/>
       <c r="G71" s="2" t="str">
         <f t="shared" si="3"/>
         <v>方丽容</v>
@@ -4831,7 +4758,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="72" customHeight="1" spans="1:15">
+    <row r="72" hidden="1" customHeight="1" spans="1:15">
       <c r="A72" s="2" t="s">
         <v>127</v>
       </c>
@@ -4844,7 +4771,6 @@
       <c r="D72" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E72" s="2"/>
       <c r="G72" s="2" t="str">
         <f t="shared" si="3"/>
         <v>董宝阳</v>
@@ -4866,7 +4792,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" customHeight="1" spans="1:15">
+    <row r="73" hidden="1" customHeight="1" spans="1:15">
       <c r="A73" s="2" t="s">
         <v>129</v>
       </c>
@@ -4879,7 +4805,6 @@
       <c r="D73" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E73" s="2"/>
       <c r="G73" s="2" t="str">
         <f t="shared" si="3"/>
         <v>代玉</v>
@@ -4901,7 +4826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="74" customHeight="1" spans="1:15">
+    <row r="74" hidden="1" customHeight="1" spans="1:15">
       <c r="A74" s="2" t="s">
         <v>131</v>
       </c>
@@ -4914,7 +4839,6 @@
       <c r="D74" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E74" s="2"/>
       <c r="G74" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈婷</v>
@@ -4936,7 +4860,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" customHeight="1" spans="1:15">
+    <row r="75" hidden="1" customHeight="1" spans="1:15">
       <c r="A75" s="2" t="s">
         <v>133</v>
       </c>
@@ -4949,7 +4873,6 @@
       <c r="D75" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E75" s="2"/>
       <c r="G75" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张慧敏</v>
@@ -4971,7 +4894,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="76" customHeight="1" spans="1:15">
+    <row r="76" hidden="1" customHeight="1" spans="1:15">
       <c r="A76" s="2" t="s">
         <v>135</v>
       </c>
@@ -4984,7 +4907,6 @@
       <c r="D76" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E76" s="2"/>
       <c r="G76" s="2" t="str">
         <f t="shared" si="3"/>
         <v>曾清桦</v>
@@ -5006,7 +4928,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="1:15">
+    <row r="77" hidden="1" customHeight="1" spans="1:15">
       <c r="A77" s="2" t="s">
         <v>137</v>
       </c>
@@ -5019,7 +4941,6 @@
       <c r="D77" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="E77" s="2"/>
       <c r="G77" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈美媛</v>
@@ -5041,7 +4962,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="78" customHeight="1" spans="1:15">
+    <row r="78" hidden="1" customHeight="1" spans="1:15">
       <c r="A78" s="2" t="s">
         <v>140</v>
       </c>
@@ -5054,7 +4975,6 @@
       <c r="D78" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E78" s="2"/>
       <c r="G78" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈俊华</v>
@@ -5076,7 +4996,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" customHeight="1" spans="1:15">
+    <row r="79" hidden="1" customHeight="1" spans="1:15">
       <c r="A79" s="2" t="s">
         <v>142</v>
       </c>
@@ -5089,7 +5009,6 @@
       <c r="D79" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E79" s="2"/>
       <c r="G79" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶玲</v>
@@ -5111,7 +5030,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="80" customHeight="1" spans="1:15">
+    <row r="80" hidden="1" customHeight="1" spans="1:15">
       <c r="A80" s="2" t="s">
         <v>145</v>
       </c>
@@ -5124,7 +5043,6 @@
       <c r="D80" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="E80" s="2"/>
       <c r="G80" s="2" t="str">
         <f t="shared" si="3"/>
         <v>宋宇红</v>
@@ -5146,7 +5064,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="1:15">
+    <row r="81" hidden="1" customHeight="1" spans="1:15">
       <c r="A81" s="2" t="s">
         <v>148</v>
       </c>
@@ -5159,7 +5077,6 @@
       <c r="D81" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E81" s="2"/>
       <c r="G81" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林旭芬</v>
@@ -5181,7 +5098,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="1:15">
+    <row r="82" hidden="1" customHeight="1" spans="1:15">
       <c r="A82" s="2" t="s">
         <v>150</v>
       </c>
@@ -5194,7 +5111,6 @@
       <c r="D82" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E82" s="2"/>
       <c r="G82" s="2" t="str">
         <f t="shared" si="3"/>
         <v>王志凤</v>
@@ -5216,7 +5132,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="1:15">
+    <row r="83" hidden="1" customHeight="1" spans="1:15">
       <c r="A83" s="2" t="s">
         <v>152</v>
       </c>
@@ -5229,7 +5145,6 @@
       <c r="D83" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E83" s="2"/>
       <c r="G83" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张致远</v>
@@ -5251,7 +5166,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="1:15">
+    <row r="84" hidden="1" customHeight="1" spans="1:15">
       <c r="A84" s="2" t="s">
         <v>154</v>
       </c>
@@ -5264,7 +5179,6 @@
       <c r="D84" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E84" s="2"/>
       <c r="G84" s="2" t="str">
         <f t="shared" si="3"/>
         <v>吴启建</v>
@@ -5286,7 +5200,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="1:15">
+    <row r="85" hidden="1" customHeight="1" spans="1:15">
       <c r="A85" s="2" t="s">
         <v>156</v>
       </c>
@@ -5299,7 +5213,6 @@
       <c r="D85" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E85" s="2"/>
       <c r="G85" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑晓蓉</v>
@@ -5321,7 +5234,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="1:15">
+    <row r="86" hidden="1" customHeight="1" spans="1:15">
       <c r="A86" s="2" t="s">
         <v>158</v>
       </c>
@@ -5334,7 +5247,6 @@
       <c r="D86" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E86" s="2"/>
       <c r="G86" s="2" t="str">
         <f t="shared" si="3"/>
         <v>胡茜</v>
@@ -5356,7 +5268,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="1:15">
+    <row r="87" hidden="1" customHeight="1" spans="1:15">
       <c r="A87" s="2" t="s">
         <v>161</v>
       </c>
@@ -5369,7 +5281,6 @@
       <c r="D87" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E87" s="2"/>
       <c r="G87" s="2" t="str">
         <f t="shared" si="3"/>
         <v>杜鑫鑫</v>
@@ -5391,7 +5302,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="1:15">
+    <row r="88" hidden="1" customHeight="1" spans="1:15">
       <c r="A88" s="2" t="s">
         <v>163</v>
       </c>
@@ -5404,7 +5315,6 @@
       <c r="D88" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E88" s="2"/>
       <c r="G88" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑色艳</v>
@@ -5426,7 +5336,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="1:15">
+    <row r="89" hidden="1" customHeight="1" spans="1:15">
       <c r="A89" s="2" t="s">
         <v>165</v>
       </c>
@@ -5439,7 +5349,6 @@
       <c r="D89" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E89" s="2"/>
       <c r="G89" s="2" t="str">
         <f t="shared" si="3"/>
         <v>李珍珍</v>
@@ -5461,7 +5370,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="1:15">
+    <row r="90" hidden="1" customHeight="1" spans="1:15">
       <c r="A90" s="2" t="s">
         <v>167</v>
       </c>
@@ -5474,7 +5383,6 @@
       <c r="D90" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E90" s="2"/>
       <c r="G90" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张慧敏</v>
@@ -5496,7 +5404,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="1:15">
+    <row r="91" hidden="1" customHeight="1" spans="1:15">
       <c r="A91" s="2" t="s">
         <v>169</v>
       </c>
@@ -5509,7 +5417,6 @@
       <c r="D91" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E91" s="2"/>
       <c r="G91" s="2" t="str">
         <f t="shared" si="3"/>
         <v>冯乔芳</v>
@@ -5531,7 +5438,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="1:15">
+    <row r="92" hidden="1" customHeight="1" spans="1:15">
       <c r="A92" s="2" t="s">
         <v>172</v>
       </c>
@@ -5544,7 +5451,6 @@
       <c r="D92" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E92" s="2"/>
       <c r="G92" s="2" t="str">
         <f t="shared" si="3"/>
         <v>建站十分</v>
@@ -5566,7 +5472,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="1:15">
+    <row r="93" hidden="1" customHeight="1" spans="1:15">
       <c r="A93" s="2" t="s">
         <v>174</v>
       </c>
@@ -5579,7 +5485,6 @@
       <c r="D93" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E93" s="2"/>
       <c r="G93" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶惠</v>
@@ -5601,7 +5506,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="1:15">
+    <row r="94" hidden="1" customHeight="1" spans="1:15">
       <c r="A94" s="2" t="s">
         <v>176</v>
       </c>
@@ -5614,7 +5519,6 @@
       <c r="D94" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E94" s="2"/>
       <c r="G94" s="2" t="str">
         <f t="shared" si="3"/>
         <v>蓝淑敏</v>
@@ -5636,7 +5540,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="95" customHeight="1" spans="1:15">
+    <row r="95" hidden="1" customHeight="1" spans="1:15">
       <c r="A95" s="2" t="s">
         <v>178</v>
       </c>
@@ -5649,7 +5553,6 @@
       <c r="D95" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E95" s="2"/>
       <c r="G95" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张唯唯</v>
@@ -5671,7 +5574,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:15">
+    <row r="96" hidden="1" customHeight="1" spans="1:15">
       <c r="A96" s="2" t="s">
         <v>180</v>
       </c>
@@ -5684,7 +5587,6 @@
       <c r="D96" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E96" s="2"/>
       <c r="G96" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑秀东</v>
@@ -5706,7 +5608,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:15">
+    <row r="97" hidden="1" customHeight="1" spans="1:15">
       <c r="A97" s="2" t="s">
         <v>182</v>
       </c>
@@ -5719,7 +5621,6 @@
       <c r="D97" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E97" s="2"/>
       <c r="G97" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶晓欢</v>
@@ -5741,7 +5642,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="1:15">
+    <row r="98" hidden="1" customHeight="1" spans="1:15">
       <c r="A98" s="2" t="s">
         <v>184</v>
       </c>
@@ -5754,7 +5655,6 @@
       <c r="D98" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E98" s="2"/>
       <c r="G98" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林华卿</v>
@@ -5776,7 +5676,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="1:15">
+    <row r="99" hidden="1" customHeight="1" spans="1:15">
       <c r="A99" s="2" t="s">
         <v>186</v>
       </c>
@@ -5789,7 +5689,6 @@
       <c r="D99" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E99" s="2"/>
       <c r="G99" s="2" t="str">
         <f t="shared" si="3"/>
         <v>程秋平</v>
@@ -5811,7 +5710,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="1:15">
+    <row r="100" hidden="1" customHeight="1" spans="1:15">
       <c r="A100" s="2" t="s">
         <v>188</v>
       </c>
@@ -5824,7 +5723,6 @@
       <c r="D100" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E100" s="2"/>
       <c r="G100" s="2" t="str">
         <f t="shared" si="3"/>
         <v>刘珏</v>
@@ -5846,7 +5744,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" customHeight="1" spans="1:15">
+    <row r="101" hidden="1" customHeight="1" spans="1:15">
       <c r="A101" s="2" t="s">
         <v>191</v>
       </c>
@@ -5859,7 +5757,6 @@
       <c r="D101" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E101" s="2"/>
       <c r="G101" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林霖</v>
@@ -5881,7 +5778,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" customHeight="1" spans="1:15">
+    <row r="102" hidden="1" customHeight="1" spans="1:15">
       <c r="A102" s="2" t="s">
         <v>193</v>
       </c>
@@ -5894,7 +5791,6 @@
       <c r="D102" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E102" s="2"/>
       <c r="G102" s="2" t="str">
         <f t="shared" si="3"/>
         <v>童莺莺</v>
@@ -5916,7 +5812,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" customHeight="1" spans="1:15">
+    <row r="103" hidden="1" customHeight="1" spans="1:15">
       <c r="A103" s="2" t="s">
         <v>195</v>
       </c>
@@ -5929,7 +5825,6 @@
       <c r="D103" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E103" s="2"/>
       <c r="G103" s="2" t="str">
         <f t="shared" si="3"/>
         <v>徐林萍</v>
@@ -5951,7 +5846,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" customHeight="1" spans="1:15">
+    <row r="104" hidden="1" customHeight="1" spans="1:15">
       <c r="A104" s="2" t="s">
         <v>197</v>
       </c>
@@ -5964,7 +5859,6 @@
       <c r="D104" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E104" s="2"/>
       <c r="G104" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林裕芳</v>
@@ -5986,7 +5880,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="105" customHeight="1" spans="1:15">
+    <row r="105" hidden="1" customHeight="1" spans="1:15">
       <c r="A105" s="2" t="s">
         <v>199</v>
       </c>
@@ -5999,7 +5893,6 @@
       <c r="D105" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E105" s="2"/>
       <c r="G105" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张静</v>
@@ -6021,7 +5914,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" customHeight="1" spans="1:15">
+    <row r="106" hidden="1" customHeight="1" spans="1:15">
       <c r="A106" s="2" t="s">
         <v>201</v>
       </c>
@@ -6034,7 +5927,6 @@
       <c r="D106" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E106" s="2"/>
       <c r="G106" s="2" t="str">
         <f t="shared" si="3"/>
         <v>廖淑云</v>
@@ -6056,7 +5948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="107" customHeight="1" spans="1:15">
+    <row r="107" hidden="1" customHeight="1" spans="1:15">
       <c r="A107" s="2" t="s">
         <v>203</v>
       </c>
@@ -6069,7 +5961,6 @@
       <c r="D107" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E107" s="2"/>
       <c r="G107" s="2" t="str">
         <f t="shared" si="3"/>
         <v>黄迷</v>
@@ -6091,7 +5982,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" customHeight="1" spans="1:15">
+    <row r="108" hidden="1" customHeight="1" spans="1:15">
       <c r="A108" s="2" t="s">
         <v>205</v>
       </c>
@@ -6104,7 +5995,6 @@
       <c r="D108" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E108" s="2"/>
       <c r="G108" s="2" t="str">
         <f t="shared" si="3"/>
         <v>黄明华</v>
@@ -6126,7 +6016,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="109" customHeight="1" spans="1:15">
+    <row r="109" hidden="1" customHeight="1" spans="1:15">
       <c r="A109" s="2" t="s">
         <v>207</v>
       </c>
@@ -6139,7 +6029,6 @@
       <c r="D109" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E109" s="2"/>
       <c r="G109" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑文星</v>
@@ -6161,7 +6050,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="1:15">
+    <row r="110" hidden="1" customHeight="1" spans="1:15">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -6174,7 +6063,6 @@
       <c r="D110" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E110" s="2"/>
       <c r="G110" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑淑敏</v>
@@ -6196,7 +6084,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="111" customHeight="1" spans="1:15">
+    <row r="111" hidden="1" customHeight="1" spans="1:15">
       <c r="A111" s="2" t="s">
         <v>211</v>
       </c>
@@ -6209,7 +6097,6 @@
       <c r="D111" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E111" s="2"/>
       <c r="G111" s="2" t="str">
         <f t="shared" si="3"/>
         <v>曾清桦</v>
@@ -6231,7 +6118,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="112" customHeight="1" spans="1:15">
+    <row r="112" hidden="1" customHeight="1" spans="1:15">
       <c r="A112" s="2" t="s">
         <v>212</v>
       </c>
@@ -6244,7 +6131,6 @@
       <c r="D112" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E112" s="2"/>
       <c r="G112" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈碧云</v>
@@ -6266,7 +6152,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="113" customHeight="1" spans="1:15">
+    <row r="113" hidden="1" customHeight="1" spans="1:15">
       <c r="A113" s="2" t="s">
         <v>214</v>
       </c>
@@ -6279,7 +6165,6 @@
       <c r="D113" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E113" s="2"/>
       <c r="G113" s="2" t="str">
         <f t="shared" si="3"/>
         <v>赖春连</v>
@@ -6301,7 +6186,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="114" customHeight="1" spans="1:15">
+    <row r="114" hidden="1" customHeight="1" spans="1:15">
       <c r="A114" s="2" t="s">
         <v>216</v>
       </c>
@@ -6314,7 +6199,6 @@
       <c r="D114" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E114" s="2"/>
       <c r="G114" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈巧云</v>
@@ -6336,7 +6220,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="115" customHeight="1" spans="1:15">
+    <row r="115" hidden="1" customHeight="1" spans="1:15">
       <c r="A115" s="2" t="s">
         <v>218</v>
       </c>
@@ -6349,7 +6233,6 @@
       <c r="D115" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="E115" s="2"/>
       <c r="G115" s="2" t="str">
         <f t="shared" si="3"/>
         <v>江媚</v>
@@ -6371,7 +6254,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="116" customHeight="1" spans="1:15">
+    <row r="116" hidden="1" customHeight="1" spans="1:15">
       <c r="A116" s="2" t="s">
         <v>220</v>
       </c>
@@ -6384,7 +6267,6 @@
       <c r="D116" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E116" s="2"/>
       <c r="G116" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈丽环</v>
@@ -6406,7 +6288,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="117" customHeight="1" spans="1:15">
+    <row r="117" hidden="1" customHeight="1" spans="1:15">
       <c r="A117" s="2" t="s">
         <v>222</v>
       </c>
@@ -6419,7 +6301,6 @@
       <c r="D117" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E117" s="2"/>
       <c r="G117" s="2" t="str">
         <f t="shared" si="3"/>
         <v>李远红</v>
@@ -6441,7 +6322,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="118" customHeight="1" spans="1:15">
+    <row r="118" hidden="1" customHeight="1" spans="1:15">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -6454,7 +6335,6 @@
       <c r="D118" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E118" s="2"/>
       <c r="G118" s="2" t="str">
         <f t="shared" si="3"/>
         <v>池紫婷</v>
@@ -6476,7 +6356,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="119" customHeight="1" spans="1:15">
+    <row r="119" hidden="1" customHeight="1" spans="1:15">
       <c r="A119" s="2" t="s">
         <v>226</v>
       </c>
@@ -6489,7 +6369,6 @@
       <c r="D119" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E119" s="2"/>
       <c r="G119" s="2" t="str">
         <f t="shared" si="3"/>
         <v>廖淑云</v>
@@ -6511,7 +6390,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="120" customHeight="1" spans="1:15">
+    <row r="120" hidden="1" customHeight="1" spans="1:15">
       <c r="A120" s="2" t="s">
         <v>227</v>
       </c>
@@ -6524,7 +6403,6 @@
       <c r="D120" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E120" s="2"/>
       <c r="G120" s="2" t="str">
         <f t="shared" si="3"/>
         <v>郑秀东</v>
@@ -6546,7 +6424,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="121" customHeight="1" spans="1:15">
+    <row r="121" hidden="1" customHeight="1" spans="1:15">
       <c r="A121" s="2" t="s">
         <v>229</v>
       </c>
@@ -6559,7 +6437,6 @@
       <c r="D121" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E121" s="2"/>
       <c r="G121" s="2" t="str">
         <f t="shared" si="3"/>
         <v>林佳惠</v>
@@ -6581,7 +6458,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="122" customHeight="1" spans="1:15">
+    <row r="122" hidden="1" customHeight="1" spans="1:15">
       <c r="A122" s="2" t="s">
         <v>232</v>
       </c>
@@ -6594,7 +6471,6 @@
       <c r="D122" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E122" s="2"/>
       <c r="G122" s="2" t="str">
         <f t="shared" si="3"/>
         <v>邓玲玲</v>
@@ -6616,7 +6492,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="123" customHeight="1" spans="1:15">
+    <row r="123" hidden="1" customHeight="1" spans="1:15">
       <c r="A123" s="2" t="s">
         <v>234</v>
       </c>
@@ -6629,7 +6505,6 @@
       <c r="D123" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E123" s="2"/>
       <c r="G123" s="2" t="str">
         <f t="shared" si="3"/>
         <v>纪荣裕</v>
@@ -6651,7 +6526,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="124" customHeight="1" spans="1:15">
+    <row r="124" hidden="1" customHeight="1" spans="1:15">
       <c r="A124" s="2" t="s">
         <v>238</v>
       </c>
@@ -6664,7 +6539,6 @@
       <c r="D124" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E124" s="2"/>
       <c r="G124" s="2" t="str">
         <f t="shared" si="3"/>
         <v>吴晓燕</v>
@@ -6686,7 +6560,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="125" customHeight="1" spans="1:15">
+    <row r="125" hidden="1" customHeight="1" spans="1:15">
       <c r="A125" s="2" t="s">
         <v>241</v>
       </c>
@@ -6699,7 +6573,6 @@
       <c r="D125" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E125" s="2"/>
       <c r="G125" s="2" t="str">
         <f t="shared" si="3"/>
         <v>叶姗姗</v>
@@ -6721,7 +6594,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" customHeight="1" spans="1:15">
+    <row r="126" hidden="1" customHeight="1" spans="1:15">
       <c r="A126" s="2" t="s">
         <v>243</v>
       </c>
@@ -6734,7 +6607,6 @@
       <c r="D126" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E126" s="2"/>
       <c r="G126" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈玉云</v>
@@ -6756,7 +6628,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="127" spans="1:15">
+    <row r="127" hidden="1" spans="1:15">
       <c r="A127" s="2" t="s">
         <v>245</v>
       </c>
@@ -6769,7 +6641,6 @@
       <c r="D127" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E127" s="2"/>
       <c r="G127" s="2" t="str">
         <f t="shared" si="3"/>
         <v>方秋燕</v>
@@ -6791,7 +6662,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:15">
+    <row r="128" hidden="1" customHeight="1" spans="1:15">
       <c r="A128" s="2" t="s">
         <v>247</v>
       </c>
@@ -6804,7 +6675,6 @@
       <c r="D128" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E128" s="2"/>
       <c r="G128" s="2" t="str">
         <f t="shared" si="3"/>
         <v>张秀梅</v>
@@ -6826,7 +6696,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="1:15">
+    <row r="129" hidden="1" customHeight="1" spans="1:15">
       <c r="A129" s="2" t="s">
         <v>250</v>
       </c>
@@ -6839,7 +6709,6 @@
       <c r="D129" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E129" s="2"/>
       <c r="G129" s="2" t="str">
         <f t="shared" si="3"/>
         <v>陈鹭霞</v>
@@ -6861,7 +6730,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="1:15">
+    <row r="130" hidden="1" customHeight="1" spans="1:15">
       <c r="A130" s="2" t="s">
         <v>252</v>
       </c>
@@ -6874,7 +6743,6 @@
       <c r="D130" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E130" s="2"/>
       <c r="G130" s="2" t="str">
         <f t="shared" si="3"/>
         <v>汤斐莉</v>
@@ -6896,7 +6764,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="131" customHeight="1" spans="1:15">
+    <row r="131" hidden="1" customHeight="1" spans="1:15">
       <c r="A131" s="2" t="s">
         <v>254</v>
       </c>
@@ -6909,7 +6777,6 @@
       <c r="D131" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E131" s="2"/>
       <c r="G131" s="2" t="str">
         <f t="shared" ref="G131:G194" si="5">D131</f>
         <v>林桂英</v>
@@ -6931,7 +6798,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="1:15">
+    <row r="132" hidden="1" customHeight="1" spans="1:15">
       <c r="A132" s="2" t="s">
         <v>256</v>
       </c>
@@ -6944,7 +6811,6 @@
       <c r="D132" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E132" s="2"/>
       <c r="G132" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王智勇</v>
@@ -6966,7 +6832,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="133" customHeight="1" spans="1:15">
+    <row r="133" hidden="1" customHeight="1" spans="1:15">
       <c r="A133" s="2" t="s">
         <v>258</v>
       </c>
@@ -6979,7 +6845,6 @@
       <c r="D133" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="E133" s="2"/>
       <c r="G133" s="2" t="str">
         <f t="shared" si="5"/>
         <v>梁烨</v>
@@ -7001,7 +6866,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="134" customHeight="1" spans="1:15">
+    <row r="134" hidden="1" customHeight="1" spans="1:15">
       <c r="A134" s="2" t="s">
         <v>260</v>
       </c>
@@ -7014,7 +6879,6 @@
       <c r="D134" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E134" s="2"/>
       <c r="G134" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林志龙</v>
@@ -7036,7 +6900,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="135" customHeight="1" spans="1:15">
+    <row r="135" hidden="1" customHeight="1" spans="1:15">
       <c r="A135" s="2" t="s">
         <v>262</v>
       </c>
@@ -7049,7 +6913,6 @@
       <c r="D135" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E135" s="2"/>
       <c r="G135" s="2" t="str">
         <f t="shared" si="5"/>
         <v>苏晨</v>
@@ -7071,7 +6934,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="136" customHeight="1" spans="1:15">
+    <row r="136" hidden="1" customHeight="1" spans="1:15">
       <c r="A136" s="2" t="s">
         <v>264</v>
       </c>
@@ -7084,7 +6947,6 @@
       <c r="D136" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="E136" s="2"/>
       <c r="G136" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林志龙</v>
@@ -7106,7 +6968,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="137" customHeight="1" spans="1:15">
+    <row r="137" hidden="1" customHeight="1" spans="1:15">
       <c r="A137" s="2" t="s">
         <v>265</v>
       </c>
@@ -7119,7 +6981,6 @@
       <c r="D137" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E137" s="2"/>
       <c r="G137" s="2" t="str">
         <f t="shared" si="5"/>
         <v>纪荣裕</v>
@@ -7141,7 +7002,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="138" customHeight="1" spans="1:15">
+    <row r="138" hidden="1" customHeight="1" spans="1:15">
       <c r="A138" s="2" t="s">
         <v>266</v>
       </c>
@@ -7154,7 +7015,6 @@
       <c r="D138" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E138" s="2"/>
       <c r="G138" s="2" t="str">
         <f t="shared" si="5"/>
         <v>叶彩华</v>
@@ -7176,7 +7036,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="139" customHeight="1" spans="1:15">
+    <row r="139" hidden="1" customHeight="1" spans="1:15">
       <c r="A139" s="2" t="s">
         <v>269</v>
       </c>
@@ -7189,7 +7049,6 @@
       <c r="D139" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="E139" s="2"/>
       <c r="G139" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李华</v>
@@ -7211,7 +7070,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:15">
+    <row r="140" hidden="1" customHeight="1" spans="1:15">
       <c r="A140" s="2" t="s">
         <v>272</v>
       </c>
@@ -7224,7 +7083,6 @@
       <c r="D140" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="E140" s="2"/>
       <c r="G140" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王丽真</v>
@@ -7246,7 +7104,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:15">
+    <row r="141" hidden="1" customHeight="1" spans="1:15">
       <c r="A141" s="2" t="s">
         <v>274</v>
       </c>
@@ -7259,7 +7117,6 @@
       <c r="D141" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E141" s="2"/>
       <c r="G141" s="2" t="str">
         <f t="shared" si="5"/>
         <v>许少鸣</v>
@@ -7281,7 +7138,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" customHeight="1" spans="1:15">
+    <row r="142" hidden="1" customHeight="1" spans="1:15">
       <c r="A142" s="2" t="s">
         <v>276</v>
       </c>
@@ -7294,7 +7151,6 @@
       <c r="D142" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E142" s="2"/>
       <c r="G142" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王真珍</v>
@@ -7316,7 +7172,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="143" customHeight="1" spans="1:15">
+    <row r="143" hidden="1" customHeight="1" spans="1:15">
       <c r="A143" s="2" t="s">
         <v>278</v>
       </c>
@@ -7329,7 +7185,6 @@
       <c r="D143" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E143" s="2"/>
       <c r="G143" s="2" t="str">
         <f t="shared" si="5"/>
         <v>徐灵钰</v>
@@ -7351,7 +7206,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:15">
+    <row r="144" hidden="1" customHeight="1" spans="1:15">
       <c r="A144" s="2" t="s">
         <v>280</v>
       </c>
@@ -7364,7 +7219,6 @@
       <c r="D144" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E144" s="2"/>
       <c r="G144" s="2" t="str">
         <f t="shared" si="5"/>
         <v>游瑞凤</v>
@@ -7386,7 +7240,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:15">
+    <row r="145" hidden="1" customHeight="1" spans="1:15">
       <c r="A145" s="2" t="s">
         <v>282</v>
       </c>
@@ -7399,7 +7253,6 @@
       <c r="D145" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E145" s="2"/>
       <c r="G145" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李丽红</v>
@@ -7421,7 +7274,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="1:15">
+    <row r="146" hidden="1" customHeight="1" spans="1:15">
       <c r="A146" s="2" t="s">
         <v>284</v>
       </c>
@@ -7434,7 +7287,6 @@
       <c r="D146" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E146" s="2"/>
       <c r="G146" s="2" t="str">
         <f t="shared" si="5"/>
         <v>胡艺红</v>
@@ -7456,7 +7308,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="1:15">
+    <row r="147" hidden="1" customHeight="1" spans="1:15">
       <c r="A147" s="2" t="s">
         <v>286</v>
       </c>
@@ -7469,7 +7321,6 @@
       <c r="D147" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E147" s="2"/>
       <c r="G147" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7491,7 +7342,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:15">
+    <row r="148" hidden="1" customHeight="1" spans="1:15">
       <c r="A148" s="2" t="s">
         <v>289</v>
       </c>
@@ -7504,7 +7355,6 @@
       <c r="D148" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E148" s="2"/>
       <c r="G148" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7526,7 +7376,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="1:15">
+    <row r="149" hidden="1" customHeight="1" spans="1:15">
       <c r="A149" s="2" t="s">
         <v>290</v>
       </c>
@@ -7539,7 +7389,6 @@
       <c r="D149" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E149" s="2"/>
       <c r="G149" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾达威</v>
@@ -7561,7 +7410,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="1:15">
+    <row r="150" hidden="1" customHeight="1" spans="1:15">
       <c r="A150" s="2" t="s">
         <v>291</v>
       </c>
@@ -7574,7 +7423,6 @@
       <c r="D150" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="E150" s="2"/>
       <c r="G150" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林小凤</v>
@@ -7596,7 +7444,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:15">
+    <row r="151" hidden="1" customHeight="1" spans="1:15">
       <c r="A151" s="2" t="s">
         <v>293</v>
       </c>
@@ -7609,7 +7457,6 @@
       <c r="D151" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="E151" s="2"/>
       <c r="G151" s="2" t="str">
         <f t="shared" si="5"/>
         <v>曾雅芳</v>
@@ -7631,7 +7478,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:15">
+    <row r="152" hidden="1" customHeight="1" spans="1:15">
       <c r="A152" s="2" t="s">
         <v>295</v>
       </c>
@@ -7644,7 +7491,6 @@
       <c r="D152" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E152" s="2"/>
       <c r="G152" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林秋琼</v>
@@ -7666,7 +7512,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:15">
+    <row r="153" hidden="1" customHeight="1" spans="1:15">
       <c r="A153" s="2" t="s">
         <v>297</v>
       </c>
@@ -7679,7 +7525,6 @@
       <c r="D153" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="E153" s="2"/>
       <c r="G153" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄锴</v>
@@ -7701,7 +7546,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:15">
+    <row r="154" hidden="1" customHeight="1" spans="1:15">
       <c r="A154" s="2" t="s">
         <v>299</v>
       </c>
@@ -7714,7 +7559,6 @@
       <c r="D154" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="E154" s="2"/>
       <c r="G154" s="2" t="str">
         <f t="shared" si="5"/>
         <v>张婷婷</v>
@@ -7736,7 +7580,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="1:15">
+    <row r="155" hidden="1" customHeight="1" spans="1:15">
       <c r="A155" s="2" t="s">
         <v>301</v>
       </c>
@@ -7749,7 +7593,6 @@
       <c r="D155" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E155" s="2"/>
       <c r="G155" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄凤苗</v>
@@ -7771,7 +7614,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="1:15">
+    <row r="156" hidden="1" customHeight="1" spans="1:15">
       <c r="A156" s="2" t="s">
         <v>303</v>
       </c>
@@ -7784,7 +7627,6 @@
       <c r="D156" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="E156" s="2"/>
       <c r="G156" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴燕红</v>
@@ -7806,7 +7648,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="1:15">
+    <row r="157" hidden="1" customHeight="1" spans="1:15">
       <c r="A157" s="2" t="s">
         <v>305</v>
       </c>
@@ -7819,7 +7661,6 @@
       <c r="D157" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E157" s="2"/>
       <c r="G157" s="2" t="str">
         <f t="shared" si="5"/>
         <v>王凤钦</v>
@@ -7841,7 +7682,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:15">
+    <row r="158" hidden="1" customHeight="1" spans="1:15">
       <c r="A158" s="2" t="s">
         <v>307</v>
       </c>
@@ -7854,7 +7695,6 @@
       <c r="D158" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E158" s="2"/>
       <c r="G158" s="2" t="str">
         <f t="shared" si="5"/>
         <v>傅佳玲</v>
@@ -7876,7 +7716,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:15">
+    <row r="159" hidden="1" customHeight="1" spans="1:15">
       <c r="A159" s="2" t="s">
         <v>309</v>
       </c>
@@ -7889,7 +7729,6 @@
       <c r="D159" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="E159" s="2"/>
       <c r="G159" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴敏凤</v>
@@ -7911,7 +7750,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="1:15">
+    <row r="160" hidden="1" customHeight="1" spans="1:15">
       <c r="A160" s="2" t="s">
         <v>311</v>
       </c>
@@ -7924,7 +7763,6 @@
       <c r="D160" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E160" s="2"/>
       <c r="G160" s="2" t="str">
         <f t="shared" si="5"/>
         <v>张滟莲</v>
@@ -7946,7 +7784,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="1:15">
+    <row r="161" hidden="1" customHeight="1" spans="1:15">
       <c r="A161" s="2" t="s">
         <v>313</v>
       </c>
@@ -7959,7 +7797,6 @@
       <c r="D161" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="E161" s="2"/>
       <c r="G161" s="2" t="str">
         <f t="shared" si="5"/>
         <v>邱彬彬</v>
@@ -7981,7 +7818,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="1:15">
+    <row r="162" hidden="1" customHeight="1" spans="1:15">
       <c r="A162" s="2" t="s">
         <v>315</v>
       </c>
@@ -7994,7 +7831,6 @@
       <c r="D162" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E162" s="2"/>
       <c r="G162" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈浩</v>
@@ -8016,7 +7852,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="1:15">
+    <row r="163" hidden="1" customHeight="1" spans="1:15">
       <c r="A163" s="2" t="s">
         <v>317</v>
       </c>
@@ -8029,7 +7865,6 @@
       <c r="D163" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="E163" s="2"/>
       <c r="G163" s="2" t="str">
         <f t="shared" si="5"/>
         <v>施桂兰</v>
@@ -8051,7 +7886,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="1:15">
+    <row r="164" hidden="1" customHeight="1" spans="1:15">
       <c r="A164" s="2" t="s">
         <v>319</v>
       </c>
@@ -8064,7 +7899,6 @@
       <c r="D164" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="E164" s="2"/>
       <c r="G164" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈燕秀</v>
@@ -8086,7 +7920,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="165" customHeight="1" spans="1:15">
+    <row r="165" hidden="1" customHeight="1" spans="1:15">
       <c r="A165" s="2" t="s">
         <v>321</v>
       </c>
@@ -8099,7 +7933,6 @@
       <c r="D165" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E165" s="2"/>
       <c r="G165" s="2" t="str">
         <f t="shared" si="5"/>
         <v>吴清玉</v>
@@ -8121,7 +7954,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="166" customHeight="1" spans="1:15">
+    <row r="166" hidden="1" customHeight="1" spans="1:15">
       <c r="A166" s="2" t="s">
         <v>323</v>
       </c>
@@ -8134,7 +7967,6 @@
       <c r="D166" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E166" s="2"/>
       <c r="G166" s="2" t="str">
         <f t="shared" si="5"/>
         <v>游惠卿</v>
@@ -8156,7 +7988,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="1:15">
+    <row r="167" hidden="1" customHeight="1" spans="1:15">
       <c r="A167" s="2" t="s">
         <v>325</v>
       </c>
@@ -8169,7 +8001,6 @@
       <c r="D167" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E167" s="2"/>
       <c r="G167" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林聪义</v>
@@ -8191,7 +8022,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="1:15">
+    <row r="168" hidden="1" customHeight="1" spans="1:15">
       <c r="A168" s="2" t="s">
         <v>327</v>
       </c>
@@ -8204,7 +8035,6 @@
       <c r="D168" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="E168" s="2"/>
       <c r="G168" s="2" t="str">
         <f t="shared" si="5"/>
         <v>黄淑玲</v>
@@ -8226,7 +8056,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="1:15">
+    <row r="169" hidden="1" customHeight="1" spans="1:15">
       <c r="A169" s="2" t="s">
         <v>329</v>
       </c>
@@ -8239,7 +8069,6 @@
       <c r="D169" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="E169" s="2"/>
       <c r="G169" s="2" t="str">
         <f t="shared" si="5"/>
         <v>连海珠</v>
@@ -8261,7 +8090,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="170" customHeight="1" spans="1:15">
+    <row r="170" hidden="1" customHeight="1" spans="1:15">
       <c r="A170" s="2" t="s">
         <v>331</v>
       </c>
@@ -8274,7 +8103,6 @@
       <c r="D170" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E170" s="2"/>
       <c r="G170" s="2" t="str">
         <f t="shared" si="5"/>
         <v>洪宏</v>
@@ -8296,7 +8124,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="1:15">
+    <row r="171" hidden="1" customHeight="1" spans="1:15">
       <c r="A171" s="2" t="s">
         <v>333</v>
       </c>
@@ -8309,7 +8137,6 @@
       <c r="D171" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E171" s="2"/>
       <c r="G171" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈秋菊</v>
@@ -8331,7 +8158,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="172" customHeight="1" spans="1:15">
+    <row r="172" hidden="1" customHeight="1" spans="1:15">
       <c r="A172" s="2" t="s">
         <v>335</v>
       </c>
@@ -8344,7 +8171,6 @@
       <c r="D172" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="E172" s="2"/>
       <c r="G172" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林惠兰</v>
@@ -8366,7 +8192,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" customHeight="1" spans="1:15">
+    <row r="173" hidden="1" customHeight="1" spans="1:15">
       <c r="A173" s="2" t="s">
         <v>339</v>
       </c>
@@ -8379,7 +8205,6 @@
       <c r="D173" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="E173" s="2"/>
       <c r="G173" s="2" t="str">
         <f t="shared" si="5"/>
         <v>丁洁</v>
@@ -8401,7 +8226,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="1:15">
+    <row r="174" hidden="1" customHeight="1" spans="1:15">
       <c r="A174" s="2" t="s">
         <v>341</v>
       </c>
@@ -8414,7 +8239,6 @@
       <c r="D174" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E174" s="2"/>
       <c r="G174" s="2" t="str">
         <f t="shared" si="5"/>
         <v>夏皖鹭</v>
@@ -8436,7 +8260,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="1:15">
+    <row r="175" hidden="1" customHeight="1" spans="1:15">
       <c r="A175" s="2" t="s">
         <v>343</v>
       </c>
@@ -8449,7 +8273,6 @@
       <c r="D175" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E175" s="2"/>
       <c r="G175" s="2" t="str">
         <f t="shared" si="5"/>
         <v>无</v>
@@ -8471,7 +8294,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="1:15">
+    <row r="176" hidden="1" customHeight="1" spans="1:15">
       <c r="A176" s="2" t="s">
         <v>345</v>
       </c>
@@ -8484,7 +8307,6 @@
       <c r="D176" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="E176" s="2"/>
       <c r="G176" s="2" t="str">
         <f t="shared" si="5"/>
         <v>行发基木鱼</v>
@@ -8506,7 +8328,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="177" customHeight="1" spans="1:15">
+    <row r="177" hidden="1" customHeight="1" spans="1:15">
       <c r="A177" s="2" t="s">
         <v>347</v>
       </c>
@@ -8519,7 +8341,6 @@
       <c r="D177" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E177" s="2"/>
       <c r="G177" s="2" t="str">
         <f t="shared" si="5"/>
         <v>朱书兰</v>
@@ -8541,7 +8362,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="178" customHeight="1" spans="1:15">
+    <row r="178" hidden="1" customHeight="1" spans="1:15">
       <c r="A178" s="2" t="s">
         <v>349</v>
       </c>
@@ -8554,7 +8375,6 @@
       <c r="D178" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="E178" s="2"/>
       <c r="G178" s="2" t="str">
         <f t="shared" si="5"/>
         <v>萧月梅</v>
@@ -8576,7 +8396,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="179" customHeight="1" spans="1:15">
+    <row r="179" hidden="1" customHeight="1" spans="1:15">
       <c r="A179" s="2" t="s">
         <v>352</v>
       </c>
@@ -8589,7 +8409,6 @@
       <c r="D179" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E179" s="2"/>
       <c r="G179" s="2" t="str">
         <f t="shared" si="5"/>
         <v>胡晓惠</v>
@@ -8611,7 +8430,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180" customHeight="1" spans="1:15">
+    <row r="180" hidden="1" customHeight="1" spans="1:15">
       <c r="A180" s="2" t="s">
         <v>354</v>
       </c>
@@ -8624,7 +8443,6 @@
       <c r="D180" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E180" s="2"/>
       <c r="G180" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林丹丹</v>
@@ -8646,7 +8464,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="181" customHeight="1" spans="1:15">
+    <row r="181" hidden="1" customHeight="1" spans="1:15">
       <c r="A181" s="2" t="s">
         <v>356</v>
       </c>
@@ -8659,7 +8477,6 @@
       <c r="D181" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E181" s="2"/>
       <c r="G181" s="2" t="str">
         <f t="shared" si="5"/>
         <v>姚美玲</v>
@@ -8681,7 +8498,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="182" customHeight="1" spans="1:15">
+    <row r="182" hidden="1" customHeight="1" spans="1:15">
       <c r="A182" s="2" t="s">
         <v>358</v>
       </c>
@@ -8694,7 +8511,6 @@
       <c r="D182" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="E182" s="2"/>
       <c r="G182" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈雪梅</v>
@@ -8716,7 +8532,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="183" customHeight="1" spans="1:15">
+    <row r="183" hidden="1" customHeight="1" spans="1:15">
       <c r="A183" s="2" t="s">
         <v>360</v>
       </c>
@@ -8729,7 +8545,6 @@
       <c r="D183" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="E183" s="2"/>
       <c r="G183" s="2" t="str">
         <f t="shared" si="5"/>
         <v>詹大钧</v>
@@ -8751,7 +8566,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="184" customHeight="1" spans="1:15">
+    <row r="184" hidden="1" customHeight="1" spans="1:15">
       <c r="A184" s="2" t="s">
         <v>362</v>
       </c>
@@ -8764,7 +8579,6 @@
       <c r="D184" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="E184" s="2"/>
       <c r="G184" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郑博萱</v>
@@ -8786,7 +8600,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="185" customHeight="1" spans="1:15">
+    <row r="185" hidden="1" customHeight="1" spans="1:15">
       <c r="A185" s="2" t="s">
         <v>364</v>
       </c>
@@ -8799,7 +8613,6 @@
       <c r="D185" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E185" s="2"/>
       <c r="G185" s="2" t="str">
         <f t="shared" si="5"/>
         <v>朱丽珊</v>
@@ -8821,7 +8634,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="186" customHeight="1" spans="1:15">
+    <row r="186" hidden="1" customHeight="1" spans="1:15">
       <c r="A186" s="2" t="s">
         <v>366</v>
       </c>
@@ -8834,7 +8647,6 @@
       <c r="D186" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E186" s="2"/>
       <c r="G186" s="2" t="str">
         <f t="shared" si="5"/>
         <v>葛晓丹</v>
@@ -8856,7 +8668,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="187" customHeight="1" spans="1:15">
+    <row r="187" hidden="1" customHeight="1" spans="1:15">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -8864,12 +8676,11 @@
         <v>10</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="E187" s="2"/>
       <c r="G187" s="2" t="str">
         <f t="shared" si="5"/>
         <v>李丹凤</v>
@@ -8891,7 +8702,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="188" customHeight="1" spans="1:15">
+    <row r="188" hidden="1" customHeight="1" spans="1:15">
       <c r="A188" s="2" t="s">
         <v>370</v>
       </c>
@@ -8904,7 +8715,6 @@
       <c r="D188" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="E188" s="2"/>
       <c r="G188" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郭琳娟</v>
@@ -8926,7 +8736,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="189" customHeight="1" spans="1:15">
+    <row r="189" hidden="1" customHeight="1" spans="1:15">
       <c r="A189" s="2" t="s">
         <v>372</v>
       </c>
@@ -8939,7 +8749,6 @@
       <c r="D189" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E189" s="2"/>
       <c r="G189" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈金锐</v>
@@ -8961,7 +8770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" customHeight="1" spans="1:15">
+    <row r="190" hidden="1" customHeight="1" spans="1:15">
       <c r="A190" s="2" t="s">
         <v>373</v>
       </c>
@@ -8974,7 +8783,6 @@
       <c r="D190" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E190" s="2"/>
       <c r="G190" s="2" t="str">
         <f t="shared" si="5"/>
         <v>杨晶晶</v>
@@ -8996,7 +8804,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" customHeight="1" spans="1:15">
+    <row r="191" hidden="1" customHeight="1" spans="1:15">
       <c r="A191" s="2" t="s">
         <v>375</v>
       </c>
@@ -9009,7 +8817,6 @@
       <c r="D191" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E191" s="2"/>
       <c r="G191" s="2" t="str">
         <f t="shared" si="5"/>
         <v>陈婷</v>
@@ -9031,7 +8838,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="192" customHeight="1" spans="1:15">
+    <row r="192" hidden="1" customHeight="1" spans="1:15">
       <c r="A192" s="2" t="s">
         <v>376</v>
       </c>
@@ -9044,7 +8851,6 @@
       <c r="D192" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E192" s="2"/>
       <c r="G192" s="2" t="str">
         <f t="shared" si="5"/>
         <v>林洁</v>
@@ -9066,7 +8872,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" customHeight="1" spans="1:15">
+    <row r="193" hidden="1" customHeight="1" spans="1:15">
       <c r="A193" s="2" t="s">
         <v>379</v>
       </c>
@@ -9079,7 +8885,6 @@
       <c r="D193" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E193" s="2"/>
       <c r="G193" s="2" t="str">
         <f t="shared" si="5"/>
         <v>郑燕森</v>
@@ -9101,7 +8906,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" customHeight="1" spans="1:15">
+    <row r="194" hidden="1" customHeight="1" spans="1:15">
       <c r="A194" s="2" t="s">
         <v>381</v>
       </c>
@@ -9114,7 +8919,6 @@
       <c r="D194" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E194" s="2"/>
       <c r="G194" s="2" t="str">
         <f t="shared" si="5"/>
         <v>许珊珊</v>
@@ -9136,7 +8940,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="195" customHeight="1" spans="1:15">
+    <row r="195" hidden="1" customHeight="1" spans="1:15">
       <c r="A195" s="2" t="s">
         <v>384</v>
       </c>
@@ -9149,9 +8953,8 @@
       <c r="D195" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E195" s="2"/>
       <c r="G195" s="2" t="str">
-        <f t="shared" ref="G195:G230" si="7">D195</f>
+        <f t="shared" ref="G195:G231" si="7">D195</f>
         <v>框架</v>
       </c>
       <c r="H195" s="2" t="str">
@@ -9171,7 +8974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" customHeight="1" spans="1:15">
+    <row r="196" hidden="1" customHeight="1" spans="1:15">
       <c r="A196" s="2" t="s">
         <v>385</v>
       </c>
@@ -9184,7 +8987,6 @@
       <c r="D196" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E196" s="2"/>
       <c r="G196" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9206,7 +9008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" customHeight="1" spans="1:15">
+    <row r="197" hidden="1" customHeight="1" spans="1:15">
       <c r="A197" s="2" t="s">
         <v>386</v>
       </c>
@@ -9219,7 +9021,6 @@
       <c r="D197" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E197" s="2"/>
       <c r="G197" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9241,7 +9042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" customHeight="1" spans="1:15">
+    <row r="198" hidden="1" customHeight="1" spans="1:15">
       <c r="A198" s="2" t="s">
         <v>387</v>
       </c>
@@ -9254,7 +9055,6 @@
       <c r="D198" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E198" s="2"/>
       <c r="G198" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9276,7 +9076,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" customHeight="1" spans="1:15">
+    <row r="199" hidden="1" customHeight="1" spans="1:15">
       <c r="A199" s="2" t="s">
         <v>388</v>
       </c>
@@ -9289,7 +9089,6 @@
       <c r="D199" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E199" s="2"/>
       <c r="G199" s="2" t="str">
         <f t="shared" si="7"/>
         <v>庄艺娜</v>
@@ -9311,7 +9110,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="200" customHeight="1" spans="1:15">
+    <row r="200" hidden="1" customHeight="1" spans="1:15">
       <c r="A200" s="2" t="s">
         <v>391</v>
       </c>
@@ -9324,7 +9123,6 @@
       <c r="D200" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E200" s="2"/>
       <c r="G200" s="2" t="str">
         <f t="shared" si="7"/>
         <v>谢龙辉</v>
@@ -9346,7 +9144,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="201" customHeight="1" spans="1:15">
+    <row r="201" hidden="1" customHeight="1" spans="1:15">
       <c r="A201" s="2" t="s">
         <v>393</v>
       </c>
@@ -9359,7 +9157,6 @@
       <c r="D201" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E201" s="2"/>
       <c r="G201" s="2" t="str">
         <f t="shared" si="7"/>
         <v>无</v>
@@ -9381,7 +9178,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="202" customHeight="1" spans="1:15">
+    <row r="202" hidden="1" customHeight="1" spans="1:15">
       <c r="A202" s="2" t="s">
         <v>394</v>
       </c>
@@ -9394,7 +9191,6 @@
       <c r="D202" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="E202" s="2"/>
       <c r="G202" s="2" t="str">
         <f t="shared" si="7"/>
         <v>无</v>
@@ -9416,7 +9212,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="203" customHeight="1" spans="1:15">
+    <row r="203" hidden="1" customHeight="1" spans="1:15">
       <c r="A203" s="2" t="s">
         <v>395</v>
       </c>
@@ -9429,7 +9225,6 @@
       <c r="D203" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E203" s="2"/>
       <c r="G203" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9451,7 +9246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" customHeight="1" spans="1:15">
+    <row r="204" hidden="1" customHeight="1" spans="1:15">
       <c r="A204" s="2" t="s">
         <v>396</v>
       </c>
@@ -9464,7 +9259,6 @@
       <c r="D204" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E204" s="2"/>
       <c r="G204" s="2" t="str">
         <f t="shared" si="7"/>
         <v>王达斌</v>
@@ -9486,7 +9280,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="205" customHeight="1" spans="1:15">
+    <row r="205" hidden="1" customHeight="1" spans="1:15">
       <c r="A205" s="2" t="s">
         <v>398</v>
       </c>
@@ -9499,7 +9293,6 @@
       <c r="D205" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E205" s="2"/>
       <c r="G205" s="2" t="str">
         <f t="shared" si="7"/>
         <v>苏巧萍</v>
@@ -9521,7 +9314,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="206" customHeight="1" spans="1:15">
+    <row r="206" hidden="1" customHeight="1" spans="1:15">
       <c r="A206" s="2" t="s">
         <v>400</v>
       </c>
@@ -9534,7 +9327,6 @@
       <c r="D206" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E206" s="2"/>
       <c r="G206" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -9556,7 +9348,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" customHeight="1" spans="1:15">
+    <row r="207" hidden="1" customHeight="1" spans="1:15">
       <c r="A207" s="2" t="s">
         <v>401</v>
       </c>
@@ -9569,7 +9361,6 @@
       <c r="D207" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E207" s="2"/>
       <c r="G207" s="2" t="str">
         <f t="shared" si="7"/>
         <v>黄春荣</v>
@@ -9591,7 +9382,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="208" customHeight="1" spans="1:15">
+    <row r="208" hidden="1" customHeight="1" spans="1:15">
       <c r="A208" s="2" t="s">
         <v>402</v>
       </c>
@@ -9604,7 +9395,6 @@
       <c r="D208" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E208" s="2"/>
       <c r="G208" s="2" t="str">
         <f t="shared" si="7"/>
         <v>茅巧丽</v>
@@ -9626,7 +9416,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="209" customHeight="1" spans="1:15">
+    <row r="209" hidden="1" customHeight="1" spans="1:15">
       <c r="A209" s="2" t="s">
         <v>404</v>
       </c>
@@ -9639,7 +9429,6 @@
       <c r="D209" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="E209" s="2"/>
       <c r="G209" s="2" t="str">
         <f t="shared" si="7"/>
         <v>林婷</v>
@@ -9661,7 +9450,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="210" customHeight="1" spans="1:15">
+    <row r="210" hidden="1" customHeight="1" spans="1:15">
       <c r="A210" s="2" t="s">
         <v>406</v>
       </c>
@@ -9674,7 +9463,6 @@
       <c r="D210" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E210" s="2"/>
       <c r="G210" s="2" t="str">
         <f t="shared" si="7"/>
         <v>李佳敏</v>
@@ -9696,7 +9484,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="211" customHeight="1" spans="1:15">
+    <row r="211" hidden="1" customHeight="1" spans="1:15">
       <c r="A211" s="2" t="s">
         <v>408</v>
       </c>
@@ -9709,7 +9497,6 @@
       <c r="D211" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="E211" s="2"/>
       <c r="G211" s="2" t="str">
         <f t="shared" si="7"/>
         <v>郑博</v>
@@ -9731,7 +9518,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="212" customHeight="1" spans="1:15">
+    <row r="212" hidden="1" customHeight="1" spans="1:15">
       <c r="A212" s="2" t="s">
         <v>410</v>
       </c>
@@ -9744,7 +9531,6 @@
       <c r="D212" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E212" s="2"/>
       <c r="G212" s="2" t="str">
         <f t="shared" si="7"/>
         <v>郭雅玲</v>
@@ -9766,7 +9552,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="213" customHeight="1" spans="1:15">
+    <row r="213" hidden="1" customHeight="1" spans="1:15">
       <c r="A213" s="2" t="s">
         <v>412</v>
       </c>
@@ -9779,7 +9565,6 @@
       <c r="D213" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E213" s="2"/>
       <c r="G213" s="2" t="str">
         <f t="shared" si="7"/>
         <v>张燕红</v>
@@ -9801,7 +9586,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="214" customHeight="1" spans="1:15">
+    <row r="214" hidden="1" customHeight="1" spans="1:15">
       <c r="A214" s="2" t="s">
         <v>414</v>
       </c>
@@ -9814,7 +9599,6 @@
       <c r="D214" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E214" s="2"/>
       <c r="G214" s="2" t="str">
         <f t="shared" si="7"/>
         <v>周莉莉</v>
@@ -9846,13 +9630,12 @@
       <c r="C215" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D215" t="s">
-        <v>417</v>
-      </c>
-      <c r="E215" s="2"/>
+      <c r="D215" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="G215" s="2" t="str">
         <f t="shared" si="7"/>
-        <v>何清霞</v>
+        <v>李丹凤</v>
       </c>
       <c r="H215" s="2" t="str">
         <f t="shared" si="8"/>
@@ -9868,12 +9651,12 @@
         <v>230</v>
       </c>
       <c r="O215" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="216" hidden="1" customHeight="1" spans="1:15">
+      <c r="A216" s="2" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="216" customHeight="1" spans="1:15">
-      <c r="A216" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>10</v>
@@ -9884,7 +9667,6 @@
       <c r="D216" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E216" s="2"/>
       <c r="G216" s="2" t="str">
         <f t="shared" si="7"/>
         <v>陈沅</v>
@@ -9894,7 +9676,7 @@
         <v>大客部门</v>
       </c>
       <c r="L216" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M216" s="2" t="s">
         <v>10</v>
@@ -9906,9 +9688,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" customHeight="1" spans="1:15">
+    <row r="217" hidden="1" customHeight="1" spans="1:15">
       <c r="A217" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>235</v>
@@ -9919,7 +9701,6 @@
       <c r="D217" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="E217" s="2"/>
       <c r="G217" s="2" t="str">
         <f t="shared" si="7"/>
         <v>纪荣裕</v>
@@ -9929,7 +9710,7 @@
         <v>失效挽救部</v>
       </c>
       <c r="L217" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M217" s="2" t="s">
         <v>235</v>
@@ -9941,9 +9722,9 @@
         <v>237</v>
       </c>
     </row>
-    <row r="218" customHeight="1" spans="1:15">
+    <row r="218" hidden="1" customHeight="1" spans="1:15">
       <c r="A218" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>235</v>
@@ -9954,7 +9735,6 @@
       <c r="D218" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E218" s="2"/>
       <c r="G218" s="2" t="str">
         <f t="shared" si="7"/>
         <v>苏晨</v>
@@ -9964,7 +9744,7 @@
         <v>失效挽救部</v>
       </c>
       <c r="L218" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M218" s="2" t="s">
         <v>235</v>
@@ -9976,12 +9756,12 @@
         <v>263</v>
       </c>
     </row>
-    <row r="219" customHeight="1" spans="1:15">
+    <row r="219" hidden="1" customHeight="1" spans="1:15">
       <c r="A219" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>382</v>
@@ -9989,7 +9769,6 @@
       <c r="D219" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="E219" s="2"/>
       <c r="G219" s="2" t="str">
         <f t="shared" si="7"/>
         <v>谢龙辉</v>
@@ -9999,10 +9778,10 @@
         <v>泉州KOL部门</v>
       </c>
       <c r="L219" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="M219" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="M219" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="N219" s="2" t="s">
         <v>382</v>
@@ -10011,12 +9790,12 @@
         <v>392</v>
       </c>
     </row>
-    <row r="220" customHeight="1" spans="1:15">
+    <row r="220" hidden="1" customHeight="1" spans="1:15">
       <c r="A220" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>382</v>
@@ -10024,7 +9803,6 @@
       <c r="D220" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E220" s="2"/>
       <c r="G220" s="2" t="str">
         <f t="shared" si="7"/>
         <v>许珊珊</v>
@@ -10034,10 +9812,10 @@
         <v>泉州KOL部门</v>
       </c>
       <c r="L220" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M220" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N220" s="2" t="s">
         <v>382</v>
@@ -10046,9 +9824,9 @@
         <v>383</v>
       </c>
     </row>
-    <row r="221" customHeight="1" spans="1:15">
+    <row r="221" hidden="1" customHeight="1" spans="1:15">
       <c r="A221" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>10</v>
@@ -10059,7 +9837,6 @@
       <c r="D221" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="E221" s="2"/>
       <c r="G221" s="2" t="str">
         <f t="shared" si="7"/>
         <v>林洁</v>
@@ -10069,7 +9846,7 @@
         <v>大客部门</v>
       </c>
       <c r="L221" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M221" s="2" t="s">
         <v>10</v>
@@ -10081,20 +9858,19 @@
         <v>378</v>
       </c>
     </row>
-    <row r="222" customHeight="1" spans="1:15">
+    <row r="222" hidden="1" customHeight="1" spans="1:15">
       <c r="A222" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="E222" s="2"/>
       <c r="G222" s="2" t="str">
         <f t="shared" si="7"/>
         <v>杨晶晶</v>
@@ -10104,21 +9880,21 @@
         <v>大客部门</v>
       </c>
       <c r="L222" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="N222" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O222" s="2" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="223" customHeight="1" spans="1:15">
+    <row r="223" hidden="1" customHeight="1" spans="1:15">
       <c r="A223" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>14</v>
@@ -10129,7 +9905,6 @@
       <c r="D223" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E223" s="2"/>
       <c r="G223" s="2" t="str">
         <f t="shared" si="7"/>
         <v>叶玲</v>
@@ -10139,7 +9914,7 @@
         <v>维护部门</v>
       </c>
       <c r="L223" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M223" s="2" t="s">
         <v>14</v>
@@ -10151,9 +9926,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="224" customHeight="1" spans="1:15">
+    <row r="224" hidden="1" customHeight="1" spans="1:15">
       <c r="A224" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>45</v>
@@ -10164,7 +9939,6 @@
       <c r="D224" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E224" s="2"/>
       <c r="G224" s="2" t="str">
         <f t="shared" si="7"/>
         <v>胡晓惠</v>
@@ -10174,7 +9948,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M224" s="2" t="s">
         <v>45</v>
@@ -10186,9 +9960,9 @@
         <v>353</v>
       </c>
     </row>
-    <row r="225" customHeight="1" spans="1:15">
+    <row r="225" hidden="1" customHeight="1" spans="1:15">
       <c r="A225" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>35</v>
@@ -10199,7 +9973,6 @@
       <c r="D225" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E225" s="2"/>
       <c r="G225" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10209,21 +9982,21 @@
         <v>框架</v>
       </c>
       <c r="L225" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="M225" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N225" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O225" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="226" hidden="1" customHeight="1" spans="1:15">
+      <c r="A226" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="M225" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N225" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O225" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="226" customHeight="1" spans="1:15">
-      <c r="A226" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>14</v>
@@ -10234,7 +10007,6 @@
       <c r="D226" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E226" s="2"/>
       <c r="G226" s="2" t="str">
         <f t="shared" si="7"/>
         <v>杜鑫鑫</v>
@@ -10244,7 +10016,7 @@
         <v>维护部门</v>
       </c>
       <c r="L226" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="M226" s="2" t="s">
         <v>14</v>
@@ -10256,9 +10028,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="227" customHeight="1" spans="1:15">
+    <row r="227" hidden="1" customHeight="1" spans="1:15">
       <c r="A227" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>35</v>
@@ -10269,7 +10041,6 @@
       <c r="D227" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E227" s="2"/>
       <c r="G227" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10279,21 +10050,21 @@
         <v>框架</v>
       </c>
       <c r="L227" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="M227" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N227" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O227" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="228" hidden="1" customHeight="1" spans="1:15">
+      <c r="A228" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="M227" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N227" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O227" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="228" customHeight="1" spans="1:15">
-      <c r="A228" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>45</v>
@@ -10304,7 +10075,6 @@
       <c r="D228" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E228" s="2"/>
       <c r="G228" s="2" t="str">
         <f t="shared" si="7"/>
         <v>胡晓惠</v>
@@ -10314,7 +10084,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L228" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M228" s="2" t="s">
         <v>45</v>
@@ -10326,9 +10096,9 @@
         <v>353</v>
       </c>
     </row>
-    <row r="229" customHeight="1" spans="1:15">
+    <row r="229" hidden="1" customHeight="1" spans="1:15">
       <c r="A229" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>35</v>
@@ -10339,7 +10109,6 @@
       <c r="D229" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E229" s="2"/>
       <c r="G229" s="2" t="str">
         <f t="shared" si="7"/>
         <v>框架</v>
@@ -10349,21 +10118,21 @@
         <v>框架</v>
       </c>
       <c r="L229" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="M229" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N229" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O229" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="230" hidden="1" customHeight="1" spans="1:15">
+      <c r="A230" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="M229" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N229" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O229" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="230" customHeight="1" spans="1:15">
-      <c r="A230" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>45</v>
@@ -10374,7 +10143,6 @@
       <c r="D230" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E230" s="2"/>
       <c r="G230" s="2" t="str">
         <f t="shared" si="7"/>
         <v>周莉莉</v>
@@ -10384,7 +10152,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M230" s="2" t="s">
         <v>45</v>
@@ -10396,9 +10164,9 @@
         <v>415</v>
       </c>
     </row>
-    <row r="231" customHeight="1" spans="1:15">
+    <row r="231" hidden="1" customHeight="1" spans="1:15">
       <c r="A231" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>35</v>
@@ -10409,9 +10177,8 @@
       <c r="D231" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E231" s="2"/>
       <c r="G231" s="2" t="str">
-        <f>D231</f>
+        <f t="shared" si="7"/>
         <v>框架</v>
       </c>
       <c r="H231" s="2" t="str">
@@ -10419,22 +10186,22 @@
         <v>框架</v>
       </c>
       <c r="L231" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="M231" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N231" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O231" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="232" hidden="1" customHeight="1" spans="1:15">
+      <c r="A232" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="M231" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N231" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O231" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="232" customHeight="1" spans="1:15">
-      <c r="A232" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="B232" s="2" t="s">
         <v>35</v>
       </c>
@@ -10444,7 +10211,6 @@
       <c r="D232" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E232" s="2"/>
       <c r="G232" s="2" t="str">
         <f t="shared" ref="G231:G232" si="10">D232</f>
         <v>框架</v>
@@ -10454,22 +10220,22 @@
         <v>框架</v>
       </c>
       <c r="L232" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="M232" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N232" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O232" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="233" hidden="1" customHeight="1" spans="1:15">
+      <c r="A233" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="M232" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N232" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O232" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="233" customHeight="1" spans="1:15">
-      <c r="A233" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="B233" s="2" t="s">
         <v>35</v>
       </c>
@@ -10479,7 +10245,6 @@
       <c r="D233" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E233" s="2"/>
       <c r="G233" s="2" t="str">
         <f t="shared" ref="G233" si="11">D233</f>
         <v>框架</v>
@@ -10489,22 +10254,22 @@
         <v>框架</v>
       </c>
       <c r="L233" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="M233" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N233" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O233" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="234" hidden="1" customHeight="1" spans="1:15">
+      <c r="A234" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="M233" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N233" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O233" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="234" customHeight="1" spans="1:15">
-      <c r="A234" s="2" t="s">
-        <v>439</v>
-      </c>
       <c r="B234" s="2" t="s">
         <v>35</v>
       </c>
@@ -10514,7 +10279,6 @@
       <c r="D234" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E234" s="2"/>
       <c r="G234" s="2" t="str">
         <f t="shared" ref="G234" si="13">D234</f>
         <v>框架</v>
@@ -10524,21 +10288,21 @@
         <v>框架</v>
       </c>
       <c r="L234" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="M234" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N234" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O234" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="235" hidden="1" spans="1:15">
+      <c r="A235" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="M234" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N234" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O234" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="235" spans="1:15">
-      <c r="A235" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>6</v>
@@ -10549,7 +10313,6 @@
       <c r="D235" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="E235" s="2"/>
       <c r="G235" s="2" t="str">
         <f t="shared" ref="G235:G236" si="15">D235</f>
         <v>叶惠</v>
@@ -10559,7 +10322,7 @@
         <v>新开部门</v>
       </c>
       <c r="L235" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M235" s="2" t="s">
         <v>6</v>
@@ -10571,9 +10334,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" hidden="1" spans="1:15">
       <c r="A236" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>45</v>
@@ -10582,9 +10345,8 @@
         <v>350</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="E236" s="2"/>
+        <v>441</v>
+      </c>
       <c r="G236" s="2" t="str">
         <f t="shared" si="15"/>
         <v>厦门自营电商</v>
@@ -10594,7 +10356,7 @@
         <v>行发维护大区</v>
       </c>
       <c r="L236" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M236" s="2" t="s">
         <v>45</v>
@@ -10603,10 +10365,18 @@
         <v>350</v>
       </c>
       <c r="O236" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D236">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="equal" val="xmk02"/>
+      </customFilters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="A2:A232">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/通讯录.xlsx
+++ b/通讯录.xlsx
@@ -1350,10 +1350,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1377,8 +1377,23 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1391,39 +1406,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1445,6 +1437,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1453,8 +1452,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1468,11 +1475,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1484,31 +1499,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1536,13 +1536,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1554,73 +1608,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1638,55 +1674,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1698,19 +1710,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1721,6 +1721,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1754,26 +1763,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1785,6 +1774,17 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1827,10 +1827,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1839,133 +1839,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2333,7 +2333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:O236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -2378,7 +2378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" hidden="1" customHeight="1" spans="1:15">
+    <row r="2" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" hidden="1" customHeight="1" spans="1:15">
+    <row r="3" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" hidden="1" customHeight="1" spans="1:15">
+    <row r="4" customHeight="1" spans="1:15">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" hidden="1" customHeight="1" spans="1:15">
+    <row r="5" customHeight="1" spans="1:15">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" hidden="1" customHeight="1" spans="1:15">
+    <row r="6" customHeight="1" spans="1:15">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" hidden="1" customHeight="1" spans="1:15">
+    <row r="7" customHeight="1" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" hidden="1" customHeight="1" spans="1:15">
+    <row r="8" customHeight="1" spans="1:15">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" hidden="1" customHeight="1" spans="1:15">
+    <row r="9" customHeight="1" spans="1:15">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -2650,7 +2650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" hidden="1" customHeight="1" spans="1:15">
+    <row r="10" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" hidden="1" customHeight="1" spans="1:15">
+    <row r="11" customHeight="1" spans="1:15">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" hidden="1" customHeight="1" spans="1:15">
+    <row r="12" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" hidden="1" customHeight="1" spans="1:15">
+    <row r="13" customHeight="1" spans="1:15">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" hidden="1" customHeight="1" spans="1:15">
+    <row r="14" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" hidden="1" customHeight="1" spans="1:15">
+    <row r="15" customHeight="1" spans="1:15">
       <c r="A15" s="2" t="s">
         <v>48</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" hidden="1" customHeight="1" spans="1:15">
+    <row r="16" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" hidden="1" customHeight="1" spans="1:15">
+    <row r="17" customHeight="1" spans="1:15">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" hidden="1" customHeight="1" spans="1:15">
+    <row r="18" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" hidden="1" customHeight="1" spans="1:15">
+    <row r="19" customHeight="1" spans="1:15">
       <c r="A19" s="2" t="s">
         <v>53</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" hidden="1" customHeight="1" spans="1:15">
+    <row r="20" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
         <v>54</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" hidden="1" customHeight="1" spans="1:15">
+    <row r="21" customHeight="1" spans="1:15">
       <c r="A21" s="2" t="s">
         <v>55</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" hidden="1" customHeight="1" spans="1:15">
+    <row r="22" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
         <v>56</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" hidden="1" customHeight="1" spans="1:15">
+    <row r="23" customHeight="1" spans="1:15">
       <c r="A23" s="2" t="s">
         <v>57</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" hidden="1" customHeight="1" spans="1:15">
+    <row r="24" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
         <v>58</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" hidden="1" customHeight="1" spans="1:15">
+    <row r="25" customHeight="1" spans="1:15">
       <c r="A25" s="2" t="s">
         <v>59</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" hidden="1" customHeight="1" spans="1:15">
+    <row r="26" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
         <v>60</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" hidden="1" customHeight="1" spans="1:15">
+    <row r="27" customHeight="1" spans="1:15">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" hidden="1" customHeight="1" spans="1:15">
+    <row r="28" customHeight="1" spans="1:15">
       <c r="A28" s="2" t="s">
         <v>62</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" hidden="1" customHeight="1" spans="1:15">
+    <row r="29" customHeight="1" spans="1:15">
       <c r="A29" s="2" t="s">
         <v>63</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" hidden="1" customHeight="1" spans="1:15">
+    <row r="30" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" hidden="1" customHeight="1" spans="1:15">
+    <row r="31" customHeight="1" spans="1:15">
       <c r="A31" s="2" t="s">
         <v>65</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" hidden="1" customHeight="1" spans="1:15">
+    <row r="32" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
         <v>66</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" hidden="1" customHeight="1" spans="1:15">
+    <row r="33" customHeight="1" spans="1:15">
       <c r="A33" s="2" t="s">
         <v>67</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" hidden="1" customHeight="1" spans="1:15">
+    <row r="34" customHeight="1" spans="1:15">
       <c r="A34" s="2" t="s">
         <v>68</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" hidden="1" customHeight="1" spans="1:15">
+    <row r="35" customHeight="1" spans="1:15">
       <c r="A35" s="2" t="s">
         <v>69</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" hidden="1" customHeight="1" spans="1:15">
+    <row r="36" customHeight="1" spans="1:15">
       <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" hidden="1" customHeight="1" spans="1:15">
+    <row r="37" customHeight="1" spans="1:15">
       <c r="A37" s="2" t="s">
         <v>71</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" hidden="1" customHeight="1" spans="1:15">
+    <row r="38" customHeight="1" spans="1:15">
       <c r="A38" s="2" t="s">
         <v>72</v>
       </c>
@@ -3636,7 +3636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" hidden="1" customHeight="1" spans="1:15">
+    <row r="39" customHeight="1" spans="1:15">
       <c r="A39" s="2" t="s">
         <v>73</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" hidden="1" customHeight="1" spans="1:15">
+    <row r="40" customHeight="1" spans="1:15">
       <c r="A40" s="2" t="s">
         <v>74</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" hidden="1" customHeight="1" spans="1:15">
+    <row r="41" customHeight="1" spans="1:15">
       <c r="A41" s="2" t="s">
         <v>75</v>
       </c>
@@ -3738,7 +3738,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" hidden="1" customHeight="1" spans="1:15">
+    <row r="42" customHeight="1" spans="1:15">
       <c r="A42" s="2" t="s">
         <v>76</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" hidden="1" customHeight="1" spans="1:15">
+    <row r="43" customHeight="1" spans="1:15">
       <c r="A43" s="2" t="s">
         <v>77</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" hidden="1" customHeight="1" spans="1:15">
+    <row r="44" customHeight="1" spans="1:15">
       <c r="A44" s="2" t="s">
         <v>78</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" hidden="1" customHeight="1" spans="1:15">
+    <row r="45" customHeight="1" spans="1:15">
       <c r="A45" s="2" t="s">
         <v>79</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" hidden="1" customHeight="1" spans="1:15">
+    <row r="46" customHeight="1" spans="1:15">
       <c r="A46" s="2" t="s">
         <v>80</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" hidden="1" customHeight="1" spans="1:15">
+    <row r="47" customHeight="1" spans="1:15">
       <c r="A47" s="2" t="s">
         <v>81</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" hidden="1" customHeight="1" spans="1:15">
+    <row r="48" customHeight="1" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>82</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" hidden="1" customHeight="1" spans="1:15">
+    <row r="49" customHeight="1" spans="1:15">
       <c r="A49" s="2" t="s">
         <v>83</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" hidden="1" customHeight="1" spans="1:15">
+    <row r="50" customHeight="1" spans="1:15">
       <c r="A50" s="2" t="s">
         <v>84</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" hidden="1" customHeight="1" spans="1:15">
+    <row r="51" customHeight="1" spans="1:15">
       <c r="A51" s="2" t="s">
         <v>85</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" hidden="1" customHeight="1" spans="1:15">
+    <row r="52" customHeight="1" spans="1:15">
       <c r="A52" s="2" t="s">
         <v>86</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" hidden="1" customHeight="1" spans="1:15">
+    <row r="53" customHeight="1" spans="1:15">
       <c r="A53" s="2" t="s">
         <v>87</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" hidden="1" customHeight="1" spans="1:15">
+    <row r="54" customHeight="1" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>88</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" hidden="1" customHeight="1" spans="1:15">
+    <row r="55" customHeight="1" spans="1:15">
       <c r="A55" s="2" t="s">
         <v>89</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" hidden="1" customHeight="1" spans="1:15">
+    <row r="56" customHeight="1" spans="1:15">
       <c r="A56" s="2" t="s">
         <v>90</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" hidden="1" customHeight="1" spans="1:15">
+    <row r="57" customHeight="1" spans="1:15">
       <c r="A57" s="2" t="s">
         <v>91</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" hidden="1" customHeight="1" spans="1:15">
+    <row r="58" customHeight="1" spans="1:15">
       <c r="A58" s="2" t="s">
         <v>93</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="59" hidden="1" customHeight="1" spans="1:15">
+    <row r="59" customHeight="1" spans="1:15">
       <c r="A59" s="2" t="s">
         <v>95</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" hidden="1" customHeight="1" spans="1:15">
+    <row r="60" customHeight="1" spans="1:15">
       <c r="A60" s="2" t="s">
         <v>97</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61" hidden="1" customHeight="1" spans="1:15">
+    <row r="61" customHeight="1" spans="1:15">
       <c r="A61" s="2" t="s">
         <v>100</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" hidden="1" customHeight="1" spans="1:15">
+    <row r="62" customHeight="1" spans="1:15">
       <c r="A62" s="2" t="s">
         <v>103</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" hidden="1" customHeight="1" spans="1:15">
+    <row r="63" customHeight="1" spans="1:15">
       <c r="A63" s="2" t="s">
         <v>107</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="64" hidden="1" customHeight="1" spans="1:15">
+    <row r="64" customHeight="1" spans="1:15">
       <c r="A64" s="2" t="s">
         <v>109</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="65" hidden="1" customHeight="1" spans="1:15">
+    <row r="65" customHeight="1" spans="1:15">
       <c r="A65" s="2" t="s">
         <v>111</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="66" hidden="1" customHeight="1" spans="1:15">
+    <row r="66" customHeight="1" spans="1:15">
       <c r="A66" s="2" t="s">
         <v>114</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" hidden="1" customHeight="1" spans="1:15">
+    <row r="67" customHeight="1" spans="1:15">
       <c r="A67" s="2" t="s">
         <v>116</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" hidden="1" customHeight="1" spans="1:15">
+    <row r="68" customHeight="1" spans="1:15">
       <c r="A68" s="2" t="s">
         <v>119</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" hidden="1" customHeight="1" spans="1:15">
+    <row r="69" customHeight="1" spans="1:15">
       <c r="A69" s="2" t="s">
         <v>120</v>
       </c>
@@ -4690,7 +4690,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" hidden="1" customHeight="1" spans="1:15">
+    <row r="70" customHeight="1" spans="1:15">
       <c r="A70" s="2" t="s">
         <v>121</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" hidden="1" customHeight="1" spans="1:15">
+    <row r="71" customHeight="1" spans="1:15">
       <c r="A71" s="2" t="s">
         <v>124</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="72" hidden="1" customHeight="1" spans="1:15">
+    <row r="72" customHeight="1" spans="1:15">
       <c r="A72" s="2" t="s">
         <v>127</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="73" hidden="1" customHeight="1" spans="1:15">
+    <row r="73" customHeight="1" spans="1:15">
       <c r="A73" s="2" t="s">
         <v>129</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="74" hidden="1" customHeight="1" spans="1:15">
+    <row r="74" customHeight="1" spans="1:15">
       <c r="A74" s="2" t="s">
         <v>131</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="75" hidden="1" customHeight="1" spans="1:15">
+    <row r="75" customHeight="1" spans="1:15">
       <c r="A75" s="2" t="s">
         <v>133</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="76" hidden="1" customHeight="1" spans="1:15">
+    <row r="76" customHeight="1" spans="1:15">
       <c r="A76" s="2" t="s">
         <v>135</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="77" hidden="1" customHeight="1" spans="1:15">
+    <row r="77" customHeight="1" spans="1:15">
       <c r="A77" s="2" t="s">
         <v>137</v>
       </c>
@@ -4962,7 +4962,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="78" hidden="1" customHeight="1" spans="1:15">
+    <row r="78" customHeight="1" spans="1:15">
       <c r="A78" s="2" t="s">
         <v>140</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" hidden="1" customHeight="1" spans="1:15">
+    <row r="79" customHeight="1" spans="1:15">
       <c r="A79" s="2" t="s">
         <v>142</v>
       </c>
@@ -5030,7 +5030,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="80" hidden="1" customHeight="1" spans="1:15">
+    <row r="80" customHeight="1" spans="1:15">
       <c r="A80" s="2" t="s">
         <v>145</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="81" hidden="1" customHeight="1" spans="1:15">
+    <row r="81" customHeight="1" spans="1:15">
       <c r="A81" s="2" t="s">
         <v>148</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="82" hidden="1" customHeight="1" spans="1:15">
+    <row r="82" customHeight="1" spans="1:15">
       <c r="A82" s="2" t="s">
         <v>150</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" hidden="1" customHeight="1" spans="1:15">
+    <row r="83" customHeight="1" spans="1:15">
       <c r="A83" s="2" t="s">
         <v>152</v>
       </c>
@@ -5166,7 +5166,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="84" hidden="1" customHeight="1" spans="1:15">
+    <row r="84" customHeight="1" spans="1:15">
       <c r="A84" s="2" t="s">
         <v>154</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="85" hidden="1" customHeight="1" spans="1:15">
+    <row r="85" customHeight="1" spans="1:15">
       <c r="A85" s="2" t="s">
         <v>156</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="86" hidden="1" customHeight="1" spans="1:15">
+    <row r="86" customHeight="1" spans="1:15">
       <c r="A86" s="2" t="s">
         <v>158</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="87" hidden="1" customHeight="1" spans="1:15">
+    <row r="87" customHeight="1" spans="1:15">
       <c r="A87" s="2" t="s">
         <v>161</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="88" hidden="1" customHeight="1" spans="1:15">
+    <row r="88" customHeight="1" spans="1:15">
       <c r="A88" s="2" t="s">
         <v>163</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="89" hidden="1" customHeight="1" spans="1:15">
+    <row r="89" customHeight="1" spans="1:15">
       <c r="A89" s="2" t="s">
         <v>165</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="90" hidden="1" customHeight="1" spans="1:15">
+    <row r="90" customHeight="1" spans="1:15">
       <c r="A90" s="2" t="s">
         <v>167</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="91" hidden="1" customHeight="1" spans="1:15">
+    <row r="91" customHeight="1" spans="1:15">
       <c r="A91" s="2" t="s">
         <v>169</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="92" hidden="1" customHeight="1" spans="1:15">
+    <row r="92" customHeight="1" spans="1:15">
       <c r="A92" s="2" t="s">
         <v>172</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="93" hidden="1" customHeight="1" spans="1:15">
+    <row r="93" customHeight="1" spans="1:15">
       <c r="A93" s="2" t="s">
         <v>174</v>
       </c>
@@ -5506,7 +5506,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="94" hidden="1" customHeight="1" spans="1:15">
+    <row r="94" customHeight="1" spans="1:15">
       <c r="A94" s="2" t="s">
         <v>176</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="95" hidden="1" customHeight="1" spans="1:15">
+    <row r="95" customHeight="1" spans="1:15">
       <c r="A95" s="2" t="s">
         <v>178</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="96" hidden="1" customHeight="1" spans="1:15">
+    <row r="96" customHeight="1" spans="1:15">
       <c r="A96" s="2" t="s">
         <v>180</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="97" hidden="1" customHeight="1" spans="1:15">
+    <row r="97" customHeight="1" spans="1:15">
       <c r="A97" s="2" t="s">
         <v>182</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="98" hidden="1" customHeight="1" spans="1:15">
+    <row r="98" customHeight="1" spans="1:15">
       <c r="A98" s="2" t="s">
         <v>184</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="99" hidden="1" customHeight="1" spans="1:15">
+    <row r="99" customHeight="1" spans="1:15">
       <c r="A99" s="2" t="s">
         <v>186</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="100" hidden="1" customHeight="1" spans="1:15">
+    <row r="100" customHeight="1" spans="1:15">
       <c r="A100" s="2" t="s">
         <v>188</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="101" hidden="1" customHeight="1" spans="1:15">
+    <row r="101" customHeight="1" spans="1:15">
       <c r="A101" s="2" t="s">
         <v>191</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="102" hidden="1" customHeight="1" spans="1:15">
+    <row r="102" customHeight="1" spans="1:15">
       <c r="A102" s="2" t="s">
         <v>193</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="103" hidden="1" customHeight="1" spans="1:15">
+    <row r="103" customHeight="1" spans="1:15">
       <c r="A103" s="2" t="s">
         <v>195</v>
       </c>
@@ -5846,7 +5846,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="104" hidden="1" customHeight="1" spans="1:15">
+    <row r="104" customHeight="1" spans="1:15">
       <c r="A104" s="2" t="s">
         <v>197</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="105" hidden="1" customHeight="1" spans="1:15">
+    <row r="105" customHeight="1" spans="1:15">
       <c r="A105" s="2" t="s">
         <v>199</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" hidden="1" customHeight="1" spans="1:15">
+    <row r="106" customHeight="1" spans="1:15">
       <c r="A106" s="2" t="s">
         <v>201</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="107" hidden="1" customHeight="1" spans="1:15">
+    <row r="107" customHeight="1" spans="1:15">
       <c r="A107" s="2" t="s">
         <v>203</v>
       </c>
@@ -5982,7 +5982,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="108" hidden="1" customHeight="1" spans="1:15">
+    <row r="108" customHeight="1" spans="1:15">
       <c r="A108" s="2" t="s">
         <v>205</v>
       </c>
@@ -6016,7 +6016,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="109" hidden="1" customHeight="1" spans="1:15">
+    <row r="109" customHeight="1" spans="1:15">
       <c r="A109" s="2" t="s">
         <v>207</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="110" hidden="1" customHeight="1" spans="1:15">
+    <row r="110" customHeight="1" spans="1:15">
       <c r="A110" s="2" t="s">
         <v>209</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="111" hidden="1" customHeight="1" spans="1:15">
+    <row r="111" customHeight="1" spans="1:15">
       <c r="A111" s="2" t="s">
         <v>211</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="112" hidden="1" customHeight="1" spans="1:15">
+    <row r="112" customHeight="1" spans="1:15">
       <c r="A112" s="2" t="s">
         <v>212</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="113" hidden="1" customHeight="1" spans="1:15">
+    <row r="113" customHeight="1" spans="1:15">
       <c r="A113" s="2" t="s">
         <v>214</v>
       </c>
@@ -6186,7 +6186,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="114" hidden="1" customHeight="1" spans="1:15">
+    <row r="114" customHeight="1" spans="1:15">
       <c r="A114" s="2" t="s">
         <v>216</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="115" hidden="1" customHeight="1" spans="1:15">
+    <row r="115" customHeight="1" spans="1:15">
       <c r="A115" s="2" t="s">
         <v>218</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="116" hidden="1" customHeight="1" spans="1:15">
+    <row r="116" customHeight="1" spans="1:15">
       <c r="A116" s="2" t="s">
         <v>220</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="117" hidden="1" customHeight="1" spans="1:15">
+    <row r="117" customHeight="1" spans="1:15">
       <c r="A117" s="2" t="s">
         <v>222</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="118" hidden="1" customHeight="1" spans="1:15">
+    <row r="118" customHeight="1" spans="1:15">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="119" hidden="1" customHeight="1" spans="1:15">
+    <row r="119" customHeight="1" spans="1:15">
       <c r="A119" s="2" t="s">
         <v>226</v>
       </c>
@@ -6390,7 +6390,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="120" hidden="1" customHeight="1" spans="1:15">
+    <row r="120" customHeight="1" spans="1:15">
       <c r="A120" s="2" t="s">
         <v>227</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="121" hidden="1" customHeight="1" spans="1:15">
+    <row r="121" customHeight="1" spans="1:15">
       <c r="A121" s="2" t="s">
         <v>229</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="122" hidden="1" customHeight="1" spans="1:15">
+    <row r="122" customHeight="1" spans="1:15">
       <c r="A122" s="2" t="s">
         <v>232</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="123" hidden="1" customHeight="1" spans="1:15">
+    <row r="123" customHeight="1" spans="1:15">
       <c r="A123" s="2" t="s">
         <v>234</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="124" hidden="1" customHeight="1" spans="1:15">
+    <row r="124" customHeight="1" spans="1:15">
       <c r="A124" s="2" t="s">
         <v>238</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="125" hidden="1" customHeight="1" spans="1:15">
+    <row r="125" customHeight="1" spans="1:15">
       <c r="A125" s="2" t="s">
         <v>241</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="126" hidden="1" customHeight="1" spans="1:15">
+    <row r="126" customHeight="1" spans="1:15">
       <c r="A126" s="2" t="s">
         <v>243</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:15">
+    <row r="127" spans="1:15">
       <c r="A127" s="2" t="s">
         <v>245</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="128" hidden="1" customHeight="1" spans="1:15">
+    <row r="128" customHeight="1" spans="1:15">
       <c r="A128" s="2" t="s">
         <v>247</v>
       </c>
@@ -6696,7 +6696,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="129" hidden="1" customHeight="1" spans="1:15">
+    <row r="129" customHeight="1" spans="1:15">
       <c r="A129" s="2" t="s">
         <v>250</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="130" hidden="1" customHeight="1" spans="1:15">
+    <row r="130" customHeight="1" spans="1:15">
       <c r="A130" s="2" t="s">
         <v>252</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="131" hidden="1" customHeight="1" spans="1:15">
+    <row r="131" customHeight="1" spans="1:15">
       <c r="A131" s="2" t="s">
         <v>254</v>
       </c>
@@ -6798,7 +6798,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="132" hidden="1" customHeight="1" spans="1:15">
+    <row r="132" customHeight="1" spans="1:15">
       <c r="A132" s="2" t="s">
         <v>256</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="133" hidden="1" customHeight="1" spans="1:15">
+    <row r="133" customHeight="1" spans="1:15">
       <c r="A133" s="2" t="s">
         <v>258</v>
       </c>
@@ -6866,7 +6866,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="134" hidden="1" customHeight="1" spans="1:15">
+    <row r="134" customHeight="1" spans="1:15">
       <c r="A134" s="2" t="s">
         <v>260</v>
       </c>
@@ -6900,7 +6900,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="135" hidden="1" customHeight="1" spans="1:15">
+    <row r="135" customHeight="1" spans="1:15">
       <c r="A135" s="2" t="s">
         <v>262</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="136" hidden="1" customHeight="1" spans="1:15">
+    <row r="136" customHeight="1" spans="1:15">
       <c r="A136" s="2" t="s">
         <v>264</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="137" hidden="1" customHeight="1" spans="1:15">
+    <row r="137" customHeight="1" spans="1:15">
       <c r="A137" s="2" t="s">
         <v>265</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="138" hidden="1" customHeight="1" spans="1:15">
+    <row r="138" customHeight="1" spans="1:15">
       <c r="A138" s="2" t="s">
         <v>266</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="139" hidden="1" customHeight="1" spans="1:15">
+    <row r="139" customHeight="1" spans="1:15">
       <c r="A139" s="2" t="s">
         <v>269</v>
       </c>
@@ -7070,7 +7070,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="140" hidden="1" customHeight="1" spans="1:15">
+    <row r="140" customHeight="1" spans="1:15">
       <c r="A140" s="2" t="s">
         <v>272</v>
       </c>
@@ -7104,7 +7104,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="141" hidden="1" customHeight="1" spans="1:15">
+    <row r="141" customHeight="1" spans="1:15">
       <c r="A141" s="2" t="s">
         <v>274</v>
       </c>
@@ -7138,7 +7138,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" hidden="1" customHeight="1" spans="1:15">
+    <row r="142" customHeight="1" spans="1:15">
       <c r="A142" s="2" t="s">
         <v>276</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="143" hidden="1" customHeight="1" spans="1:15">
+    <row r="143" customHeight="1" spans="1:15">
       <c r="A143" s="2" t="s">
         <v>278</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="144" hidden="1" customHeight="1" spans="1:15">
+    <row r="144" customHeight="1" spans="1:15">
       <c r="A144" s="2" t="s">
         <v>280</v>
       </c>
@@ -7240,7 +7240,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="145" hidden="1" customHeight="1" spans="1:15">
+    <row r="145" customHeight="1" spans="1:15">
       <c r="A145" s="2" t="s">
         <v>282</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="146" hidden="1" customHeight="1" spans="1:15">
+    <row r="146" customHeight="1" spans="1:15">
       <c r="A146" s="2" t="s">
         <v>284</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="147" hidden="1" customHeight="1" spans="1:15">
+    <row r="147" customHeight="1" spans="1:15">
       <c r="A147" s="2" t="s">
         <v>286</v>
       </c>
@@ -7342,7 +7342,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="148" hidden="1" customHeight="1" spans="1:15">
+    <row r="148" customHeight="1" spans="1:15">
       <c r="A148" s="2" t="s">
         <v>289</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="149" hidden="1" customHeight="1" spans="1:15">
+    <row r="149" customHeight="1" spans="1:15">
       <c r="A149" s="2" t="s">
         <v>290</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="150" hidden="1" customHeight="1" spans="1:15">
+    <row r="150" customHeight="1" spans="1:15">
       <c r="A150" s="2" t="s">
         <v>291</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" hidden="1" customHeight="1" spans="1:15">
+    <row r="151" customHeight="1" spans="1:15">
       <c r="A151" s="2" t="s">
         <v>293</v>
       </c>
@@ -7478,7 +7478,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="152" hidden="1" customHeight="1" spans="1:15">
+    <row r="152" customHeight="1" spans="1:15">
       <c r="A152" s="2" t="s">
         <v>295</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="153" hidden="1" customHeight="1" spans="1:15">
+    <row r="153" customHeight="1" spans="1:15">
       <c r="A153" s="2" t="s">
         <v>297</v>
       </c>
@@ -7546,7 +7546,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="154" hidden="1" customHeight="1" spans="1:15">
+    <row r="154" customHeight="1" spans="1:15">
       <c r="A154" s="2" t="s">
         <v>299</v>
       </c>
@@ -7580,7 +7580,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="155" hidden="1" customHeight="1" spans="1:15">
+    <row r="155" customHeight="1" spans="1:15">
       <c r="A155" s="2" t="s">
         <v>301</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="156" hidden="1" customHeight="1" spans="1:15">
+    <row r="156" customHeight="1" spans="1:15">
       <c r="A156" s="2" t="s">
         <v>303</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="157" hidden="1" customHeight="1" spans="1:15">
+    <row r="157" customHeight="1" spans="1:15">
       <c r="A157" s="2" t="s">
         <v>305</v>
       </c>
@@ -7682,7 +7682,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="158" hidden="1" customHeight="1" spans="1:15">
+    <row r="158" customHeight="1" spans="1:15">
       <c r="A158" s="2" t="s">
         <v>307</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="159" hidden="1" customHeight="1" spans="1:15">
+    <row r="159" customHeight="1" spans="1:15">
       <c r="A159" s="2" t="s">
         <v>309</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="160" hidden="1" customHeight="1" spans="1:15">
+    <row r="160" customHeight="1" spans="1:15">
       <c r="A160" s="2" t="s">
         <v>311</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="161" hidden="1" customHeight="1" spans="1:15">
+    <row r="161" customHeight="1" spans="1:15">
       <c r="A161" s="2" t="s">
         <v>313</v>
       </c>
@@ -7818,7 +7818,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="162" hidden="1" customHeight="1" spans="1:15">
+    <row r="162" customHeight="1" spans="1:15">
       <c r="A162" s="2" t="s">
         <v>315</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="163" hidden="1" customHeight="1" spans="1:15">
+    <row r="163" customHeight="1" spans="1:15">
       <c r="A163" s="2" t="s">
         <v>317</v>
       </c>
@@ -7886,7 +7886,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="164" hidden="1" customHeight="1" spans="1:15">
+    <row r="164" customHeight="1" spans="1:15">
       <c r="A164" s="2" t="s">
         <v>319</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="165" hidden="1" customHeight="1" spans="1:15">
+    <row r="165" customHeight="1" spans="1:15">
       <c r="A165" s="2" t="s">
         <v>321</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="166" hidden="1" customHeight="1" spans="1:15">
+    <row r="166" customHeight="1" spans="1:15">
       <c r="A166" s="2" t="s">
         <v>323</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="167" hidden="1" customHeight="1" spans="1:15">
+    <row r="167" customHeight="1" spans="1:15">
       <c r="A167" s="2" t="s">
         <v>325</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="168" hidden="1" customHeight="1" spans="1:15">
+    <row r="168" customHeight="1" spans="1:15">
       <c r="A168" s="2" t="s">
         <v>327</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="169" hidden="1" customHeight="1" spans="1:15">
+    <row r="169" customHeight="1" spans="1:15">
       <c r="A169" s="2" t="s">
         <v>329</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="170" hidden="1" customHeight="1" spans="1:15">
+    <row r="170" customHeight="1" spans="1:15">
       <c r="A170" s="2" t="s">
         <v>331</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" hidden="1" customHeight="1" spans="1:15">
+    <row r="171" customHeight="1" spans="1:15">
       <c r="A171" s="2" t="s">
         <v>333</v>
       </c>
@@ -8158,7 +8158,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="172" hidden="1" customHeight="1" spans="1:15">
+    <row r="172" customHeight="1" spans="1:15">
       <c r="A172" s="2" t="s">
         <v>335</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="173" hidden="1" customHeight="1" spans="1:15">
+    <row r="173" customHeight="1" spans="1:15">
       <c r="A173" s="2" t="s">
         <v>339</v>
       </c>
@@ -8226,7 +8226,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="174" hidden="1" customHeight="1" spans="1:15">
+    <row r="174" customHeight="1" spans="1:15">
       <c r="A174" s="2" t="s">
         <v>341</v>
       </c>
@@ -8260,7 +8260,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="175" hidden="1" customHeight="1" spans="1:15">
+    <row r="175" customHeight="1" spans="1:15">
       <c r="A175" s="2" t="s">
         <v>343</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="176" hidden="1" customHeight="1" spans="1:15">
+    <row r="176" customHeight="1" spans="1:15">
       <c r="A176" s="2" t="s">
         <v>345</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="177" hidden="1" customHeight="1" spans="1:15">
+    <row r="177" customHeight="1" spans="1:15">
       <c r="A177" s="2" t="s">
         <v>347</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="178" hidden="1" customHeight="1" spans="1:15">
+    <row r="178" customHeight="1" spans="1:15">
       <c r="A178" s="2" t="s">
         <v>349</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="179" hidden="1" customHeight="1" spans="1:15">
+    <row r="179" customHeight="1" spans="1:15">
       <c r="A179" s="2" t="s">
         <v>352</v>
       </c>
@@ -8430,7 +8430,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="180" hidden="1" customHeight="1" spans="1:15">
+    <row r="180" customHeight="1" spans="1:15">
       <c r="A180" s="2" t="s">
         <v>354</v>
       </c>
@@ -8464,7 +8464,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="181" hidden="1" customHeight="1" spans="1:15">
+    <row r="181" customHeight="1" spans="1:15">
       <c r="A181" s="2" t="s">
         <v>356</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="182" hidden="1" customHeight="1" spans="1:15">
+    <row r="182" customHeight="1" spans="1:15">
       <c r="A182" s="2" t="s">
         <v>358</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="183" hidden="1" customHeight="1" spans="1:15">
+    <row r="183" customHeight="1" spans="1:15">
       <c r="A183" s="2" t="s">
         <v>360</v>
       </c>
@@ -8566,7 +8566,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="184" hidden="1" customHeight="1" spans="1:15">
+    <row r="184" customHeight="1" spans="1:15">
       <c r="A184" s="2" t="s">
         <v>362</v>
       </c>
@@ -8600,7 +8600,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="185" hidden="1" customHeight="1" spans="1:15">
+    <row r="185" customHeight="1" spans="1:15">
       <c r="A185" s="2" t="s">
         <v>364</v>
       </c>
@@ -8634,7 +8634,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="186" hidden="1" customHeight="1" spans="1:15">
+    <row r="186" customHeight="1" spans="1:15">
       <c r="A186" s="2" t="s">
         <v>366</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="187" hidden="1" customHeight="1" spans="1:15">
+    <row r="187" customHeight="1" spans="1:15">
       <c r="A187" s="2" t="s">
         <v>368</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="188" hidden="1" customHeight="1" spans="1:15">
+    <row r="188" customHeight="1" spans="1:15">
       <c r="A188" s="2" t="s">
         <v>370</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="189" hidden="1" customHeight="1" spans="1:15">
+    <row r="189" customHeight="1" spans="1:15">
       <c r="A189" s="2" t="s">
         <v>372</v>
       </c>
@@ -8770,7 +8770,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="190" hidden="1" customHeight="1" spans="1:15">
+    <row r="190" customHeight="1" spans="1:15">
       <c r="A190" s="2" t="s">
         <v>373</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="191" hidden="1" customHeight="1" spans="1:15">
+    <row r="191" customHeight="1" spans="1:15">
       <c r="A191" s="2" t="s">
         <v>375</v>
       </c>
@@ -8838,7 +8838,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="192" hidden="1" customHeight="1" spans="1:15">
+    <row r="192" customHeight="1" spans="1:15">
       <c r="A192" s="2" t="s">
         <v>376</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" hidden="1" customHeight="1" spans="1:15">
+    <row r="193" customHeight="1" spans="1:15">
       <c r="A193" s="2" t="s">
         <v>379</v>
       </c>
@@ -8906,7 +8906,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="194" hidden="1" customHeight="1" spans="1:15">
+    <row r="194" customHeight="1" spans="1:15">
       <c r="A194" s="2" t="s">
         <v>381</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="195" hidden="1" customHeight="1" spans="1:15">
+    <row r="195" customHeight="1" spans="1:15">
       <c r="A195" s="2" t="s">
         <v>384</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" hidden="1" customHeight="1" spans="1:15">
+    <row r="196" customHeight="1" spans="1:15">
       <c r="A196" s="2" t="s">
         <v>385</v>
       </c>
@@ -9008,7 +9008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" hidden="1" customHeight="1" spans="1:15">
+    <row r="197" customHeight="1" spans="1:15">
       <c r="A197" s="2" t="s">
         <v>386</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" hidden="1" customHeight="1" spans="1:15">
+    <row r="198" customHeight="1" spans="1:15">
       <c r="A198" s="2" t="s">
         <v>387</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" hidden="1" customHeight="1" spans="1:15">
+    <row r="199" customHeight="1" spans="1:15">
       <c r="A199" s="2" t="s">
         <v>388</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="200" hidden="1" customHeight="1" spans="1:15">
+    <row r="200" customHeight="1" spans="1:15">
       <c r="A200" s="2" t="s">
         <v>391</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="201" hidden="1" customHeight="1" spans="1:15">
+    <row r="201" customHeight="1" spans="1:15">
       <c r="A201" s="2" t="s">
         <v>393</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="202" hidden="1" customHeight="1" spans="1:15">
+    <row r="202" customHeight="1" spans="1:15">
       <c r="A202" s="2" t="s">
         <v>394</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="203" hidden="1" customHeight="1" spans="1:15">
+    <row r="203" customHeight="1" spans="1:15">
       <c r="A203" s="2" t="s">
         <v>395</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" hidden="1" customHeight="1" spans="1:15">
+    <row r="204" customHeight="1" spans="1:15">
       <c r="A204" s="2" t="s">
         <v>396</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="205" hidden="1" customHeight="1" spans="1:15">
+    <row r="205" customHeight="1" spans="1:15">
       <c r="A205" s="2" t="s">
         <v>398</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="206" hidden="1" customHeight="1" spans="1:15">
+    <row r="206" customHeight="1" spans="1:15">
       <c r="A206" s="2" t="s">
         <v>400</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" hidden="1" customHeight="1" spans="1:15">
+    <row r="207" customHeight="1" spans="1:15">
       <c r="A207" s="2" t="s">
         <v>401</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="208" hidden="1" customHeight="1" spans="1:15">
+    <row r="208" customHeight="1" spans="1:15">
       <c r="A208" s="2" t="s">
         <v>402</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="209" hidden="1" customHeight="1" spans="1:15">
+    <row r="209" customHeight="1" spans="1:15">
       <c r="A209" s="2" t="s">
         <v>404</v>
       </c>
@@ -9450,7 +9450,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="210" hidden="1" customHeight="1" spans="1:15">
+    <row r="210" customHeight="1" spans="1:15">
       <c r="A210" s="2" t="s">
         <v>406</v>
       </c>
@@ -9484,7 +9484,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="211" hidden="1" customHeight="1" spans="1:15">
+    <row r="211" customHeight="1" spans="1:15">
       <c r="A211" s="2" t="s">
         <v>408</v>
       </c>
@@ -9518,7 +9518,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="212" hidden="1" customHeight="1" spans="1:15">
+    <row r="212" customHeight="1" spans="1:15">
       <c r="A212" s="2" t="s">
         <v>410</v>
       </c>
@@ -9552,7 +9552,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="213" hidden="1" customHeight="1" spans="1:15">
+    <row r="213" customHeight="1" spans="1:15">
       <c r="A213" s="2" t="s">
         <v>412</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="214" hidden="1" customHeight="1" spans="1:15">
+    <row r="214" customHeight="1" spans="1:15">
       <c r="A214" s="2" t="s">
         <v>414</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="216" hidden="1" customHeight="1" spans="1:15">
+    <row r="216" customHeight="1" spans="1:15">
       <c r="A216" s="2" t="s">
         <v>418</v>
       </c>
@@ -9688,7 +9688,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="217" hidden="1" customHeight="1" spans="1:15">
+    <row r="217" customHeight="1" spans="1:15">
       <c r="A217" s="2" t="s">
         <v>419</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="218" hidden="1" customHeight="1" spans="1:15">
+    <row r="218" customHeight="1" spans="1:15">
       <c r="A218" s="2" t="s">
         <v>420</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="219" hidden="1" customHeight="1" spans="1:15">
+    <row r="219" customHeight="1" spans="1:15">
       <c r="A219" s="2" t="s">
         <v>421</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="220" hidden="1" customHeight="1" spans="1:15">
+    <row r="220" customHeight="1" spans="1:15">
       <c r="A220" s="2" t="s">
         <v>423</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="221" hidden="1" customHeight="1" spans="1:15">
+    <row r="221" customHeight="1" spans="1:15">
       <c r="A221" s="2" t="s">
         <v>424</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="222" hidden="1" customHeight="1" spans="1:15">
+    <row r="222" customHeight="1" spans="1:15">
       <c r="A222" s="2" t="s">
         <v>425</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="223" hidden="1" customHeight="1" spans="1:15">
+    <row r="223" customHeight="1" spans="1:15">
       <c r="A223" s="2" t="s">
         <v>427</v>
       </c>
@@ -9926,7 +9926,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="224" hidden="1" customHeight="1" spans="1:15">
+    <row r="224" customHeight="1" spans="1:15">
       <c r="A224" s="2" t="s">
         <v>428</v>
       </c>
@@ -9960,7 +9960,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="225" hidden="1" customHeight="1" spans="1:15">
+    <row r="225" customHeight="1" spans="1:15">
       <c r="A225" s="2" t="s">
         <v>429</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="226" hidden="1" customHeight="1" spans="1:15">
+    <row r="226" customHeight="1" spans="1:15">
       <c r="A226" s="2" t="s">
         <v>430</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="227" hidden="1" customHeight="1" spans="1:15">
+    <row r="227" customHeight="1" spans="1:15">
       <c r="A227" s="2" t="s">
         <v>431</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="228" hidden="1" customHeight="1" spans="1:15">
+    <row r="228" customHeight="1" spans="1:15">
       <c r="A228" s="2" t="s">
         <v>432</v>
       </c>
@@ -10096,7 +10096,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="229" hidden="1" customHeight="1" spans="1:15">
+    <row r="229" customHeight="1" spans="1:15">
       <c r="A229" s="2" t="s">
         <v>433</v>
       </c>
@@ -10130,7 +10130,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="230" hidden="1" customHeight="1" spans="1:15">
+    <row r="230" customHeight="1" spans="1:15">
       <c r="A230" s="2" t="s">
         <v>434</v>
       </c>
@@ -10164,7 +10164,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="231" hidden="1" customHeight="1" spans="1:15">
+    <row r="231" customHeight="1" spans="1:15">
       <c r="A231" s="2" t="s">
         <v>435</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="232" hidden="1" customHeight="1" spans="1:15">
+    <row r="232" customHeight="1" spans="1:15">
       <c r="A232" s="2" t="s">
         <v>436</v>
       </c>
@@ -10232,7 +10232,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="233" hidden="1" customHeight="1" spans="1:15">
+    <row r="233" customHeight="1" spans="1:15">
       <c r="A233" s="2" t="s">
         <v>437</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="234" hidden="1" customHeight="1" spans="1:15">
+    <row r="234" customHeight="1" spans="1:15">
       <c r="A234" s="2" t="s">
         <v>438</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="235" hidden="1" spans="1:15">
+    <row r="235" spans="1:15">
       <c r="A235" s="2" t="s">
         <v>439</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="236" hidden="1" spans="1:15">
+    <row r="236" spans="1:15">
       <c r="A236" s="2" t="s">
         <v>440</v>
       </c>
@@ -10369,14 +10369,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D236">
-    <filterColumn colId="0">
-      <customFilters>
-        <customFilter operator="equal" val="xmk02"/>
-      </customFilters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <conditionalFormatting sqref="A2:A232">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
